--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Water year - Rapel" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Daily" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Reservoirs" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Method" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2010,7 +2011,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total_Mm3 = Colbún + Rapel + Ralco + Pangue + Lago Laja (Laguna de La Laja) + Laguna del Maule - the six reservoirs DGA classes as generation or generation-and-irrigation, the bulk of the SEN's storable hydro energy. Only filled when all six have a value that day.</t>
+          <t>Total_Mm3 = Colbún + Rapel + Ralco + Pangue + Lago Laja (Laguna de La Laja) + Laguna del Maule - the six reservoirs DGA classes as generation or generation-and-irrigation, the bulk of the SEN's storable hydro energy. Days where a reservoir has no reading bridge gaps of up to 10 days by straight-line interpolation (for the total only; the reservoir columns stay blank); longer gaps leave the total blank. Laguna del Maule falls back to DGA's dam gauge (07300006-8) on days its main station (07300000-9) has no reading.</t>
         </is>
       </c>
     </row>
@@ -2046,6 +2047,44 @@
       <c r="A15" t="inlineStr">
         <is>
           <t>DGA Visualizador Hidrométrico Nacional - https://vipnet.mop.gob.cl (API https://vipnet.mop.gob.cl/v1/vipnet/estacion/valores, station codes in the script). DGA Boletín Hidrométrico (monthly) - https://dga.mop.gob.cl/servicios-de-informacion/boletines/ . DGA online data is provisional and can be revised. Updated daily by GitHub Actions (chile_hydro_reservoirs.yml).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>daily_method</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -4339,10 +4378,10 @@
         <v>57.39</v>
       </c>
       <c r="E116" t="n">
-        <v>50.01</v>
+        <v>50.03</v>
       </c>
       <c r="F116" t="n">
-        <v>45.49</v>
+        <v>45.57</v>
       </c>
     </row>
     <row r="117">
@@ -4361,10 +4400,10 @@
         <v>57.27</v>
       </c>
       <c r="E117" t="n">
-        <v>49.87</v>
+        <v>49.89</v>
       </c>
       <c r="F117" t="n">
-        <v>45.3</v>
+        <v>45.38</v>
       </c>
     </row>
     <row r="118">
@@ -4383,10 +4422,10 @@
         <v>57.14</v>
       </c>
       <c r="E118" t="n">
-        <v>49.73</v>
+        <v>49.76</v>
       </c>
       <c r="F118" t="n">
-        <v>45.11</v>
+        <v>45.22</v>
       </c>
     </row>
     <row r="119">
@@ -4405,10 +4444,10 @@
         <v>57</v>
       </c>
       <c r="E119" t="n">
-        <v>49.59</v>
+        <v>49.63</v>
       </c>
       <c r="F119" t="n">
-        <v>44.92</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="120">
@@ -4427,10 +4466,10 @@
         <v>56.89</v>
       </c>
       <c r="E120" t="n">
-        <v>49.44</v>
+        <v>49.47</v>
       </c>
       <c r="F120" t="n">
-        <v>44.73</v>
+        <v>44.84</v>
       </c>
     </row>
     <row r="121">
@@ -4449,10 +4488,10 @@
         <v>56.82</v>
       </c>
       <c r="E121" t="n">
-        <v>49.3</v>
+        <v>49.33</v>
       </c>
       <c r="F121" t="n">
-        <v>44.54</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="122">
@@ -4471,10 +4510,10 @@
         <v>56.75</v>
       </c>
       <c r="E122" t="n">
-        <v>49.16</v>
+        <v>49.18</v>
       </c>
       <c r="F122" t="n">
-        <v>44.35</v>
+        <v>44.43</v>
       </c>
     </row>
     <row r="123">
@@ -4518,7 +4557,7 @@
         <v>48.9</v>
       </c>
       <c r="F124" t="n">
-        <v>43.97</v>
+        <v>43.99</v>
       </c>
     </row>
     <row r="125">
@@ -5697,13 +5736,13 @@
         <v>31</v>
       </c>
       <c r="C178" t="n">
-        <v>16.16</v>
+        <v>16.14</v>
       </c>
       <c r="D178" t="n">
-        <v>47.16</v>
+        <v>47.14</v>
       </c>
       <c r="E178" t="n">
-        <v>40.87</v>
+        <v>40.86</v>
       </c>
       <c r="F178" t="n">
         <v>38.3</v>
@@ -6187,7 +6226,7 @@
         <v>43.96</v>
       </c>
       <c r="E200" t="n">
-        <v>37.12</v>
+        <v>38.8</v>
       </c>
       <c r="F200" t="n">
         <v>36.66</v>
@@ -6209,7 +6248,7 @@
         <v>43.84</v>
       </c>
       <c r="E201" t="n">
-        <v>37.06</v>
+        <v>38.74</v>
       </c>
       <c r="F201" t="n">
         <v>36.56</v>
@@ -6231,7 +6270,7 @@
         <v>43.73</v>
       </c>
       <c r="E202" t="n">
-        <v>36.98</v>
+        <v>38.65</v>
       </c>
       <c r="F202" t="n">
         <v>36.43</v>
@@ -6253,7 +6292,7 @@
         <v>43.61</v>
       </c>
       <c r="E203" t="n">
-        <v>36.94</v>
+        <v>38.57</v>
       </c>
       <c r="F203" t="n">
         <v>36.39</v>
@@ -6275,7 +6314,7 @@
         <v>43.5</v>
       </c>
       <c r="E204" t="n">
-        <v>36.88</v>
+        <v>38.47</v>
       </c>
       <c r="F204" t="n">
         <v>36.29</v>
@@ -6297,7 +6336,7 @@
         <v>43.38</v>
       </c>
       <c r="E205" t="n">
-        <v>36.81</v>
+        <v>38.4</v>
       </c>
       <c r="F205" t="n">
         <v>36.18</v>
@@ -6319,7 +6358,7 @@
         <v>43.27</v>
       </c>
       <c r="E206" t="n">
-        <v>36.76</v>
+        <v>38.37</v>
       </c>
       <c r="F206" t="n">
         <v>36.12</v>
@@ -6341,7 +6380,7 @@
         <v>43.15</v>
       </c>
       <c r="E207" t="n">
-        <v>36.65</v>
+        <v>38.28</v>
       </c>
       <c r="F207" t="n">
         <v>35.89</v>
@@ -6357,13 +6396,13 @@
         <v>30.94</v>
       </c>
       <c r="C208" t="n">
-        <v>12.1</v>
+        <v>12.14</v>
       </c>
       <c r="D208" t="n">
-        <v>43.03</v>
+        <v>43.08</v>
       </c>
       <c r="E208" t="n">
-        <v>36.59</v>
+        <v>38.21</v>
       </c>
       <c r="F208" t="n">
         <v>35.81</v>
@@ -6379,13 +6418,13 @@
         <v>30.96</v>
       </c>
       <c r="C209" t="n">
-        <v>11.96</v>
+        <v>11.99</v>
       </c>
       <c r="D209" t="n">
-        <v>42.92</v>
+        <v>42.95</v>
       </c>
       <c r="E209" t="n">
-        <v>36.54</v>
+        <v>38.14</v>
       </c>
       <c r="F209" t="n">
         <v>35.73</v>
@@ -8246,19 +8285,19 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>32.72</v>
+        <v>32.51</v>
       </c>
       <c r="C294" t="n">
-        <v>18.03</v>
+        <v>18.24</v>
       </c>
       <c r="D294" t="n">
         <v>50.75</v>
       </c>
       <c r="E294" t="n">
-        <v>39.16</v>
+        <v>39.09</v>
       </c>
       <c r="F294" t="n">
-        <v>32.72</v>
+        <v>32.51</v>
       </c>
     </row>
     <row r="295">
@@ -62265,6 +62304,12 @@
       <c r="I315" t="n">
         <v>146.18</v>
       </c>
+      <c r="J315" t="n">
+        <v>4919.6</v>
+      </c>
+      <c r="K315" t="n">
+        <v>47.14</v>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63136,6 +63181,12 @@
       <c r="I337" t="n">
         <v>124.15</v>
       </c>
+      <c r="J337" t="n">
+        <v>4576</v>
+      </c>
+      <c r="K337" t="n">
+        <v>43.84</v>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63167,6 +63218,12 @@
       <c r="I338" t="n">
         <v>123.25</v>
       </c>
+      <c r="J338" t="n">
+        <v>4570.3</v>
+      </c>
+      <c r="K338" t="n">
+        <v>43.79</v>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63198,6 +63255,12 @@
       <c r="I339" t="n">
         <v>122.27</v>
       </c>
+      <c r="J339" t="n">
+        <v>4556.3</v>
+      </c>
+      <c r="K339" t="n">
+        <v>43.66</v>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63229,6 +63292,12 @@
       <c r="I340" t="n">
         <v>120.93</v>
       </c>
+      <c r="J340" t="n">
+        <v>4536.1</v>
+      </c>
+      <c r="K340" t="n">
+        <v>43.46</v>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63260,6 +63329,12 @@
       <c r="I341" t="n">
         <v>119.52</v>
       </c>
+      <c r="J341" t="n">
+        <v>4515.6</v>
+      </c>
+      <c r="K341" t="n">
+        <v>43.27</v>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63291,6 +63366,12 @@
       <c r="I342" t="n">
         <v>118.26</v>
       </c>
+      <c r="J342" t="n">
+        <v>4508</v>
+      </c>
+      <c r="K342" t="n">
+        <v>43.19</v>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63319,6 +63400,12 @@
       <c r="I343" t="n">
         <v>116.99</v>
       </c>
+      <c r="J343" t="n">
+        <v>4510.5</v>
+      </c>
+      <c r="K343" t="n">
+        <v>43.22</v>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63350,6 +63437,12 @@
       <c r="I344" t="n">
         <v>115.77</v>
       </c>
+      <c r="J344" t="n">
+        <v>4503.8</v>
+      </c>
+      <c r="K344" t="n">
+        <v>43.15</v>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63381,6 +63474,12 @@
       <c r="I345" t="n">
         <v>115.12</v>
       </c>
+      <c r="J345" t="n">
+        <v>4496</v>
+      </c>
+      <c r="K345" t="n">
+        <v>43.08</v>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63412,6 +63511,12 @@
       <c r="I346" t="n">
         <v>113.84</v>
       </c>
+      <c r="J346" t="n">
+        <v>4482.4</v>
+      </c>
+      <c r="K346" t="n">
+        <v>42.95</v>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -71940,6 +72045,12 @@
       <c r="I618" t="n">
         <v>140.78</v>
       </c>
+      <c r="J618" t="n">
+        <v>4755.7</v>
+      </c>
+      <c r="K618" t="n">
+        <v>45.57</v>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -71971,6 +72082,12 @@
       <c r="I619" t="n">
         <v>140.47</v>
       </c>
+      <c r="J619" t="n">
+        <v>4735.8</v>
+      </c>
+      <c r="K619" t="n">
+        <v>45.38</v>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72002,6 +72119,12 @@
       <c r="I620" t="n">
         <v>140.44</v>
       </c>
+      <c r="J620" t="n">
+        <v>4719.2</v>
+      </c>
+      <c r="K620" t="n">
+        <v>45.22</v>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72033,6 +72156,12 @@
       <c r="I621" t="n">
         <v>140.16</v>
       </c>
+      <c r="J621" t="n">
+        <v>4703.3</v>
+      </c>
+      <c r="K621" t="n">
+        <v>45.06</v>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72064,6 +72193,12 @@
       <c r="I622" t="n">
         <v>139.47</v>
       </c>
+      <c r="J622" t="n">
+        <v>4680</v>
+      </c>
+      <c r="K622" t="n">
+        <v>44.84</v>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72095,6 +72230,12 @@
       <c r="I623" t="n">
         <v>139.26</v>
       </c>
+      <c r="J623" t="n">
+        <v>4661.3</v>
+      </c>
+      <c r="K623" t="n">
+        <v>44.66</v>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72126,6 +72267,12 @@
       <c r="I624" t="n">
         <v>139.26</v>
       </c>
+      <c r="J624" t="n">
+        <v>4637.3</v>
+      </c>
+      <c r="K624" t="n">
+        <v>44.43</v>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72157,6 +72304,12 @@
       <c r="I625" t="n">
         <v>138.79</v>
       </c>
+      <c r="J625" t="n">
+        <v>4609.5</v>
+      </c>
+      <c r="K625" t="n">
+        <v>44.16</v>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -72188,6 +72341,12 @@
       <c r="I626" t="n">
         <v>138.32</v>
       </c>
+      <c r="J626" t="n">
+        <v>4591.1</v>
+      </c>
+      <c r="K626" t="n">
+        <v>43.99</v>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -78942,6 +79101,12 @@
       </c>
       <c r="I796" t="n">
         <v>19.34</v>
+      </c>
+      <c r="J796" t="n">
+        <v>3392.7</v>
+      </c>
+      <c r="K796" t="n">
+        <v>32.51</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -2011,7 +2011,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Total_Mm3 = Colbún + Rapel + Ralco + Pangue + Lago Laja (Laguna de La Laja) + Laguna del Maule - the six reservoirs DGA classes as generation or generation-and-irrigation, the bulk of the SEN's storable hydro energy. Days where a reservoir has no reading bridge gaps of up to 10 days by straight-line interpolation (for the total only; the reservoir columns stay blank); longer gaps leave the total blank. Laguna del Maule falls back to DGA's dam gauge (07300006-8) on days its main station (07300000-9) has no reading.</t>
+          <t>Total_Mm3 = Colbún + Rapel + Ralco + Pangue + Lago Laja (Laguna de La Laja) + Laguna del Maule - the six reservoirs DGA classes as generation or generation-and-irrigation, the bulk of the SEN's storable hydro energy. Days where a reservoir has no reading bridge gaps of up to 10 days by straight-line interpolation (for the total only; the reservoir columns stay blank); longer gaps leave the total blank. Laguna del Maule had no online readings from mid-Apr-2025 to Jan-2026 (nor did its dam gauge 07300006-8, the fallback station): its Apr-Sep 2025 month-ends come from the Sep-2025 bulletin (Source column says so) and the total joins them up (gaps up to 35 days for this slow lake). Oct-2025 to early Jan-2026 stays blank in the total until DGA publishes its Sep-2026 bulletin, which the script looks for on every run.</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,10 @@
         <v>47.86</v>
       </c>
       <c r="E2" t="n">
-        <v>42.8</v>
+        <v>42.88</v>
+      </c>
+      <c r="F2" t="n">
+        <v>43.06</v>
       </c>
       <c r="G2" t="n">
         <v>52.76</v>
@@ -2186,7 +2189,10 @@
         <v>48.22</v>
       </c>
       <c r="E3" t="n">
-        <v>43.1</v>
+        <v>43.09</v>
+      </c>
+      <c r="F3" t="n">
+        <v>43.07</v>
       </c>
     </row>
     <row r="4">
@@ -2205,7 +2211,10 @@
         <v>48.51</v>
       </c>
       <c r="E4" t="n">
-        <v>43.37</v>
+        <v>43.27</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.06</v>
       </c>
     </row>
     <row r="5">
@@ -2224,7 +2233,10 @@
         <v>48.54</v>
       </c>
       <c r="E5" t="n">
-        <v>43.52</v>
+        <v>43.43</v>
+      </c>
+      <c r="F5" t="n">
+        <v>43.27</v>
       </c>
     </row>
     <row r="6">
@@ -2243,7 +2255,10 @@
         <v>48.75</v>
       </c>
       <c r="E6" t="n">
-        <v>43.75</v>
+        <v>43.68</v>
+      </c>
+      <c r="F6" t="n">
+        <v>43.55</v>
       </c>
     </row>
     <row r="7">
@@ -2262,7 +2277,10 @@
         <v>49.08</v>
       </c>
       <c r="E7" t="n">
-        <v>44.04</v>
+        <v>43.99</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.88</v>
       </c>
     </row>
     <row r="8">
@@ -2281,7 +2299,10 @@
         <v>49.36</v>
       </c>
       <c r="E8" t="n">
-        <v>44.3</v>
+        <v>44.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>43.98</v>
       </c>
     </row>
     <row r="9">
@@ -2300,7 +2321,10 @@
         <v>49.59</v>
       </c>
       <c r="E9" t="n">
-        <v>44.55</v>
+        <v>44.35</v>
+      </c>
+      <c r="F9" t="n">
+        <v>43.97</v>
       </c>
     </row>
     <row r="10">
@@ -2319,7 +2343,10 @@
         <v>50.04</v>
       </c>
       <c r="E10" t="n">
-        <v>44.9</v>
+        <v>44.58</v>
+      </c>
+      <c r="F10" t="n">
+        <v>43.95</v>
       </c>
     </row>
     <row r="11">
@@ -2338,7 +2365,10 @@
         <v>50.56</v>
       </c>
       <c r="E11" t="n">
-        <v>45.28</v>
+        <v>44.84</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.94</v>
       </c>
     </row>
     <row r="12">
@@ -2357,7 +2387,10 @@
         <v>51.19</v>
       </c>
       <c r="E12" t="n">
-        <v>45.72</v>
+        <v>45.17</v>
+      </c>
+      <c r="F12" t="n">
+        <v>44.05</v>
       </c>
     </row>
     <row r="13">
@@ -2376,7 +2409,10 @@
         <v>51.82</v>
       </c>
       <c r="E13" t="n">
-        <v>46.17</v>
+        <v>45.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>44.16</v>
       </c>
     </row>
     <row r="14">
@@ -2395,7 +2431,10 @@
         <v>52.26</v>
       </c>
       <c r="E14" t="n">
-        <v>46.51</v>
+        <v>45.75</v>
+      </c>
+      <c r="F14" t="n">
+        <v>44.24</v>
       </c>
     </row>
     <row r="15">
@@ -2414,7 +2453,10 @@
         <v>52.64</v>
       </c>
       <c r="E15" t="n">
-        <v>46.83</v>
+        <v>46.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>44.37</v>
       </c>
     </row>
     <row r="16">
@@ -2433,7 +2475,10 @@
         <v>52.95</v>
       </c>
       <c r="E16" t="n">
-        <v>47.11</v>
+        <v>46.21</v>
+      </c>
+      <c r="F16" t="n">
+        <v>44.41</v>
       </c>
     </row>
     <row r="17">
@@ -2452,7 +2497,10 @@
         <v>53.19</v>
       </c>
       <c r="E17" t="n">
-        <v>47.36</v>
+        <v>46.42</v>
+      </c>
+      <c r="F17" t="n">
+        <v>44.55</v>
       </c>
     </row>
     <row r="18">
@@ -2471,7 +2519,10 @@
         <v>53.56</v>
       </c>
       <c r="E18" t="n">
-        <v>47.67</v>
+        <v>46.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>44.76</v>
       </c>
     </row>
     <row r="19">
@@ -2490,7 +2541,10 @@
         <v>53.97</v>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>46.97</v>
+      </c>
+      <c r="F19" t="n">
+        <v>44.92</v>
       </c>
     </row>
     <row r="20">
@@ -2509,7 +2563,10 @@
         <v>54.37</v>
       </c>
       <c r="E20" t="n">
-        <v>48.32</v>
+        <v>47.22</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45.01</v>
       </c>
     </row>
     <row r="21">
@@ -2528,7 +2585,10 @@
         <v>54.87</v>
       </c>
       <c r="E21" t="n">
-        <v>48.7</v>
+        <v>47.49</v>
+      </c>
+      <c r="F21" t="n">
+        <v>45.07</v>
       </c>
     </row>
     <row r="22">
@@ -2547,7 +2607,10 @@
         <v>55.33</v>
       </c>
       <c r="E22" t="n">
-        <v>49.06</v>
+        <v>47.75</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45.14</v>
       </c>
     </row>
     <row r="23">
@@ -2566,7 +2629,10 @@
         <v>55.77</v>
       </c>
       <c r="E23" t="n">
-        <v>49.4</v>
+        <v>48</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45.2</v>
       </c>
     </row>
     <row r="24">
@@ -2585,7 +2651,10 @@
         <v>56.26</v>
       </c>
       <c r="E24" t="n">
-        <v>49.77</v>
+        <v>48.29</v>
+      </c>
+      <c r="F24" t="n">
+        <v>45.31</v>
       </c>
     </row>
     <row r="25">
@@ -2604,7 +2673,10 @@
         <v>56.68</v>
       </c>
       <c r="E25" t="n">
-        <v>50.11</v>
+        <v>48.5</v>
+      </c>
+      <c r="F25" t="n">
+        <v>45.27</v>
       </c>
     </row>
     <row r="26">
@@ -2623,7 +2695,10 @@
         <v>56.96</v>
       </c>
       <c r="E26" t="n">
-        <v>50.38</v>
+        <v>48.71</v>
+      </c>
+      <c r="F26" t="n">
+        <v>45.38</v>
       </c>
     </row>
     <row r="27">
@@ -2642,7 +2717,10 @@
         <v>57.16</v>
       </c>
       <c r="E27" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
+      </c>
+      <c r="F27" t="n">
+        <v>45.5</v>
       </c>
     </row>
     <row r="28">
@@ -2661,7 +2739,10 @@
         <v>57.41</v>
       </c>
       <c r="E28" t="n">
-        <v>50.85</v>
+        <v>49.11</v>
+      </c>
+      <c r="F28" t="n">
+        <v>45.61</v>
       </c>
     </row>
     <row r="29">
@@ -2680,7 +2761,10 @@
         <v>57.69</v>
       </c>
       <c r="E29" t="n">
-        <v>51.12</v>
+        <v>49.28</v>
+      </c>
+      <c r="F29" t="n">
+        <v>45.61</v>
       </c>
     </row>
     <row r="30">
@@ -2699,7 +2783,10 @@
         <v>57.98</v>
       </c>
       <c r="E30" t="n">
-        <v>51.39</v>
+        <v>49.49</v>
+      </c>
+      <c r="F30" t="n">
+        <v>45.69</v>
       </c>
     </row>
     <row r="31">
@@ -2718,7 +2805,10 @@
         <v>58.38</v>
       </c>
       <c r="E31" t="n">
-        <v>51.72</v>
+        <v>49.76</v>
+      </c>
+      <c r="F31" t="n">
+        <v>45.84</v>
       </c>
     </row>
     <row r="32">
@@ -2737,7 +2827,10 @@
         <v>58.8</v>
       </c>
       <c r="E32" t="n">
-        <v>53.1</v>
+        <v>51.32</v>
+      </c>
+      <c r="F32" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="33">
@@ -2756,7 +2849,10 @@
         <v>59.15</v>
       </c>
       <c r="E33" t="n">
-        <v>53.26</v>
+        <v>51.49</v>
+      </c>
+      <c r="F33" t="n">
+        <v>46.17</v>
       </c>
     </row>
     <row r="34">
@@ -2775,7 +2871,10 @@
         <v>59.46</v>
       </c>
       <c r="E34" t="n">
-        <v>53.42</v>
+        <v>51.65</v>
+      </c>
+      <c r="F34" t="n">
+        <v>46.33</v>
       </c>
     </row>
     <row r="35">
@@ -2794,7 +2893,10 @@
         <v>59.64</v>
       </c>
       <c r="E35" t="n">
-        <v>53.53</v>
+        <v>51.77</v>
+      </c>
+      <c r="F35" t="n">
+        <v>46.5</v>
       </c>
     </row>
     <row r="36">
@@ -2813,7 +2915,10 @@
         <v>59.74</v>
       </c>
       <c r="E36" t="n">
-        <v>53.61</v>
+        <v>51.87</v>
+      </c>
+      <c r="F36" t="n">
+        <v>46.65</v>
       </c>
     </row>
     <row r="37">
@@ -6292,7 +6397,7 @@
         <v>43.61</v>
       </c>
       <c r="E203" t="n">
-        <v>38.57</v>
+        <v>38.56</v>
       </c>
       <c r="F203" t="n">
         <v>36.39</v>
@@ -6314,7 +6419,7 @@
         <v>43.5</v>
       </c>
       <c r="E204" t="n">
-        <v>38.47</v>
+        <v>38.46</v>
       </c>
       <c r="F204" t="n">
         <v>36.29</v>
@@ -6336,7 +6441,7 @@
         <v>43.38</v>
       </c>
       <c r="E205" t="n">
-        <v>38.4</v>
+        <v>38.39</v>
       </c>
       <c r="F205" t="n">
         <v>36.18</v>
@@ -6358,7 +6463,7 @@
         <v>43.27</v>
       </c>
       <c r="E206" t="n">
-        <v>38.37</v>
+        <v>38.36</v>
       </c>
       <c r="F206" t="n">
         <v>36.12</v>
@@ -6380,7 +6485,7 @@
         <v>43.15</v>
       </c>
       <c r="E207" t="n">
-        <v>38.28</v>
+        <v>38.26</v>
       </c>
       <c r="F207" t="n">
         <v>35.89</v>
@@ -6396,13 +6501,13 @@
         <v>30.94</v>
       </c>
       <c r="C208" t="n">
-        <v>12.14</v>
+        <v>12.1</v>
       </c>
       <c r="D208" t="n">
-        <v>43.08</v>
+        <v>43.03</v>
       </c>
       <c r="E208" t="n">
-        <v>38.21</v>
+        <v>38.2</v>
       </c>
       <c r="F208" t="n">
         <v>35.81</v>
@@ -6418,13 +6523,13 @@
         <v>30.96</v>
       </c>
       <c r="C209" t="n">
-        <v>11.99</v>
+        <v>11.96</v>
       </c>
       <c r="D209" t="n">
-        <v>42.95</v>
+        <v>42.92</v>
       </c>
       <c r="E209" t="n">
-        <v>38.14</v>
+        <v>38.12</v>
       </c>
       <c r="F209" t="n">
         <v>35.73</v>
@@ -6446,7 +6551,7 @@
         <v>42.8</v>
       </c>
       <c r="E210" t="n">
-        <v>36.47</v>
+        <v>38.04</v>
       </c>
       <c r="F210" t="n">
         <v>35.62</v>
@@ -6468,7 +6573,7 @@
         <v>42.69</v>
       </c>
       <c r="E211" t="n">
-        <v>36.33</v>
+        <v>37.91</v>
       </c>
       <c r="F211" t="n">
         <v>35.29</v>
@@ -6490,7 +6595,7 @@
         <v>42.57</v>
       </c>
       <c r="E212" t="n">
-        <v>36.3</v>
+        <v>37.84</v>
       </c>
       <c r="F212" t="n">
         <v>35.29</v>
@@ -6512,7 +6617,7 @@
         <v>42.46</v>
       </c>
       <c r="E213" t="n">
-        <v>36.25</v>
+        <v>37.73</v>
       </c>
       <c r="F213" t="n">
         <v>35.23</v>
@@ -6534,7 +6639,7 @@
         <v>42.34</v>
       </c>
       <c r="E214" t="n">
-        <v>36.21</v>
+        <v>37.68</v>
       </c>
       <c r="F214" t="n">
         <v>35.18</v>
@@ -6556,7 +6661,7 @@
         <v>42.23</v>
       </c>
       <c r="E215" t="n">
-        <v>36.16</v>
+        <v>37.6</v>
       </c>
       <c r="F215" t="n">
         <v>35.1</v>
@@ -6578,7 +6683,7 @@
         <v>42.13</v>
       </c>
       <c r="E216" t="n">
-        <v>36.1</v>
+        <v>37.49</v>
       </c>
       <c r="F216" t="n">
         <v>34.95</v>
@@ -6600,7 +6705,7 @@
         <v>42.02</v>
       </c>
       <c r="E217" t="n">
-        <v>36.03</v>
+        <v>37.39</v>
       </c>
       <c r="F217" t="n">
         <v>34.79</v>
@@ -6622,7 +6727,7 @@
         <v>41.91</v>
       </c>
       <c r="E218" t="n">
-        <v>35.97</v>
+        <v>37.29</v>
       </c>
       <c r="F218" t="n">
         <v>34.68</v>
@@ -6644,7 +6749,7 @@
         <v>41.8</v>
       </c>
       <c r="E219" t="n">
-        <v>35.93</v>
+        <v>37.22</v>
       </c>
       <c r="F219" t="n">
         <v>34.6</v>
@@ -6666,7 +6771,7 @@
         <v>41.7</v>
       </c>
       <c r="E220" t="n">
-        <v>35.99</v>
+        <v>37.22</v>
       </c>
       <c r="F220" t="n">
         <v>34.84</v>
@@ -6688,7 +6793,7 @@
         <v>41.59</v>
       </c>
       <c r="E221" t="n">
-        <v>36.03</v>
+        <v>37.22</v>
       </c>
       <c r="F221" t="n">
         <v>35</v>
@@ -6710,7 +6815,7 @@
         <v>41.48</v>
       </c>
       <c r="E222" t="n">
-        <v>36.01</v>
+        <v>37.18</v>
       </c>
       <c r="F222" t="n">
         <v>35</v>
@@ -6732,7 +6837,7 @@
         <v>41.37</v>
       </c>
       <c r="E223" t="n">
-        <v>35.92</v>
+        <v>37.1</v>
       </c>
       <c r="F223" t="n">
         <v>34.78</v>
@@ -6754,7 +6859,7 @@
         <v>41.27</v>
       </c>
       <c r="E224" t="n">
-        <v>35.87</v>
+        <v>37.04</v>
       </c>
       <c r="F224" t="n">
         <v>34.67</v>
@@ -6776,7 +6881,7 @@
         <v>41.16</v>
       </c>
       <c r="E225" t="n">
-        <v>35.83</v>
+        <v>36.97</v>
       </c>
       <c r="F225" t="n">
         <v>34.61</v>
@@ -6798,7 +6903,7 @@
         <v>41.05</v>
       </c>
       <c r="E226" t="n">
-        <v>35.8</v>
+        <v>36.92</v>
       </c>
       <c r="F226" t="n">
         <v>34.58</v>
@@ -6820,7 +6925,7 @@
         <v>40.94</v>
       </c>
       <c r="E227" t="n">
-        <v>35.79</v>
+        <v>36.88</v>
       </c>
       <c r="F227" t="n">
         <v>34.6</v>
@@ -6842,7 +6947,7 @@
         <v>40.84</v>
       </c>
       <c r="E228" t="n">
-        <v>35.75</v>
+        <v>36.81</v>
       </c>
       <c r="F228" t="n">
         <v>34.53</v>
@@ -6864,7 +6969,7 @@
         <v>40.73</v>
       </c>
       <c r="E229" t="n">
-        <v>35.74</v>
+        <v>36.75</v>
       </c>
       <c r="F229" t="n">
         <v>34.55</v>
@@ -6886,7 +6991,7 @@
         <v>40.62</v>
       </c>
       <c r="E230" t="n">
-        <v>35.73</v>
+        <v>36.74</v>
       </c>
       <c r="F230" t="n">
         <v>34.58</v>
@@ -6908,7 +7013,7 @@
         <v>40.51</v>
       </c>
       <c r="E231" t="n">
-        <v>35.71</v>
+        <v>36.69</v>
       </c>
       <c r="F231" t="n">
         <v>34.55</v>
@@ -6930,7 +7035,7 @@
         <v>40.41</v>
       </c>
       <c r="E232" t="n">
-        <v>35.63</v>
+        <v>36.6</v>
       </c>
       <c r="F232" t="n">
         <v>34.36</v>
@@ -6952,7 +7057,7 @@
         <v>40.3</v>
       </c>
       <c r="E233" t="n">
-        <v>35.58</v>
+        <v>36.56</v>
       </c>
       <c r="F233" t="n">
         <v>34.26</v>
@@ -6974,7 +7079,7 @@
         <v>40.19</v>
       </c>
       <c r="E234" t="n">
-        <v>35.52</v>
+        <v>36.5</v>
       </c>
       <c r="F234" t="n">
         <v>34.16</v>
@@ -6996,7 +7101,7 @@
         <v>40.08</v>
       </c>
       <c r="E235" t="n">
-        <v>35.45</v>
+        <v>36.43</v>
       </c>
       <c r="F235" t="n">
         <v>33.98</v>
@@ -7018,7 +7123,7 @@
         <v>39.98</v>
       </c>
       <c r="E236" t="n">
-        <v>35.38</v>
+        <v>36.33</v>
       </c>
       <c r="F236" t="n">
         <v>33.84</v>
@@ -7040,7 +7145,7 @@
         <v>39.87</v>
       </c>
       <c r="E237" t="n">
-        <v>35.33</v>
+        <v>36.25</v>
       </c>
       <c r="F237" t="n">
         <v>33.72</v>
@@ -7062,7 +7167,7 @@
         <v>39.76</v>
       </c>
       <c r="E238" t="n">
-        <v>35.26</v>
+        <v>36.17</v>
       </c>
       <c r="F238" t="n">
         <v>33.57</v>
@@ -7084,7 +7189,7 @@
         <v>39.65</v>
       </c>
       <c r="E239" t="n">
-        <v>35.19</v>
+        <v>36.14</v>
       </c>
       <c r="F239" t="n">
         <v>33.41</v>
@@ -7106,7 +7211,7 @@
         <v>39.55</v>
       </c>
       <c r="E240" t="n">
-        <v>35.08</v>
+        <v>36.07</v>
       </c>
       <c r="F240" t="n">
         <v>33.13</v>
@@ -7128,7 +7233,7 @@
         <v>39.44</v>
       </c>
       <c r="E241" t="n">
-        <v>35.01</v>
+        <v>36.01</v>
       </c>
       <c r="F241" t="n">
         <v>32.97</v>
@@ -7150,7 +7255,7 @@
         <v>39.33</v>
       </c>
       <c r="E242" t="n">
-        <v>34.93</v>
+        <v>35.94</v>
       </c>
       <c r="F242" t="n">
         <v>32.8</v>
@@ -7172,7 +7277,7 @@
         <v>39.22</v>
       </c>
       <c r="E243" t="n">
-        <v>34.87</v>
+        <v>35.85</v>
       </c>
       <c r="F243" t="n">
         <v>32.66</v>
@@ -7194,7 +7299,7 @@
         <v>39.12</v>
       </c>
       <c r="E244" t="n">
-        <v>34.82</v>
+        <v>35.81</v>
       </c>
       <c r="F244" t="n">
         <v>32.56</v>
@@ -7216,7 +7321,7 @@
         <v>39.01</v>
       </c>
       <c r="E245" t="n">
-        <v>34.71</v>
+        <v>35.72</v>
       </c>
       <c r="F245" t="n">
         <v>32.37</v>
@@ -7238,7 +7343,7 @@
         <v>39.47</v>
       </c>
       <c r="E246" t="n">
-        <v>34.81</v>
+        <v>35.73</v>
       </c>
       <c r="F246" t="n">
         <v>32.24</v>
@@ -7260,7 +7365,7 @@
         <v>39.94</v>
       </c>
       <c r="E247" t="n">
-        <v>34.91</v>
+        <v>35.77</v>
       </c>
       <c r="F247" t="n">
         <v>32.11</v>
@@ -7282,7 +7387,7 @@
         <v>40.4</v>
       </c>
       <c r="E248" t="n">
-        <v>35.03</v>
+        <v>35.8</v>
       </c>
       <c r="F248" t="n">
         <v>32.03</v>
@@ -7304,7 +7409,7 @@
         <v>40.86</v>
       </c>
       <c r="E249" t="n">
-        <v>35.11</v>
+        <v>35.85</v>
       </c>
       <c r="F249" t="n">
         <v>31.85</v>
@@ -7326,7 +7431,7 @@
         <v>41.32</v>
       </c>
       <c r="E250" t="n">
-        <v>35.2</v>
+        <v>35.86</v>
       </c>
       <c r="F250" t="n">
         <v>31.67</v>
@@ -7348,7 +7453,7 @@
         <v>41.79</v>
       </c>
       <c r="E251" t="n">
-        <v>35.32</v>
+        <v>35.89</v>
       </c>
       <c r="F251" t="n">
         <v>31.59</v>
@@ -7370,7 +7475,7 @@
         <v>42.25</v>
       </c>
       <c r="E252" t="n">
-        <v>35.41</v>
+        <v>35.94</v>
       </c>
       <c r="F252" t="n">
         <v>31.45</v>
@@ -7392,7 +7497,7 @@
         <v>42.71</v>
       </c>
       <c r="E253" t="n">
-        <v>35.51</v>
+        <v>35.95</v>
       </c>
       <c r="F253" t="n">
         <v>31.3</v>
@@ -7414,7 +7519,7 @@
         <v>43.18</v>
       </c>
       <c r="E254" t="n">
-        <v>35.61</v>
+        <v>35.97</v>
       </c>
       <c r="F254" t="n">
         <v>31.18</v>
@@ -7436,7 +7541,7 @@
         <v>43.64</v>
       </c>
       <c r="E255" t="n">
-        <v>35.72</v>
+        <v>36.02</v>
       </c>
       <c r="F255" t="n">
         <v>31.07</v>
@@ -7458,7 +7563,7 @@
         <v>44.1</v>
       </c>
       <c r="E256" t="n">
-        <v>35.84</v>
+        <v>36.09</v>
       </c>
       <c r="F256" t="n">
         <v>30.98</v>
@@ -7480,7 +7585,7 @@
         <v>44.57</v>
       </c>
       <c r="E257" t="n">
-        <v>35.96</v>
+        <v>36.13</v>
       </c>
       <c r="F257" t="n">
         <v>30.92</v>
@@ -7502,7 +7607,7 @@
         <v>45.03</v>
       </c>
       <c r="E258" t="n">
-        <v>36.08</v>
+        <v>36.18</v>
       </c>
       <c r="F258" t="n">
         <v>30.86</v>
@@ -7524,7 +7629,7 @@
         <v>45.49</v>
       </c>
       <c r="E259" t="n">
-        <v>36.22</v>
+        <v>36.29</v>
       </c>
       <c r="F259" t="n">
         <v>30.82</v>
@@ -7546,7 +7651,7 @@
         <v>45.96</v>
       </c>
       <c r="E260" t="n">
-        <v>36.32</v>
+        <v>36.36</v>
       </c>
       <c r="F260" t="n">
         <v>30.7</v>
@@ -7568,7 +7673,7 @@
         <v>46.42</v>
       </c>
       <c r="E261" t="n">
-        <v>36.4</v>
+        <v>36.39</v>
       </c>
       <c r="F261" t="n">
         <v>30.52</v>
@@ -7590,7 +7695,7 @@
         <v>46.88</v>
       </c>
       <c r="E262" t="n">
-        <v>36.5</v>
+        <v>36.45</v>
       </c>
       <c r="F262" t="n">
         <v>30.37</v>
@@ -7612,7 +7717,7 @@
         <v>47.34</v>
       </c>
       <c r="E263" t="n">
-        <v>36.61</v>
+        <v>36.53</v>
       </c>
       <c r="F263" t="n">
         <v>30.26</v>
@@ -7634,7 +7739,7 @@
         <v>47.81</v>
       </c>
       <c r="E264" t="n">
-        <v>36.73</v>
+        <v>36.58</v>
       </c>
       <c r="F264" t="n">
         <v>30.19</v>
@@ -7656,7 +7761,7 @@
         <v>48.27</v>
       </c>
       <c r="E265" t="n">
-        <v>36.87</v>
+        <v>36.64</v>
       </c>
       <c r="F265" t="n">
         <v>30.18</v>
@@ -7678,7 +7783,7 @@
         <v>48.73</v>
       </c>
       <c r="E266" t="n">
-        <v>36.98</v>
+        <v>36.75</v>
       </c>
       <c r="F266" t="n">
         <v>30.08</v>
@@ -7700,7 +7805,7 @@
         <v>49.2</v>
       </c>
       <c r="E267" t="n">
-        <v>37.07</v>
+        <v>36.82</v>
       </c>
       <c r="F267" t="n">
         <v>29.93</v>
@@ -7722,7 +7827,7 @@
         <v>49.66</v>
       </c>
       <c r="E268" t="n">
-        <v>37.15</v>
+        <v>36.84</v>
       </c>
       <c r="F268" t="n">
         <v>29.72</v>
@@ -7744,7 +7849,7 @@
         <v>50.12</v>
       </c>
       <c r="E269" t="n">
-        <v>37.28</v>
+        <v>36.87</v>
       </c>
       <c r="F269" t="n">
         <v>29.67</v>
@@ -7766,7 +7871,7 @@
         <v>50.58</v>
       </c>
       <c r="E270" t="n">
-        <v>37.32</v>
+        <v>36.87</v>
       </c>
       <c r="F270" t="n">
         <v>29.37</v>
@@ -7788,7 +7893,7 @@
         <v>51.05</v>
       </c>
       <c r="E271" t="n">
-        <v>37.44</v>
+        <v>36.94</v>
       </c>
       <c r="F271" t="n">
         <v>29.3</v>
@@ -7810,7 +7915,7 @@
         <v>51.51</v>
       </c>
       <c r="E272" t="n">
-        <v>37.55</v>
+        <v>36.99</v>
       </c>
       <c r="F272" t="n">
         <v>29.2</v>
@@ -7832,7 +7937,7 @@
         <v>51.97</v>
       </c>
       <c r="E273" t="n">
-        <v>37.69</v>
+        <v>37.09</v>
       </c>
       <c r="F273" t="n">
         <v>29.18</v>
@@ -7854,7 +7959,7 @@
         <v>52.44</v>
       </c>
       <c r="E274" t="n">
-        <v>37.81</v>
+        <v>37.19</v>
       </c>
       <c r="F274" t="n">
         <v>29.09</v>
@@ -7876,7 +7981,7 @@
         <v>52.9</v>
       </c>
       <c r="E275" t="n">
-        <v>37.91</v>
+        <v>37.17</v>
       </c>
       <c r="F275" t="n">
         <v>28.82</v>
@@ -7898,7 +8003,7 @@
         <v>52.99</v>
       </c>
       <c r="E276" t="n">
-        <v>37.95</v>
+        <v>37.19</v>
       </c>
       <c r="F276" t="n">
         <v>28.76</v>
@@ -7920,7 +8025,7 @@
         <v>53.17</v>
       </c>
       <c r="E277" t="n">
-        <v>37.99</v>
+        <v>37.19</v>
       </c>
       <c r="F277" t="n">
         <v>28.58</v>
@@ -7942,7 +8047,7 @@
         <v>53.39</v>
       </c>
       <c r="E278" t="n">
-        <v>38.03</v>
+        <v>37.21</v>
       </c>
       <c r="F278" t="n">
         <v>28.37</v>
@@ -7964,7 +8069,7 @@
         <v>53.5</v>
       </c>
       <c r="E279" t="n">
-        <v>38.05</v>
+        <v>37.24</v>
       </c>
       <c r="F279" t="n">
         <v>28.23</v>
@@ -7986,7 +8091,7 @@
         <v>53.52</v>
       </c>
       <c r="E280" t="n">
-        <v>38.03</v>
+        <v>37.26</v>
       </c>
       <c r="F280" t="n">
         <v>28.04</v>
@@ -8008,7 +8113,7 @@
         <v>53.52</v>
       </c>
       <c r="E281" t="n">
-        <v>38.01</v>
+        <v>37.28</v>
       </c>
       <c r="F281" t="n">
         <v>27.86</v>
@@ -8030,7 +8135,7 @@
         <v>53.51</v>
       </c>
       <c r="E282" t="n">
-        <v>38.06</v>
+        <v>37.34</v>
       </c>
       <c r="F282" t="n">
         <v>27.92</v>
@@ -8052,7 +8157,7 @@
         <v>53.44</v>
       </c>
       <c r="E283" t="n">
-        <v>38.09</v>
+        <v>37.37</v>
       </c>
       <c r="F283" t="n">
         <v>27.99</v>
@@ -8074,7 +8179,7 @@
         <v>53.35</v>
       </c>
       <c r="E284" t="n">
-        <v>38.18</v>
+        <v>37.45</v>
       </c>
       <c r="F284" t="n">
         <v>28.23</v>
@@ -8096,7 +8201,7 @@
         <v>53.17</v>
       </c>
       <c r="E285" t="n">
-        <v>38.38</v>
+        <v>37.62</v>
       </c>
       <c r="F285" t="n">
         <v>28.92</v>
@@ -8118,7 +8223,7 @@
         <v>53.01</v>
       </c>
       <c r="E286" t="n">
-        <v>38.44</v>
+        <v>37.69</v>
       </c>
       <c r="F286" t="n">
         <v>29.13</v>
@@ -8140,7 +8245,7 @@
         <v>52.79</v>
       </c>
       <c r="E287" t="n">
-        <v>38.43</v>
+        <v>37.66</v>
       </c>
       <c r="F287" t="n">
         <v>29.22</v>
@@ -8162,7 +8267,7 @@
         <v>52.58</v>
       </c>
       <c r="E288" t="n">
-        <v>38.36</v>
+        <v>37.57</v>
       </c>
       <c r="F288" t="n">
         <v>29.13</v>
@@ -8184,7 +8289,7 @@
         <v>52.34</v>
       </c>
       <c r="E289" t="n">
-        <v>38.41</v>
+        <v>37.45</v>
       </c>
       <c r="F289" t="n">
         <v>29.41</v>
@@ -8206,7 +8311,7 @@
         <v>52.08</v>
       </c>
       <c r="E290" t="n">
-        <v>38.63</v>
+        <v>37.61</v>
       </c>
       <c r="F290" t="n">
         <v>30.23</v>
@@ -8228,7 +8333,7 @@
         <v>51.71</v>
       </c>
       <c r="E291" t="n">
-        <v>38.84</v>
+        <v>37.78</v>
       </c>
       <c r="F291" t="n">
         <v>31.12</v>
@@ -8250,7 +8355,7 @@
         <v>51.34</v>
       </c>
       <c r="E292" t="n">
-        <v>38.95</v>
+        <v>37.86</v>
       </c>
       <c r="F292" t="n">
         <v>31.7</v>
@@ -8272,7 +8377,7 @@
         <v>50.95</v>
       </c>
       <c r="E293" t="n">
-        <v>38.99</v>
+        <v>37.87</v>
       </c>
       <c r="F293" t="n">
         <v>32.1</v>
@@ -8294,7 +8399,7 @@
         <v>50.75</v>
       </c>
       <c r="E294" t="n">
-        <v>39.09</v>
+        <v>37.95</v>
       </c>
       <c r="F294" t="n">
         <v>32.51</v>
@@ -8316,7 +8421,7 @@
         <v>50.49</v>
       </c>
       <c r="E295" t="n">
-        <v>39.32</v>
+        <v>38.1</v>
       </c>
       <c r="F295" t="n">
         <v>33.34</v>
@@ -8338,7 +8443,7 @@
         <v>50.26</v>
       </c>
       <c r="E296" t="n">
-        <v>39.51</v>
+        <v>38.25</v>
       </c>
       <c r="F296" t="n">
         <v>34.04</v>
@@ -8360,7 +8465,7 @@
         <v>50.01</v>
       </c>
       <c r="E297" t="n">
-        <v>39.58</v>
+        <v>38.29</v>
       </c>
       <c r="F297" t="n">
         <v>34.39</v>
@@ -8373,16 +8478,16 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>34.44</v>
+        <v>34.4</v>
       </c>
       <c r="C298" t="n">
-        <v>15.32</v>
+        <v>15.36</v>
       </c>
       <c r="D298" t="n">
         <v>49.76</v>
       </c>
       <c r="E298" t="n">
-        <v>39.66</v>
+        <v>38.34</v>
       </c>
       <c r="F298" t="n">
         <v>34.77</v>
@@ -8395,16 +8500,16 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>34.55</v>
+        <v>34.5</v>
       </c>
       <c r="C299" t="n">
-        <v>14.99</v>
+        <v>15.04</v>
       </c>
       <c r="D299" t="n">
         <v>49.54</v>
       </c>
       <c r="E299" t="n">
-        <v>39.75</v>
+        <v>38.44</v>
       </c>
       <c r="F299" t="n">
         <v>35.15</v>
@@ -8417,16 +8522,16 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>34.66</v>
+        <v>34.45</v>
       </c>
       <c r="C300" t="n">
-        <v>14.71</v>
+        <v>14.92</v>
       </c>
       <c r="D300" t="n">
         <v>49.37</v>
       </c>
       <c r="E300" t="n">
-        <v>40.08</v>
+        <v>38.67</v>
       </c>
       <c r="F300" t="n">
         <v>36.2</v>
@@ -8439,16 +8544,16 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>34.76</v>
+        <v>34.44</v>
       </c>
       <c r="C301" t="n">
-        <v>14.42</v>
+        <v>14.74</v>
       </c>
       <c r="D301" t="n">
         <v>49.18</v>
       </c>
       <c r="E301" t="n">
-        <v>40.87</v>
+        <v>39.26</v>
       </c>
       <c r="F301" t="n">
         <v>38.67</v>
@@ -8461,16 +8566,16 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>34.87</v>
+        <v>34.46</v>
       </c>
       <c r="C302" t="n">
-        <v>14.14</v>
+        <v>14.55</v>
       </c>
       <c r="D302" t="n">
         <v>49.01</v>
       </c>
       <c r="E302" t="n">
-        <v>41.45</v>
+        <v>39.7</v>
       </c>
       <c r="F302" t="n">
         <v>40.47</v>
@@ -8483,16 +8588,16 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>34.98</v>
+        <v>34.48</v>
       </c>
       <c r="C303" t="n">
-        <v>13.87</v>
+        <v>14.37</v>
       </c>
       <c r="D303" t="n">
         <v>48.85</v>
       </c>
       <c r="E303" t="n">
-        <v>41.8</v>
+        <v>39.97</v>
       </c>
       <c r="F303" t="n">
         <v>41.56</v>
@@ -8505,16 +8610,16 @@
         </is>
       </c>
       <c r="B304" t="n">
-        <v>35.08</v>
+        <v>34.56</v>
       </c>
       <c r="C304" t="n">
-        <v>13.49</v>
+        <v>14.01</v>
       </c>
       <c r="D304" t="n">
         <v>48.57</v>
       </c>
       <c r="E304" t="n">
-        <v>41.98</v>
+        <v>40.13</v>
       </c>
       <c r="F304" t="n">
         <v>42.3</v>
@@ -8527,16 +8632,16 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>35.19</v>
+        <v>35.11</v>
       </c>
       <c r="C305" t="n">
-        <v>13.03</v>
+        <v>13.11</v>
       </c>
       <c r="D305" t="n">
         <v>48.22</v>
       </c>
       <c r="E305" t="n">
-        <v>42.16</v>
+        <v>40.4</v>
       </c>
       <c r="F305" t="n">
         <v>43.07</v>
@@ -8558,7 +8663,7 @@
         <v>47.92</v>
       </c>
       <c r="E306" t="n">
-        <v>42.39</v>
+        <v>40.74</v>
       </c>
       <c r="F306" t="n">
         <v>44.03</v>
@@ -8580,7 +8685,7 @@
         <v>47.72</v>
       </c>
       <c r="E307" t="n">
-        <v>42.67</v>
+        <v>41.16</v>
       </c>
       <c r="F307" t="n">
         <v>45.03</v>
@@ -8602,7 +8707,7 @@
         <v>48.05</v>
       </c>
       <c r="E308" t="n">
-        <v>43.2</v>
+        <v>41.72</v>
       </c>
       <c r="F308" t="n">
         <v>46.24</v>
@@ -8624,7 +8729,7 @@
         <v>49.03</v>
       </c>
       <c r="E309" t="n">
-        <v>43.76</v>
+        <v>42.14</v>
       </c>
       <c r="F309" t="n">
         <v>46.93</v>
@@ -8646,7 +8751,7 @@
         <v>49.61</v>
       </c>
       <c r="E310" t="n">
-        <v>44.11</v>
+        <v>42.37</v>
       </c>
       <c r="F310" t="n">
         <v>47.35</v>
@@ -8668,7 +8773,7 @@
         <v>49.93</v>
       </c>
       <c r="E311" t="n">
-        <v>44.31</v>
+        <v>42.54</v>
       </c>
       <c r="F311" t="n">
         <v>47.59</v>
@@ -8690,7 +8795,7 @@
         <v>50.06</v>
       </c>
       <c r="E312" t="n">
-        <v>44.44</v>
+        <v>42.73</v>
       </c>
       <c r="F312" t="n">
         <v>47.82</v>
@@ -8712,7 +8817,7 @@
         <v>50.08</v>
       </c>
       <c r="E313" t="n">
-        <v>44.54</v>
+        <v>42.85</v>
       </c>
       <c r="F313" t="n">
         <v>48.05</v>
@@ -8734,7 +8839,7 @@
         <v>50.01</v>
       </c>
       <c r="E314" t="n">
-        <v>44.58</v>
+        <v>42.89</v>
       </c>
       <c r="F314" t="n">
         <v>48.21</v>
@@ -8756,7 +8861,7 @@
         <v>49.95</v>
       </c>
       <c r="E315" t="n">
-        <v>44.58</v>
+        <v>42.94</v>
       </c>
       <c r="F315" t="n">
         <v>48.25</v>
@@ -8778,7 +8883,7 @@
         <v>49.87</v>
       </c>
       <c r="E316" t="n">
-        <v>44.56</v>
+        <v>42.95</v>
       </c>
       <c r="F316" t="n">
         <v>48.24</v>
@@ -8800,7 +8905,7 @@
         <v>49.86</v>
       </c>
       <c r="E317" t="n">
-        <v>44.58</v>
+        <v>43.02</v>
       </c>
       <c r="F317" t="n">
         <v>48.27</v>
@@ -8822,7 +8927,7 @@
         <v>49.72</v>
       </c>
       <c r="E318" t="n">
-        <v>44.53</v>
+        <v>43.01</v>
       </c>
       <c r="F318" t="n">
         <v>48.22</v>
@@ -8844,7 +8949,7 @@
         <v>49.59</v>
       </c>
       <c r="E319" t="n">
-        <v>44.49</v>
+        <v>42.99</v>
       </c>
       <c r="F319" t="n">
         <v>48.19</v>
@@ -8866,7 +8971,7 @@
         <v>49.49</v>
       </c>
       <c r="E320" t="n">
-        <v>44.57</v>
+        <v>43.06</v>
       </c>
       <c r="F320" t="n">
         <v>48.48</v>
@@ -8888,7 +8993,7 @@
         <v>49.31</v>
       </c>
       <c r="E321" t="n">
-        <v>44.64</v>
+        <v>43.09</v>
       </c>
       <c r="F321" t="n">
         <v>48.85</v>
@@ -8910,7 +9015,7 @@
         <v>49.21</v>
       </c>
       <c r="E322" t="n">
-        <v>44.74</v>
+        <v>43.16</v>
       </c>
       <c r="F322" t="n">
         <v>49.2</v>
@@ -8932,7 +9037,7 @@
         <v>49.23</v>
       </c>
       <c r="E323" t="n">
-        <v>44.71</v>
+        <v>43.14</v>
       </c>
       <c r="F323" t="n">
         <v>49.23</v>
@@ -8954,7 +9059,7 @@
         <v>49.4</v>
       </c>
       <c r="E324" t="n">
-        <v>44.72</v>
+        <v>43.11</v>
       </c>
       <c r="F324" t="n">
         <v>49.4</v>
@@ -8976,7 +9081,7 @@
         <v>49.49</v>
       </c>
       <c r="E325" t="n">
-        <v>44.69</v>
+        <v>43.15</v>
       </c>
       <c r="F325" t="n">
         <v>49.49</v>
@@ -8998,7 +9103,7 @@
         <v>49.61</v>
       </c>
       <c r="E326" t="n">
-        <v>44.69</v>
+        <v>43.2</v>
       </c>
       <c r="F326" t="n">
         <v>49.61</v>
@@ -9020,7 +9125,7 @@
         <v>49.54</v>
       </c>
       <c r="E327" t="n">
-        <v>44.6</v>
+        <v>43.09</v>
       </c>
       <c r="F327" t="n">
         <v>49.54</v>
@@ -9042,7 +9147,7 @@
         <v>49.29</v>
       </c>
       <c r="E328" t="n">
-        <v>44.44</v>
+        <v>42.97</v>
       </c>
       <c r="F328" t="n">
         <v>49.29</v>
@@ -9064,7 +9169,7 @@
         <v>49.07</v>
       </c>
       <c r="E329" t="n">
-        <v>44.32</v>
+        <v>42.93</v>
       </c>
       <c r="F329" t="n">
         <v>49.07</v>
@@ -9086,7 +9191,7 @@
         <v>49.12</v>
       </c>
       <c r="E330" t="n">
-        <v>44.31</v>
+        <v>42.97</v>
       </c>
       <c r="F330" t="n">
         <v>49.12</v>
@@ -9108,7 +9213,7 @@
         <v>49.82</v>
       </c>
       <c r="E331" t="n">
-        <v>44.49</v>
+        <v>43.14</v>
       </c>
       <c r="F331" t="n">
         <v>49.82</v>
@@ -9130,7 +9235,7 @@
         <v>50.43</v>
       </c>
       <c r="E332" t="n">
-        <v>44.68</v>
+        <v>43.33</v>
       </c>
       <c r="F332" t="n">
         <v>50.43</v>
@@ -9152,7 +9257,7 @@
         <v>50.49</v>
       </c>
       <c r="E333" t="n">
-        <v>44.69</v>
+        <v>43.35</v>
       </c>
       <c r="F333" t="n">
         <v>50.49</v>
@@ -9174,7 +9279,7 @@
         <v>50.55</v>
       </c>
       <c r="E334" t="n">
-        <v>44.7</v>
+        <v>43.36</v>
       </c>
       <c r="F334" t="n">
         <v>50.55</v>
@@ -9196,7 +9301,7 @@
         <v>50.69</v>
       </c>
       <c r="E335" t="n">
-        <v>44.69</v>
+        <v>43.39</v>
       </c>
       <c r="F335" t="n">
         <v>50.69</v>
@@ -9218,7 +9323,7 @@
         <v>50.73</v>
       </c>
       <c r="E336" t="n">
-        <v>44.59</v>
+        <v>43.34</v>
       </c>
       <c r="F336" t="n">
         <v>50.73</v>
@@ -9240,7 +9345,7 @@
         <v>50.71</v>
       </c>
       <c r="E337" t="n">
-        <v>44.55</v>
+        <v>43.37</v>
       </c>
       <c r="F337" t="n">
         <v>50.71</v>
@@ -9262,7 +9367,7 @@
         <v>50.88</v>
       </c>
       <c r="E338" t="n">
-        <v>44.6</v>
+        <v>43.41</v>
       </c>
       <c r="F338" t="n">
         <v>50.88</v>
@@ -9284,7 +9389,7 @@
         <v>51.02</v>
       </c>
       <c r="E339" t="n">
-        <v>44.68</v>
+        <v>43.48</v>
       </c>
       <c r="F339" t="n">
         <v>51.02</v>
@@ -9306,7 +9411,7 @@
         <v>51.07</v>
       </c>
       <c r="E340" t="n">
-        <v>44.72</v>
+        <v>43.55</v>
       </c>
       <c r="F340" t="n">
         <v>51.07</v>
@@ -9328,7 +9433,7 @@
         <v>51.11</v>
       </c>
       <c r="E341" t="n">
-        <v>44.76</v>
+        <v>43.6</v>
       </c>
       <c r="F341" t="n">
         <v>51.11</v>
@@ -9350,7 +9455,7 @@
         <v>51.05</v>
       </c>
       <c r="E342" t="n">
-        <v>44.75</v>
+        <v>43.58</v>
       </c>
       <c r="F342" t="n">
         <v>51.05</v>
@@ -9372,7 +9477,7 @@
         <v>51.06</v>
       </c>
       <c r="E343" t="n">
-        <v>44.75</v>
+        <v>43.55</v>
       </c>
       <c r="F343" t="n">
         <v>51.06</v>
@@ -9394,7 +9499,7 @@
         <v>51.1</v>
       </c>
       <c r="E344" t="n">
-        <v>44.77</v>
+        <v>43.55</v>
       </c>
       <c r="F344" t="n">
         <v>51.1</v>
@@ -9416,7 +9521,7 @@
         <v>51.1</v>
       </c>
       <c r="E345" t="n">
-        <v>44.76</v>
+        <v>43.59</v>
       </c>
       <c r="F345" t="n">
         <v>51.1</v>
@@ -9438,7 +9543,7 @@
         <v>51.01</v>
       </c>
       <c r="E346" t="n">
-        <v>44.7</v>
+        <v>43.62</v>
       </c>
       <c r="F346" t="n">
         <v>51.01</v>
@@ -9460,7 +9565,7 @@
         <v>50.93</v>
       </c>
       <c r="E347" t="n">
-        <v>44.7</v>
+        <v>43.7</v>
       </c>
       <c r="F347" t="n">
         <v>50.93</v>
@@ -9482,7 +9587,7 @@
         <v>50.97</v>
       </c>
       <c r="E348" t="n">
-        <v>44.72</v>
+        <v>43.73</v>
       </c>
       <c r="F348" t="n">
         <v>50.97</v>
@@ -9504,7 +9609,7 @@
         <v>51.05</v>
       </c>
       <c r="E349" t="n">
-        <v>44.75</v>
+        <v>43.77</v>
       </c>
       <c r="F349" t="n">
         <v>51.05</v>
@@ -9526,7 +9631,7 @@
         <v>51.01</v>
       </c>
       <c r="E350" t="n">
-        <v>44.75</v>
+        <v>43.82</v>
       </c>
       <c r="F350" t="n">
         <v>51.01</v>
@@ -9548,7 +9653,7 @@
         <v>51.05</v>
       </c>
       <c r="E351" t="n">
-        <v>44.78</v>
+        <v>43.88</v>
       </c>
       <c r="F351" t="n">
         <v>51.05</v>
@@ -9570,7 +9675,7 @@
         <v>51.02</v>
       </c>
       <c r="E352" t="n">
-        <v>44.79</v>
+        <v>43.93</v>
       </c>
       <c r="F352" t="n">
         <v>51.02</v>
@@ -9592,7 +9697,7 @@
         <v>50.93</v>
       </c>
       <c r="E353" t="n">
-        <v>44.8</v>
+        <v>43.93</v>
       </c>
       <c r="F353" t="n">
         <v>50.93</v>
@@ -9614,7 +9719,7 @@
         <v>50.73</v>
       </c>
       <c r="E354" t="n">
-        <v>44.72</v>
+        <v>43.89</v>
       </c>
       <c r="F354" t="n">
         <v>50.73</v>
@@ -9636,7 +9741,7 @@
         <v>50.72</v>
       </c>
       <c r="E355" t="n">
-        <v>44.7</v>
+        <v>43.89</v>
       </c>
       <c r="F355" t="n">
         <v>50.72</v>
@@ -9658,7 +9763,7 @@
         <v>51.07</v>
       </c>
       <c r="E356" t="n">
-        <v>44.88</v>
+        <v>44.05</v>
       </c>
       <c r="F356" t="n">
         <v>51.07</v>
@@ -9680,7 +9785,7 @@
         <v>51.19</v>
       </c>
       <c r="E357" t="n">
-        <v>44.99</v>
+        <v>44.17</v>
       </c>
       <c r="F357" t="n">
         <v>51.19</v>
@@ -9702,7 +9807,7 @@
         <v>51.35</v>
       </c>
       <c r="E358" t="n">
-        <v>45.1</v>
+        <v>44.27</v>
       </c>
       <c r="F358" t="n">
         <v>51.35</v>
@@ -9724,7 +9829,7 @@
         <v>51.44</v>
       </c>
       <c r="E359" t="n">
-        <v>45.2</v>
+        <v>44.38</v>
       </c>
       <c r="F359" t="n">
         <v>51.44</v>
@@ -9746,7 +9851,7 @@
         <v>51.88</v>
       </c>
       <c r="E360" t="n">
-        <v>45.42</v>
+        <v>44.57</v>
       </c>
       <c r="F360" t="n">
         <v>51.88</v>
@@ -9768,7 +9873,7 @@
         <v>52.16</v>
       </c>
       <c r="E361" t="n">
-        <v>45.55</v>
+        <v>44.69</v>
       </c>
       <c r="F361" t="n">
         <v>52.16</v>
@@ -9790,7 +9895,7 @@
         <v>52.14</v>
       </c>
       <c r="E362" t="n">
-        <v>45.6</v>
+        <v>44.75</v>
       </c>
       <c r="F362" t="n">
         <v>52.14</v>
@@ -9812,7 +9917,7 @@
         <v>52.26</v>
       </c>
       <c r="E363" t="n">
-        <v>45.68</v>
+        <v>44.88</v>
       </c>
       <c r="F363" t="n">
         <v>52.26</v>
@@ -9834,7 +9939,7 @@
         <v>52.39</v>
       </c>
       <c r="E364" t="n">
-        <v>45.72</v>
+        <v>44.96</v>
       </c>
       <c r="F364" t="n">
         <v>52.39</v>
@@ -9856,7 +9961,7 @@
         <v>52.52</v>
       </c>
       <c r="E365" t="n">
-        <v>45.77</v>
+        <v>45.04</v>
       </c>
       <c r="F365" t="n">
         <v>52.52</v>
@@ -9878,7 +9983,7 @@
         <v>52.72</v>
       </c>
       <c r="E366" t="n">
-        <v>45.91</v>
+        <v>45.19</v>
       </c>
       <c r="F366" t="n">
         <v>52.72</v>
@@ -26155,7 +26260,7 @@
         <v>494.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1154.61</v>
+        <v>1154.77</v>
       </c>
     </row>
     <row r="3">
@@ -38299,13 +38404,13 @@
         <v>272.6</v>
       </c>
       <c r="C200" t="n">
-        <v>385.84</v>
+        <v>494.75</v>
       </c>
       <c r="D200" t="n">
-        <v>658.4400000000001</v>
+        <v>767.35</v>
       </c>
       <c r="E200" t="n">
-        <v>524.96</v>
+        <v>585.55</v>
       </c>
       <c r="F200" t="n">
         <v>658.4400000000001</v>
@@ -38321,13 +38426,13 @@
         <v>272.4</v>
       </c>
       <c r="C201" t="n">
-        <v>385.54</v>
+        <v>494.31</v>
       </c>
       <c r="D201" t="n">
-        <v>657.9400000000001</v>
+        <v>766.71</v>
       </c>
       <c r="E201" t="n">
-        <v>524.9299999999999</v>
+        <v>585.38</v>
       </c>
       <c r="F201" t="n">
         <v>657.9400000000001</v>
@@ -38343,13 +38448,13 @@
         <v>272.2</v>
       </c>
       <c r="C202" t="n">
-        <v>385.23</v>
+        <v>493.88</v>
       </c>
       <c r="D202" t="n">
-        <v>657.4299999999999</v>
+        <v>766.08</v>
       </c>
       <c r="E202" t="n">
-        <v>524.9</v>
+        <v>585.2</v>
       </c>
       <c r="F202" t="n">
         <v>657.4299999999999</v>
@@ -38365,13 +38470,13 @@
         <v>272</v>
       </c>
       <c r="C203" t="n">
-        <v>385.43</v>
+        <v>493.44</v>
       </c>
       <c r="D203" t="n">
-        <v>657.4299999999999</v>
+        <v>765.4400000000001</v>
       </c>
       <c r="E203" t="n">
-        <v>525.05</v>
+        <v>585.14</v>
       </c>
       <c r="F203" t="n">
         <v>657.4299999999999</v>
@@ -38387,13 +38492,13 @@
         <v>271.8</v>
       </c>
       <c r="C204" t="n">
-        <v>384.63</v>
+        <v>493.01</v>
       </c>
       <c r="D204" t="n">
-        <v>656.4299999999999</v>
+        <v>764.8099999999999</v>
       </c>
       <c r="E204" t="n">
-        <v>524.85</v>
+        <v>584.84</v>
       </c>
       <c r="F204" t="n">
         <v>656.4299999999999</v>
@@ -38409,13 +38514,13 @@
         <v>271.6</v>
       </c>
       <c r="C205" t="n">
-        <v>383.82</v>
+        <v>492.57</v>
       </c>
       <c r="D205" t="n">
-        <v>655.42</v>
+        <v>764.17</v>
       </c>
       <c r="E205" t="n">
-        <v>524.66</v>
+        <v>584.54</v>
       </c>
       <c r="F205" t="n">
         <v>655.42</v>
@@ -38431,13 +38536,13 @@
         <v>271.4</v>
       </c>
       <c r="C206" t="n">
-        <v>383.02</v>
+        <v>492.14</v>
       </c>
       <c r="D206" t="n">
-        <v>654.42</v>
+        <v>763.54</v>
       </c>
       <c r="E206" t="n">
-        <v>524.47</v>
+        <v>584.24</v>
       </c>
       <c r="F206" t="n">
         <v>654.42</v>
@@ -38453,13 +38558,13 @@
         <v>271.2</v>
       </c>
       <c r="C207" t="n">
-        <v>382.21</v>
+        <v>491.71</v>
       </c>
       <c r="D207" t="n">
-        <v>653.41</v>
+        <v>762.91</v>
       </c>
       <c r="E207" t="n">
-        <v>524.27</v>
+        <v>583.9299999999999</v>
       </c>
       <c r="F207" t="n">
         <v>653.41</v>
@@ -38475,13 +38580,13 @@
         <v>271</v>
       </c>
       <c r="C208" t="n">
-        <v>381.41</v>
+        <v>491.27</v>
       </c>
       <c r="D208" t="n">
-        <v>652.41</v>
+        <v>762.27</v>
       </c>
       <c r="E208" t="n">
-        <v>524.08</v>
+        <v>583.63</v>
       </c>
       <c r="F208" t="n">
         <v>652.41</v>
@@ -38497,13 +38602,13 @@
         <v>270.8</v>
       </c>
       <c r="C209" t="n">
-        <v>380.1</v>
+        <v>490.84</v>
       </c>
       <c r="D209" t="n">
-        <v>650.9</v>
+        <v>761.64</v>
       </c>
       <c r="E209" t="n">
-        <v>523.72</v>
+        <v>583.2</v>
       </c>
       <c r="F209" t="n">
         <v>650.9</v>
@@ -38519,13 +38624,13 @@
         <v>270.6</v>
       </c>
       <c r="C210" t="n">
-        <v>379.8</v>
+        <v>490.4</v>
       </c>
       <c r="D210" t="n">
-        <v>650.4</v>
+        <v>761</v>
       </c>
       <c r="E210" t="n">
-        <v>523.7</v>
+        <v>583.02</v>
       </c>
       <c r="F210" t="n">
         <v>650.4</v>
@@ -38541,13 +38646,13 @@
         <v>270.4</v>
       </c>
       <c r="C211" t="n">
-        <v>380.32</v>
+        <v>489.97</v>
       </c>
       <c r="D211" t="n">
-        <v>650.72</v>
+        <v>760.37</v>
       </c>
       <c r="E211" t="n">
-        <v>523.67</v>
+        <v>582.85</v>
       </c>
       <c r="F211" t="n">
         <v>649.9</v>
@@ -38563,13 +38668,13 @@
         <v>270.2</v>
       </c>
       <c r="C212" t="n">
-        <v>381.15</v>
+        <v>489.53</v>
       </c>
       <c r="D212" t="n">
-        <v>651.35</v>
+        <v>759.73</v>
       </c>
       <c r="E212" t="n">
-        <v>523.8200000000001</v>
+        <v>582.8</v>
       </c>
       <c r="F212" t="n">
         <v>649.9</v>
@@ -38585,13 +38690,13 @@
         <v>270</v>
       </c>
       <c r="C213" t="n">
-        <v>381.97</v>
+        <v>489.1</v>
       </c>
       <c r="D213" t="n">
-        <v>651.97</v>
+        <v>759.1</v>
       </c>
       <c r="E213" t="n">
-        <v>523.62</v>
+        <v>582.49</v>
       </c>
       <c r="F213" t="n">
         <v>648.89</v>
@@ -38607,13 +38712,13 @@
         <v>270.19</v>
       </c>
       <c r="C214" t="n">
-        <v>382.41</v>
+        <v>488.39</v>
       </c>
       <c r="D214" t="n">
-        <v>652.6</v>
+        <v>758.58</v>
       </c>
       <c r="E214" t="n">
-        <v>523.5599999999999</v>
+        <v>582.3200000000001</v>
       </c>
       <c r="F214" t="n">
         <v>647.89</v>
@@ -38629,13 +38734,13 @@
         <v>270.39</v>
       </c>
       <c r="C215" t="n">
-        <v>382.1</v>
+        <v>487.68</v>
       </c>
       <c r="D215" t="n">
-        <v>652.48</v>
+        <v>758.0700000000001</v>
       </c>
       <c r="E215" t="n">
-        <v>523.25</v>
+        <v>581.95</v>
       </c>
       <c r="F215" t="n">
         <v>646.88</v>
@@ -38651,13 +38756,13 @@
         <v>270.58</v>
       </c>
       <c r="C216" t="n">
-        <v>381.79</v>
+        <v>486.97</v>
       </c>
       <c r="D216" t="n">
-        <v>652.37</v>
+        <v>757.55</v>
       </c>
       <c r="E216" t="n">
-        <v>522.9400000000001</v>
+        <v>581.6</v>
       </c>
       <c r="F216" t="n">
         <v>645.88</v>
@@ -38673,13 +38778,13 @@
         <v>270.77</v>
       </c>
       <c r="C217" t="n">
-        <v>381.48</v>
+        <v>486.26</v>
       </c>
       <c r="D217" t="n">
-        <v>652.25</v>
+        <v>757.04</v>
       </c>
       <c r="E217" t="n">
-        <v>522.64</v>
+        <v>581.24</v>
       </c>
       <c r="F217" t="n">
         <v>644.88</v>
@@ -38695,13 +38800,13 @@
         <v>270.97</v>
       </c>
       <c r="C218" t="n">
-        <v>381.17</v>
+        <v>485.55</v>
       </c>
       <c r="D218" t="n">
-        <v>652.14</v>
+        <v>756.52</v>
       </c>
       <c r="E218" t="n">
-        <v>522.3200000000001</v>
+        <v>580.87</v>
       </c>
       <c r="F218" t="n">
         <v>643.87</v>
@@ -38717,13 +38822,13 @@
         <v>271.16</v>
       </c>
       <c r="C219" t="n">
-        <v>380.86</v>
+        <v>484.84</v>
       </c>
       <c r="D219" t="n">
-        <v>652.02</v>
+        <v>756</v>
       </c>
       <c r="E219" t="n">
-        <v>522.27</v>
+        <v>580.7</v>
       </c>
       <c r="F219" t="n">
         <v>643.62</v>
@@ -38739,13 +38844,13 @@
         <v>271.35</v>
       </c>
       <c r="C220" t="n">
-        <v>380.55</v>
+        <v>484.13</v>
       </c>
       <c r="D220" t="n">
-        <v>651.9</v>
+        <v>755.49</v>
       </c>
       <c r="E220" t="n">
-        <v>522.21</v>
+        <v>580.53</v>
       </c>
       <c r="F220" t="n">
         <v>643.37</v>
@@ -38761,13 +38866,13 @@
         <v>271.55</v>
       </c>
       <c r="C221" t="n">
-        <v>380.24</v>
+        <v>483.42</v>
       </c>
       <c r="D221" t="n">
-        <v>651.79</v>
+        <v>754.97</v>
       </c>
       <c r="E221" t="n">
-        <v>521.9</v>
+        <v>580.17</v>
       </c>
       <c r="F221" t="n">
         <v>642.37</v>
@@ -38783,13 +38888,13 @@
         <v>271.74</v>
       </c>
       <c r="C222" t="n">
-        <v>379.93</v>
+        <v>482.71</v>
       </c>
       <c r="D222" t="n">
-        <v>651.67</v>
+        <v>754.45</v>
       </c>
       <c r="E222" t="n">
-        <v>521.59</v>
+        <v>579.8099999999999</v>
       </c>
       <c r="F222" t="n">
         <v>641.36</v>
@@ -38805,13 +38910,13 @@
         <v>271.94</v>
       </c>
       <c r="C223" t="n">
-        <v>379.62</v>
+        <v>482</v>
       </c>
       <c r="D223" t="n">
-        <v>651.55</v>
+        <v>753.9400000000001</v>
       </c>
       <c r="E223" t="n">
-        <v>521.37</v>
+        <v>579.51</v>
       </c>
       <c r="F223" t="n">
         <v>640.61</v>
@@ -38827,13 +38932,13 @@
         <v>272.13</v>
       </c>
       <c r="C224" t="n">
-        <v>379.31</v>
+        <v>481.29</v>
       </c>
       <c r="D224" t="n">
-        <v>651.4400000000001</v>
+        <v>753.42</v>
       </c>
       <c r="E224" t="n">
-        <v>521.14</v>
+        <v>579.21</v>
       </c>
       <c r="F224" t="n">
         <v>639.86</v>
@@ -38849,13 +38954,13 @@
         <v>272.32</v>
       </c>
       <c r="C225" t="n">
-        <v>379</v>
+        <v>480.58</v>
       </c>
       <c r="D225" t="n">
-        <v>651.3200000000001</v>
+        <v>752.91</v>
       </c>
       <c r="E225" t="n">
-        <v>520.83</v>
+        <v>578.85</v>
       </c>
       <c r="F225" t="n">
         <v>638.85</v>
@@ -38871,13 +38976,13 @@
         <v>272.52</v>
       </c>
       <c r="C226" t="n">
-        <v>378.69</v>
+        <v>479.87</v>
       </c>
       <c r="D226" t="n">
-        <v>651.21</v>
+        <v>752.39</v>
       </c>
       <c r="E226" t="n">
-        <v>520.52</v>
+        <v>578.49</v>
       </c>
       <c r="F226" t="n">
         <v>637.85</v>
@@ -38893,13 +38998,13 @@
         <v>272.71</v>
       </c>
       <c r="C227" t="n">
-        <v>378.38</v>
+        <v>479.16</v>
       </c>
       <c r="D227" t="n">
-        <v>651.09</v>
+        <v>751.87</v>
       </c>
       <c r="E227" t="n">
-        <v>520.22</v>
+        <v>578.13</v>
       </c>
       <c r="F227" t="n">
         <v>636.85</v>
@@ -38915,13 +39020,13 @@
         <v>272.9</v>
       </c>
       <c r="C228" t="n">
-        <v>378.07</v>
+        <v>478.45</v>
       </c>
       <c r="D228" t="n">
-        <v>650.97</v>
+        <v>751.36</v>
       </c>
       <c r="E228" t="n">
-        <v>519.91</v>
+        <v>577.77</v>
       </c>
       <c r="F228" t="n">
         <v>635.85</v>
@@ -38937,13 +39042,13 @@
         <v>273.1</v>
       </c>
       <c r="C229" t="n">
-        <v>377.76</v>
+        <v>477.75</v>
       </c>
       <c r="D229" t="n">
-        <v>650.86</v>
+        <v>750.84</v>
       </c>
       <c r="E229" t="n">
-        <v>519.6</v>
+        <v>577.41</v>
       </c>
       <c r="F229" t="n">
         <v>634.85</v>
@@ -38959,13 +39064,13 @@
         <v>273.29</v>
       </c>
       <c r="C230" t="n">
-        <v>377.45</v>
+        <v>477.04</v>
       </c>
       <c r="D230" t="n">
-        <v>650.74</v>
+        <v>750.33</v>
       </c>
       <c r="E230" t="n">
-        <v>519.29</v>
+        <v>577.05</v>
       </c>
       <c r="F230" t="n">
         <v>633.85</v>
@@ -38981,13 +39086,13 @@
         <v>273.48</v>
       </c>
       <c r="C231" t="n">
-        <v>377.14</v>
+        <v>476.33</v>
       </c>
       <c r="D231" t="n">
-        <v>650.63</v>
+        <v>749.8099999999999</v>
       </c>
       <c r="E231" t="n">
-        <v>518.99</v>
+        <v>576.6900000000001</v>
       </c>
       <c r="F231" t="n">
         <v>632.85</v>
@@ -39003,13 +39108,13 @@
         <v>273.68</v>
       </c>
       <c r="C232" t="n">
-        <v>376.83</v>
+        <v>475.62</v>
       </c>
       <c r="D232" t="n">
-        <v>650.51</v>
+        <v>749.29</v>
       </c>
       <c r="E232" t="n">
-        <v>518.6799999999999</v>
+        <v>576.33</v>
       </c>
       <c r="F232" t="n">
         <v>631.85</v>
@@ -39025,13 +39130,13 @@
         <v>273.87</v>
       </c>
       <c r="C233" t="n">
-        <v>376.52</v>
+        <v>474.91</v>
       </c>
       <c r="D233" t="n">
-        <v>650.39</v>
+        <v>748.78</v>
       </c>
       <c r="E233" t="n">
-        <v>518.7</v>
+        <v>576.22</v>
       </c>
       <c r="F233" t="n">
         <v>631.85</v>
@@ -39047,13 +39152,13 @@
         <v>274.06</v>
       </c>
       <c r="C234" t="n">
-        <v>376.21</v>
+        <v>474.2</v>
       </c>
       <c r="D234" t="n">
-        <v>650.28</v>
+        <v>748.26</v>
       </c>
       <c r="E234" t="n">
-        <v>518.73</v>
+        <v>576.11</v>
       </c>
       <c r="F234" t="n">
         <v>631.85</v>
@@ -39069,13 +39174,13 @@
         <v>274.26</v>
       </c>
       <c r="C235" t="n">
-        <v>375.9</v>
+        <v>473.49</v>
       </c>
       <c r="D235" t="n">
-        <v>650.16</v>
+        <v>747.75</v>
       </c>
       <c r="E235" t="n">
-        <v>518.76</v>
+        <v>576</v>
       </c>
       <c r="F235" t="n">
         <v>631.85</v>
@@ -39091,13 +39196,13 @@
         <v>274.45</v>
       </c>
       <c r="C236" t="n">
-        <v>375.59</v>
+        <v>472.78</v>
       </c>
       <c r="D236" t="n">
-        <v>650.05</v>
+        <v>747.23</v>
       </c>
       <c r="E236" t="n">
-        <v>518.78</v>
+        <v>575.89</v>
       </c>
       <c r="F236" t="n">
         <v>631.85</v>
@@ -39113,13 +39218,13 @@
         <v>274.65</v>
       </c>
       <c r="C237" t="n">
-        <v>375.28</v>
+        <v>472.07</v>
       </c>
       <c r="D237" t="n">
-        <v>649.9299999999999</v>
+        <v>746.71</v>
       </c>
       <c r="E237" t="n">
-        <v>518.8099999999999</v>
+        <v>575.78</v>
       </c>
       <c r="F237" t="n">
         <v>631.85</v>
@@ -39135,13 +39240,13 @@
         <v>274.84</v>
       </c>
       <c r="C238" t="n">
-        <v>374.97</v>
+        <v>471.36</v>
       </c>
       <c r="D238" t="n">
-        <v>649.8099999999999</v>
+        <v>746.2</v>
       </c>
       <c r="E238" t="n">
-        <v>518.83</v>
+        <v>575.67</v>
       </c>
       <c r="F238" t="n">
         <v>631.85</v>
@@ -39157,13 +39262,13 @@
         <v>275.03</v>
       </c>
       <c r="C239" t="n">
-        <v>374.66</v>
+        <v>470.65</v>
       </c>
       <c r="D239" t="n">
-        <v>649.7</v>
+        <v>745.6799999999999</v>
       </c>
       <c r="E239" t="n">
-        <v>518.86</v>
+        <v>575.5599999999999</v>
       </c>
       <c r="F239" t="n">
         <v>631.85</v>
@@ -39179,13 +39284,13 @@
         <v>275.23</v>
       </c>
       <c r="C240" t="n">
-        <v>374.35</v>
+        <v>469.94</v>
       </c>
       <c r="D240" t="n">
-        <v>649.58</v>
+        <v>745.16</v>
       </c>
       <c r="E240" t="n">
-        <v>518.89</v>
+        <v>575.46</v>
       </c>
       <c r="F240" t="n">
         <v>631.85</v>
@@ -39201,13 +39306,13 @@
         <v>275.42</v>
       </c>
       <c r="C241" t="n">
-        <v>374.05</v>
+        <v>469.23</v>
       </c>
       <c r="D241" t="n">
-        <v>649.46</v>
+        <v>744.65</v>
       </c>
       <c r="E241" t="n">
-        <v>518.91</v>
+        <v>575.35</v>
       </c>
       <c r="F241" t="n">
         <v>631.85</v>
@@ -39223,13 +39328,13 @@
         <v>275.61</v>
       </c>
       <c r="C242" t="n">
-        <v>373.74</v>
+        <v>468.52</v>
       </c>
       <c r="D242" t="n">
-        <v>649.35</v>
+        <v>744.13</v>
       </c>
       <c r="E242" t="n">
-        <v>518.9400000000001</v>
+        <v>575.24</v>
       </c>
       <c r="F242" t="n">
         <v>631.85</v>
@@ -39245,13 +39350,13 @@
         <v>275.81</v>
       </c>
       <c r="C243" t="n">
-        <v>373.43</v>
+        <v>467.81</v>
       </c>
       <c r="D243" t="n">
-        <v>649.23</v>
+        <v>743.62</v>
       </c>
       <c r="E243" t="n">
-        <v>518.96</v>
+        <v>575.13</v>
       </c>
       <c r="F243" t="n">
         <v>631.85</v>
@@ -39267,13 +39372,13 @@
         <v>276</v>
       </c>
       <c r="C244" t="n">
-        <v>373.12</v>
+        <v>467.1</v>
       </c>
       <c r="D244" t="n">
-        <v>649.12</v>
+        <v>743.1</v>
       </c>
       <c r="E244" t="n">
-        <v>519.16</v>
+        <v>575.14</v>
       </c>
       <c r="F244" t="n">
         <v>632.35</v>
@@ -39289,13 +39394,13 @@
         <v>276.3</v>
       </c>
       <c r="C245" t="n">
-        <v>372.7</v>
+        <v>466.4</v>
       </c>
       <c r="D245" t="n">
-        <v>649</v>
+        <v>742.7</v>
       </c>
       <c r="E245" t="n">
-        <v>519.05</v>
+        <v>574.96</v>
       </c>
       <c r="F245" t="n">
         <v>631.85</v>
@@ -39311,13 +39416,13 @@
         <v>276.6</v>
       </c>
       <c r="C246" t="n">
-        <v>373.66</v>
+        <v>465.7</v>
       </c>
       <c r="D246" t="n">
-        <v>650.26</v>
+        <v>742.3</v>
       </c>
       <c r="E246" t="n">
-        <v>519.74</v>
+        <v>575.38</v>
       </c>
       <c r="F246" t="n">
         <v>632.35</v>
@@ -39333,13 +39438,13 @@
         <v>276.9</v>
       </c>
       <c r="C247" t="n">
-        <v>374.62</v>
+        <v>465</v>
       </c>
       <c r="D247" t="n">
-        <v>651.52</v>
+        <v>741.9</v>
       </c>
       <c r="E247" t="n">
-        <v>520.26</v>
+        <v>575.67</v>
       </c>
       <c r="F247" t="n">
         <v>632.35</v>
@@ -39355,13 +39460,13 @@
         <v>277.2</v>
       </c>
       <c r="C248" t="n">
-        <v>375.58</v>
+        <v>464.3</v>
       </c>
       <c r="D248" t="n">
-        <v>652.78</v>
+        <v>741.5</v>
       </c>
       <c r="E248" t="n">
-        <v>520.78</v>
+        <v>575.96</v>
       </c>
       <c r="F248" t="n">
         <v>632.35</v>
@@ -39377,13 +39482,13 @@
         <v>277.5</v>
       </c>
       <c r="C249" t="n">
-        <v>376.55</v>
+        <v>463.6</v>
       </c>
       <c r="D249" t="n">
-        <v>654.05</v>
+        <v>741.1</v>
       </c>
       <c r="E249" t="n">
-        <v>521.13</v>
+        <v>576.12</v>
       </c>
       <c r="F249" t="n">
         <v>631.85</v>
@@ -39399,13 +39504,13 @@
         <v>277.8</v>
       </c>
       <c r="C250" t="n">
-        <v>377.51</v>
+        <v>462.9</v>
       </c>
       <c r="D250" t="n">
-        <v>655.3099999999999</v>
+        <v>740.7</v>
       </c>
       <c r="E250" t="n">
-        <v>521.65</v>
+        <v>576.41</v>
       </c>
       <c r="F250" t="n">
         <v>631.85</v>
@@ -39421,13 +39526,13 @@
         <v>278.1</v>
       </c>
       <c r="C251" t="n">
-        <v>378.47</v>
+        <v>462.2</v>
       </c>
       <c r="D251" t="n">
-        <v>656.5700000000001</v>
+        <v>740.3</v>
       </c>
       <c r="E251" t="n">
-        <v>522.17</v>
+        <v>576.7</v>
       </c>
       <c r="F251" t="n">
         <v>631.85</v>
@@ -39443,13 +39548,13 @@
         <v>278.4</v>
       </c>
       <c r="C252" t="n">
-        <v>379.43</v>
+        <v>461.5</v>
       </c>
       <c r="D252" t="n">
-        <v>657.83</v>
+        <v>739.9</v>
       </c>
       <c r="E252" t="n">
-        <v>522.6900000000001</v>
+        <v>576.99</v>
       </c>
       <c r="F252" t="n">
         <v>631.85</v>
@@ -39465,13 +39570,13 @@
         <v>278.7</v>
       </c>
       <c r="C253" t="n">
-        <v>380.39</v>
+        <v>460.8</v>
       </c>
       <c r="D253" t="n">
-        <v>659.09</v>
+        <v>739.5</v>
       </c>
       <c r="E253" t="n">
-        <v>523.21</v>
+        <v>577.29</v>
       </c>
       <c r="F253" t="n">
         <v>631.85</v>
@@ -39487,13 +39592,13 @@
         <v>279</v>
       </c>
       <c r="C254" t="n">
-        <v>381.35</v>
+        <v>460.1</v>
       </c>
       <c r="D254" t="n">
-        <v>660.35</v>
+        <v>739.1</v>
       </c>
       <c r="E254" t="n">
-        <v>523.73</v>
+        <v>577.58</v>
       </c>
       <c r="F254" t="n">
         <v>631.85</v>
@@ -39509,13 +39614,13 @@
         <v>279.3</v>
       </c>
       <c r="C255" t="n">
-        <v>382.31</v>
+        <v>459.4</v>
       </c>
       <c r="D255" t="n">
-        <v>661.61</v>
+        <v>738.7</v>
       </c>
       <c r="E255" t="n">
-        <v>524.25</v>
+        <v>577.87</v>
       </c>
       <c r="F255" t="n">
         <v>631.85</v>
@@ -39531,13 +39636,13 @@
         <v>279.6</v>
       </c>
       <c r="C256" t="n">
-        <v>383.27</v>
+        <v>458.7</v>
       </c>
       <c r="D256" t="n">
-        <v>662.87</v>
+        <v>738.3</v>
       </c>
       <c r="E256" t="n">
-        <v>524.77</v>
+        <v>578.16</v>
       </c>
       <c r="F256" t="n">
         <v>631.85</v>
@@ -39553,13 +39658,13 @@
         <v>279.9</v>
       </c>
       <c r="C257" t="n">
-        <v>384.24</v>
+        <v>458</v>
       </c>
       <c r="D257" t="n">
-        <v>664.14</v>
+        <v>737.9</v>
       </c>
       <c r="E257" t="n">
-        <v>525.3</v>
+        <v>578.45</v>
       </c>
       <c r="F257" t="n">
         <v>631.85</v>
@@ -39575,13 +39680,13 @@
         <v>280.2</v>
       </c>
       <c r="C258" t="n">
-        <v>385.2</v>
+        <v>457.3</v>
       </c>
       <c r="D258" t="n">
-        <v>665.4</v>
+        <v>737.5</v>
       </c>
       <c r="E258" t="n">
-        <v>525.8200000000001</v>
+        <v>578.74</v>
       </c>
       <c r="F258" t="n">
         <v>631.85</v>
@@ -39597,13 +39702,13 @@
         <v>280.5</v>
       </c>
       <c r="C259" t="n">
-        <v>386.16</v>
+        <v>456.6</v>
       </c>
       <c r="D259" t="n">
-        <v>666.66</v>
+        <v>737.1</v>
       </c>
       <c r="E259" t="n">
-        <v>526.34</v>
+        <v>579.03</v>
       </c>
       <c r="F259" t="n">
         <v>631.85</v>
@@ -39619,13 +39724,13 @@
         <v>280.8</v>
       </c>
       <c r="C260" t="n">
-        <v>387.12</v>
+        <v>455.9</v>
       </c>
       <c r="D260" t="n">
-        <v>667.92</v>
+        <v>736.7</v>
       </c>
       <c r="E260" t="n">
-        <v>526.86</v>
+        <v>579.3200000000001</v>
       </c>
       <c r="F260" t="n">
         <v>631.85</v>
@@ -39641,13 +39746,13 @@
         <v>281.1</v>
       </c>
       <c r="C261" t="n">
-        <v>388.08</v>
+        <v>455.2</v>
       </c>
       <c r="D261" t="n">
-        <v>669.1799999999999</v>
+        <v>736.3</v>
       </c>
       <c r="E261" t="n">
-        <v>527.54</v>
+        <v>579.73</v>
       </c>
       <c r="F261" t="n">
         <v>632.35</v>
@@ -39663,13 +39768,13 @@
         <v>281.4</v>
       </c>
       <c r="C262" t="n">
-        <v>389.04</v>
+        <v>454.5</v>
       </c>
       <c r="D262" t="n">
-        <v>670.4400000000001</v>
+        <v>735.9</v>
       </c>
       <c r="E262" t="n">
-        <v>527.9</v>
+        <v>579.9</v>
       </c>
       <c r="F262" t="n">
         <v>631.85</v>
@@ -39685,13 +39790,13 @@
         <v>281.7</v>
       </c>
       <c r="C263" t="n">
-        <v>390</v>
+        <v>453.8</v>
       </c>
       <c r="D263" t="n">
-        <v>671.7</v>
+        <v>735.5</v>
       </c>
       <c r="E263" t="n">
-        <v>528.42</v>
+        <v>580.1900000000001</v>
       </c>
       <c r="F263" t="n">
         <v>631.85</v>
@@ -39707,13 +39812,13 @@
         <v>282</v>
       </c>
       <c r="C264" t="n">
-        <v>390.97</v>
+        <v>453.1</v>
       </c>
       <c r="D264" t="n">
-        <v>672.97</v>
+        <v>735.1</v>
       </c>
       <c r="E264" t="n">
-        <v>529.11</v>
+        <v>580.6</v>
       </c>
       <c r="F264" t="n">
         <v>632.35</v>
@@ -39729,13 +39834,13 @@
         <v>282.3</v>
       </c>
       <c r="C265" t="n">
-        <v>391.93</v>
+        <v>452.4</v>
       </c>
       <c r="D265" t="n">
-        <v>674.23</v>
+        <v>734.7</v>
       </c>
       <c r="E265" t="n">
-        <v>529.63</v>
+        <v>580.89</v>
       </c>
       <c r="F265" t="n">
         <v>632.35</v>
@@ -39751,13 +39856,13 @@
         <v>282.6</v>
       </c>
       <c r="C266" t="n">
-        <v>392.89</v>
+        <v>451.7</v>
       </c>
       <c r="D266" t="n">
-        <v>675.49</v>
+        <v>734.3</v>
       </c>
       <c r="E266" t="n">
-        <v>529.98</v>
+        <v>581.0599999999999</v>
       </c>
       <c r="F266" t="n">
         <v>631.85</v>
@@ -39773,13 +39878,13 @@
         <v>282.9</v>
       </c>
       <c r="C267" t="n">
-        <v>393.85</v>
+        <v>451</v>
       </c>
       <c r="D267" t="n">
-        <v>676.75</v>
+        <v>733.9</v>
       </c>
       <c r="E267" t="n">
-        <v>530.58</v>
+        <v>581.41</v>
       </c>
       <c r="F267" t="n">
         <v>632.1</v>
@@ -39795,13 +39900,13 @@
         <v>283.2</v>
       </c>
       <c r="C268" t="n">
-        <v>394.81</v>
+        <v>450.3</v>
       </c>
       <c r="D268" t="n">
-        <v>678.01</v>
+        <v>733.5</v>
       </c>
       <c r="E268" t="n">
-        <v>531.02</v>
+        <v>581.64</v>
       </c>
       <c r="F268" t="n">
         <v>631.85</v>
@@ -39817,13 +39922,13 @@
         <v>283.5</v>
       </c>
       <c r="C269" t="n">
-        <v>395.77</v>
+        <v>449.6</v>
       </c>
       <c r="D269" t="n">
-        <v>679.27</v>
+        <v>733.1</v>
       </c>
       <c r="E269" t="n">
-        <v>531.71</v>
+        <v>582.0599999999999</v>
       </c>
       <c r="F269" t="n">
         <v>632.35</v>
@@ -39839,13 +39944,13 @@
         <v>283.8</v>
       </c>
       <c r="C270" t="n">
-        <v>396.73</v>
+        <v>448.9</v>
       </c>
       <c r="D270" t="n">
-        <v>680.53</v>
+        <v>732.7</v>
       </c>
       <c r="E270" t="n">
-        <v>532.0599999999999</v>
+        <v>582.22</v>
       </c>
       <c r="F270" t="n">
         <v>631.85</v>
@@ -39861,13 +39966,13 @@
         <v>284.1</v>
       </c>
       <c r="C271" t="n">
-        <v>397.69</v>
+        <v>448.2</v>
       </c>
       <c r="D271" t="n">
-        <v>681.79</v>
+        <v>732.3</v>
       </c>
       <c r="E271" t="n">
-        <v>532.58</v>
+        <v>582.51</v>
       </c>
       <c r="F271" t="n">
         <v>631.85</v>
@@ -39883,13 +39988,13 @@
         <v>284.4</v>
       </c>
       <c r="C272" t="n">
-        <v>398.66</v>
+        <v>447.5</v>
       </c>
       <c r="D272" t="n">
-        <v>683.0599999999999</v>
+        <v>731.9</v>
       </c>
       <c r="E272" t="n">
-        <v>533.27</v>
+        <v>582.9299999999999</v>
       </c>
       <c r="F272" t="n">
         <v>632.35</v>
@@ -39905,13 +40010,13 @@
         <v>284.7</v>
       </c>
       <c r="C273" t="n">
-        <v>399.62</v>
+        <v>446.8</v>
       </c>
       <c r="D273" t="n">
-        <v>684.3200000000001</v>
+        <v>731.5</v>
       </c>
       <c r="E273" t="n">
-        <v>533.96</v>
+        <v>583.34</v>
       </c>
       <c r="F273" t="n">
         <v>632.85</v>
@@ -39927,13 +40032,13 @@
         <v>285</v>
       </c>
       <c r="C274" t="n">
-        <v>400.58</v>
+        <v>446.1</v>
       </c>
       <c r="D274" t="n">
-        <v>685.58</v>
+        <v>731.1</v>
       </c>
       <c r="E274" t="n">
-        <v>534.3099999999999</v>
+        <v>583.51</v>
       </c>
       <c r="F274" t="n">
         <v>632.35</v>
@@ -39949,13 +40054,13 @@
         <v>285.32</v>
       </c>
       <c r="C275" t="n">
-        <v>401.52</v>
+        <v>446.26</v>
       </c>
       <c r="D275" t="n">
-        <v>686.84</v>
+        <v>731.58</v>
       </c>
       <c r="E275" t="n">
-        <v>534.84</v>
+        <v>584.02</v>
       </c>
       <c r="F275" t="n">
         <v>632.35</v>
@@ -39971,13 +40076,13 @@
         <v>285.65</v>
       </c>
       <c r="C276" t="n">
-        <v>401.71</v>
+        <v>446.42</v>
       </c>
       <c r="D276" t="n">
-        <v>687.36</v>
+        <v>732.0700000000001</v>
       </c>
       <c r="E276" t="n">
-        <v>534.95</v>
+        <v>584.23</v>
       </c>
       <c r="F276" t="n">
         <v>631.85</v>
@@ -39993,13 +40098,13 @@
         <v>285.97</v>
       </c>
       <c r="C277" t="n">
-        <v>401.39</v>
+        <v>446.58</v>
       </c>
       <c r="D277" t="n">
-        <v>687.36</v>
+        <v>732.55</v>
       </c>
       <c r="E277" t="n">
-        <v>535.0599999999999</v>
+        <v>584.4299999999999</v>
       </c>
       <c r="F277" t="n">
         <v>631.85</v>
@@ -40015,13 +40120,13 @@
         <v>286.29</v>
       </c>
       <c r="C278" t="n">
-        <v>400.55</v>
+        <v>446.75</v>
       </c>
       <c r="D278" t="n">
-        <v>686.84</v>
+        <v>733.04</v>
       </c>
       <c r="E278" t="n">
-        <v>535.16</v>
+        <v>584.63</v>
       </c>
       <c r="F278" t="n">
         <v>632.35</v>
@@ -40037,13 +40142,13 @@
         <v>286.61</v>
       </c>
       <c r="C279" t="n">
-        <v>400.23</v>
+        <v>446.91</v>
       </c>
       <c r="D279" t="n">
-        <v>686.84</v>
+        <v>733.52</v>
       </c>
       <c r="E279" t="n">
-        <v>535.27</v>
+        <v>584.83</v>
       </c>
       <c r="F279" t="n">
         <v>632.35</v>
@@ -40059,13 +40164,13 @@
         <v>286.94</v>
       </c>
       <c r="C280" t="n">
-        <v>399.39</v>
+        <v>447.07</v>
       </c>
       <c r="D280" t="n">
-        <v>686.33</v>
+        <v>734</v>
       </c>
       <c r="E280" t="n">
-        <v>535.04</v>
+        <v>584.78</v>
       </c>
       <c r="F280" t="n">
         <v>631.85</v>
@@ -40081,13 +40186,13 @@
         <v>287.26</v>
       </c>
       <c r="C281" t="n">
-        <v>398.56</v>
+        <v>447.23</v>
       </c>
       <c r="D281" t="n">
-        <v>685.8200000000001</v>
+        <v>734.49</v>
       </c>
       <c r="E281" t="n">
-        <v>534.98</v>
+        <v>584.85</v>
       </c>
       <c r="F281" t="n">
         <v>631.85</v>
@@ -40103,13 +40208,13 @@
         <v>287.58</v>
       </c>
       <c r="C282" t="n">
-        <v>397.73</v>
+        <v>447.39</v>
       </c>
       <c r="D282" t="n">
-        <v>685.3099999999999</v>
+        <v>734.97</v>
       </c>
       <c r="E282" t="n">
-        <v>534.91</v>
+        <v>584.9299999999999</v>
       </c>
       <c r="F282" t="n">
         <v>631.85</v>
@@ -40125,13 +40230,13 @@
         <v>287.9</v>
       </c>
       <c r="C283" t="n">
-        <v>397.41</v>
+        <v>447.55</v>
       </c>
       <c r="D283" t="n">
-        <v>685.3099999999999</v>
+        <v>735.45</v>
       </c>
       <c r="E283" t="n">
-        <v>535.02</v>
+        <v>585.13</v>
       </c>
       <c r="F283" t="n">
         <v>631.85</v>
@@ -40147,13 +40252,13 @@
         <v>288.23</v>
       </c>
       <c r="C284" t="n">
-        <v>396.83</v>
+        <v>447.71</v>
       </c>
       <c r="D284" t="n">
-        <v>685.0599999999999</v>
+        <v>735.9400000000001</v>
       </c>
       <c r="E284" t="n">
-        <v>535.05</v>
+        <v>585.27</v>
       </c>
       <c r="F284" t="n">
         <v>631.85</v>
@@ -40169,13 +40274,13 @@
         <v>288.55</v>
       </c>
       <c r="C285" t="n">
-        <v>396.76</v>
+        <v>447.87</v>
       </c>
       <c r="D285" t="n">
-        <v>685.3099999999999</v>
+        <v>736.42</v>
       </c>
       <c r="E285" t="n">
-        <v>535.24</v>
+        <v>585.53</v>
       </c>
       <c r="F285" t="n">
         <v>631.85</v>
@@ -40191,13 +40296,13 @@
         <v>288.87</v>
       </c>
       <c r="C286" t="n">
-        <v>396.95</v>
+        <v>448.04</v>
       </c>
       <c r="D286" t="n">
-        <v>685.8200000000001</v>
+        <v>736.91</v>
       </c>
       <c r="E286" t="n">
-        <v>535.51</v>
+        <v>585.86</v>
       </c>
       <c r="F286" t="n">
         <v>631.85</v>
@@ -40213,13 +40318,13 @@
         <v>289.19</v>
       </c>
       <c r="C287" t="n">
-        <v>396.63</v>
+        <v>448.2</v>
       </c>
       <c r="D287" t="n">
-        <v>685.8200000000001</v>
+        <v>737.39</v>
       </c>
       <c r="E287" t="n">
-        <v>535.62</v>
+        <v>586.0599999999999</v>
       </c>
       <c r="F287" t="n">
         <v>631.85</v>
@@ -40235,13 +40340,13 @@
         <v>289.52</v>
       </c>
       <c r="C288" t="n">
-        <v>395.28</v>
+        <v>448.36</v>
       </c>
       <c r="D288" t="n">
-        <v>684.8</v>
+        <v>737.87</v>
       </c>
       <c r="E288" t="n">
-        <v>535.39</v>
+        <v>586.01</v>
       </c>
       <c r="F288" t="n">
         <v>631.85</v>
@@ -40257,13 +40362,13 @@
         <v>289.84</v>
       </c>
       <c r="C289" t="n">
-        <v>395.22</v>
+        <v>448.52</v>
       </c>
       <c r="D289" t="n">
-        <v>685.0599999999999</v>
+        <v>738.36</v>
       </c>
       <c r="E289" t="n">
-        <v>535.58</v>
+        <v>586.28</v>
       </c>
       <c r="F289" t="n">
         <v>631.85</v>
@@ -40279,13 +40384,13 @@
         <v>290.16</v>
       </c>
       <c r="C290" t="n">
-        <v>395.15</v>
+        <v>448.68</v>
       </c>
       <c r="D290" t="n">
-        <v>685.3099999999999</v>
+        <v>738.84</v>
       </c>
       <c r="E290" t="n">
-        <v>536.61</v>
+        <v>587.17</v>
       </c>
       <c r="F290" t="n">
         <v>634.35</v>
@@ -40301,13 +40406,13 @@
         <v>290.48</v>
       </c>
       <c r="C291" t="n">
-        <v>394.83</v>
+        <v>448.84</v>
       </c>
       <c r="D291" t="n">
-        <v>685.3099999999999</v>
+        <v>739.33</v>
       </c>
       <c r="E291" t="n">
-        <v>537.55</v>
+        <v>587.99</v>
       </c>
       <c r="F291" t="n">
         <v>636.85</v>
@@ -40323,13 +40428,13 @@
         <v>290.81</v>
       </c>
       <c r="C292" t="n">
-        <v>395.01</v>
+        <v>449</v>
       </c>
       <c r="D292" t="n">
-        <v>685.8200000000001</v>
+        <v>739.8099999999999</v>
       </c>
       <c r="E292" t="n">
-        <v>538.83</v>
+        <v>589.0700000000001</v>
       </c>
       <c r="F292" t="n">
         <v>639.86</v>
@@ -40345,13 +40450,13 @@
         <v>291.13</v>
       </c>
       <c r="C293" t="n">
-        <v>394.18</v>
+        <v>449.16</v>
       </c>
       <c r="D293" t="n">
-        <v>685.3099999999999</v>
+        <v>740.29</v>
       </c>
       <c r="E293" t="n">
-        <v>539.1</v>
+        <v>589.4</v>
       </c>
       <c r="F293" t="n">
         <v>640.86</v>
@@ -40367,13 +40472,13 @@
         <v>291.45</v>
       </c>
       <c r="C294" t="n">
-        <v>393.35</v>
+        <v>449.33</v>
       </c>
       <c r="D294" t="n">
-        <v>684.8</v>
+        <v>740.78</v>
       </c>
       <c r="E294" t="n">
-        <v>539.04</v>
+        <v>589.47</v>
       </c>
       <c r="F294" t="n">
         <v>640.86</v>
@@ -40389,13 +40494,13 @@
         <v>291.77</v>
       </c>
       <c r="C295" t="n">
-        <v>392.01</v>
+        <v>449.49</v>
       </c>
       <c r="D295" t="n">
-        <v>683.78</v>
+        <v>741.26</v>
       </c>
       <c r="E295" t="n">
-        <v>539.14</v>
+        <v>589.67</v>
       </c>
       <c r="F295" t="n">
         <v>641.86</v>
@@ -40411,13 +40516,13 @@
         <v>292.1</v>
       </c>
       <c r="C296" t="n">
-        <v>390.66</v>
+        <v>449.65</v>
       </c>
       <c r="D296" t="n">
-        <v>682.76</v>
+        <v>741.75</v>
       </c>
       <c r="E296" t="n">
-        <v>539.08</v>
+        <v>589.74</v>
       </c>
       <c r="F296" t="n">
         <v>642.37</v>
@@ -40433,13 +40538,13 @@
         <v>292.42</v>
       </c>
       <c r="C297" t="n">
-        <v>389.83</v>
+        <v>449.81</v>
       </c>
       <c r="D297" t="n">
-        <v>682.25</v>
+        <v>742.23</v>
       </c>
       <c r="E297" t="n">
-        <v>539.4299999999999</v>
+        <v>590.13</v>
       </c>
       <c r="F297" t="n">
         <v>643.62</v>
@@ -40455,13 +40560,13 @@
         <v>292.74</v>
       </c>
       <c r="C298" t="n">
-        <v>388.48</v>
+        <v>449.97</v>
       </c>
       <c r="D298" t="n">
-        <v>681.22</v>
+        <v>742.71</v>
       </c>
       <c r="E298" t="n">
-        <v>539.4400000000001</v>
+        <v>590.26</v>
       </c>
       <c r="F298" t="n">
         <v>644.37</v>
@@ -40477,13 +40582,13 @@
         <v>293.06</v>
       </c>
       <c r="C299" t="n">
-        <v>387.14</v>
+        <v>450.13</v>
       </c>
       <c r="D299" t="n">
-        <v>680.2</v>
+        <v>743.2</v>
       </c>
       <c r="E299" t="n">
-        <v>540.05</v>
+        <v>590.84</v>
       </c>
       <c r="F299" t="n">
         <v>646.88</v>
@@ -40499,13 +40604,13 @@
         <v>293.39</v>
       </c>
       <c r="C300" t="n">
-        <v>385.79</v>
+        <v>450.29</v>
       </c>
       <c r="D300" t="n">
-        <v>679.1799999999999</v>
+        <v>743.6799999999999</v>
       </c>
       <c r="E300" t="n">
-        <v>540.49</v>
+        <v>591.28</v>
       </c>
       <c r="F300" t="n">
         <v>648.89</v>
@@ -40521,13 +40626,13 @@
         <v>293.71</v>
       </c>
       <c r="C301" t="n">
-        <v>384.45</v>
+        <v>450.45</v>
       </c>
       <c r="D301" t="n">
-        <v>678.16</v>
+        <v>744.16</v>
       </c>
       <c r="E301" t="n">
-        <v>541.59</v>
+        <v>592.24</v>
       </c>
       <c r="F301" t="n">
         <v>652.91</v>
@@ -40543,13 +40648,13 @@
         <v>294.03</v>
       </c>
       <c r="C302" t="n">
-        <v>383.11</v>
+        <v>450.62</v>
       </c>
       <c r="D302" t="n">
-        <v>677.14</v>
+        <v>744.65</v>
       </c>
       <c r="E302" t="n">
-        <v>541.86</v>
+        <v>592.5599999999999</v>
       </c>
       <c r="F302" t="n">
         <v>654.42</v>
@@ -40565,13 +40670,13 @@
         <v>294.35</v>
       </c>
       <c r="C303" t="n">
-        <v>382.28</v>
+        <v>450.78</v>
       </c>
       <c r="D303" t="n">
-        <v>676.63</v>
+        <v>745.13</v>
       </c>
       <c r="E303" t="n">
-        <v>542.13</v>
+        <v>592.88</v>
       </c>
       <c r="F303" t="n">
         <v>655.42</v>
@@ -40587,13 +40692,13 @@
         <v>294.68</v>
       </c>
       <c r="C304" t="n">
-        <v>380.92</v>
+        <v>450.94</v>
       </c>
       <c r="D304" t="n">
-        <v>675.6</v>
+        <v>745.62</v>
       </c>
       <c r="E304" t="n">
-        <v>542.24</v>
+        <v>593.08</v>
       </c>
       <c r="F304" t="n">
         <v>656.4299999999999</v>
@@ -40609,13 +40714,13 @@
         <v>295</v>
       </c>
       <c r="C305" t="n">
-        <v>379.58</v>
+        <v>451.1</v>
       </c>
       <c r="D305" t="n">
-        <v>674.58</v>
+        <v>746.1</v>
       </c>
       <c r="E305" t="n">
-        <v>542.34</v>
+        <v>593.28</v>
       </c>
       <c r="F305" t="n">
         <v>657.4299999999999</v>
@@ -40631,13 +40736,13 @@
         <v>294.23</v>
       </c>
       <c r="C306" t="n">
-        <v>379.84</v>
+        <v>452.5</v>
       </c>
       <c r="D306" t="n">
-        <v>674.0700000000001</v>
+        <v>746.72</v>
       </c>
       <c r="E306" t="n">
-        <v>542.58</v>
+        <v>593.62</v>
       </c>
       <c r="F306" t="n">
         <v>659.45</v>
@@ -40653,13 +40758,13 @@
         <v>293.45</v>
       </c>
       <c r="C307" t="n">
-        <v>382.15</v>
+        <v>453.89</v>
       </c>
       <c r="D307" t="n">
-        <v>675.6</v>
+        <v>747.35</v>
       </c>
       <c r="E307" t="n">
-        <v>544.01</v>
+        <v>594.84</v>
       </c>
       <c r="F307" t="n">
         <v>662.97</v>
@@ -40675,13 +40780,13 @@
         <v>292.68</v>
       </c>
       <c r="C308" t="n">
-        <v>386.5</v>
+        <v>455.29</v>
       </c>
       <c r="D308" t="n">
-        <v>679.1799999999999</v>
+        <v>747.97</v>
       </c>
       <c r="E308" t="n">
-        <v>545.28</v>
+        <v>595.95</v>
       </c>
       <c r="F308" t="n">
         <v>663.97</v>
@@ -40697,13 +40802,13 @@
         <v>291.9</v>
       </c>
       <c r="C309" t="n">
-        <v>389.32</v>
+        <v>456.69</v>
       </c>
       <c r="D309" t="n">
-        <v>681.22</v>
+        <v>748.59</v>
       </c>
       <c r="E309" t="n">
-        <v>545.87</v>
+        <v>596.55</v>
       </c>
       <c r="F309" t="n">
         <v>664.48</v>
@@ -40719,13 +40824,13 @@
         <v>291.13</v>
       </c>
       <c r="C310" t="n">
-        <v>390.86</v>
+        <v>458.08</v>
       </c>
       <c r="D310" t="n">
-        <v>681.99</v>
+        <v>749.21</v>
       </c>
       <c r="E310" t="n">
-        <v>546.03</v>
+        <v>596.83</v>
       </c>
       <c r="F310" t="n">
         <v>664.98</v>
@@ -40741,13 +40846,13 @@
         <v>290.35</v>
       </c>
       <c r="C311" t="n">
-        <v>392.41</v>
+        <v>459.48</v>
       </c>
       <c r="D311" t="n">
-        <v>682.76</v>
+        <v>749.84</v>
       </c>
       <c r="E311" t="n">
-        <v>546.53</v>
+        <v>597.36</v>
       </c>
       <c r="F311" t="n">
         <v>666.49</v>
@@ -40763,13 +40868,13 @@
         <v>289.58</v>
       </c>
       <c r="C312" t="n">
-        <v>394.2</v>
+        <v>460.88</v>
       </c>
       <c r="D312" t="n">
-        <v>683.78</v>
+        <v>750.46</v>
       </c>
       <c r="E312" t="n">
-        <v>546.78</v>
+        <v>597.7</v>
       </c>
       <c r="F312" t="n">
         <v>666.99</v>
@@ -40785,13 +40890,13 @@
         <v>288.81</v>
       </c>
       <c r="C313" t="n">
-        <v>394.97</v>
+        <v>462.27</v>
       </c>
       <c r="D313" t="n">
-        <v>683.78</v>
+        <v>751.08</v>
       </c>
       <c r="E313" t="n">
-        <v>546.86</v>
+        <v>597.92</v>
       </c>
       <c r="F313" t="n">
         <v>668</v>
@@ -40807,13 +40912,13 @@
         <v>288.03</v>
       </c>
       <c r="C314" t="n">
-        <v>395.24</v>
+        <v>463.67</v>
       </c>
       <c r="D314" t="n">
-        <v>683.27</v>
+        <v>751.7</v>
       </c>
       <c r="E314" t="n">
-        <v>546.77</v>
+        <v>598</v>
       </c>
       <c r="F314" t="n">
         <v>669</v>
@@ -40829,13 +40934,13 @@
         <v>287.26</v>
       </c>
       <c r="C315" t="n">
-        <v>394.99</v>
+        <v>465.07</v>
       </c>
       <c r="D315" t="n">
-        <v>682.25</v>
+        <v>752.33</v>
       </c>
       <c r="E315" t="n">
-        <v>546.17</v>
+        <v>597.71</v>
       </c>
       <c r="F315" t="n">
         <v>669</v>
@@ -40851,13 +40956,13 @@
         <v>286.48</v>
       </c>
       <c r="C316" t="n">
-        <v>394.74</v>
+        <v>466.46</v>
       </c>
       <c r="D316" t="n">
-        <v>681.22</v>
+        <v>752.95</v>
       </c>
       <c r="E316" t="n">
-        <v>545.5700000000001</v>
+        <v>597.41</v>
       </c>
       <c r="F316" t="n">
         <v>669</v>
@@ -40873,13 +40978,13 @@
         <v>285.71</v>
       </c>
       <c r="C317" t="n">
-        <v>395</v>
+        <v>467.86</v>
       </c>
       <c r="D317" t="n">
-        <v>680.71</v>
+        <v>753.5700000000001</v>
       </c>
       <c r="E317" t="n">
-        <v>545.3099999999999</v>
+        <v>597.38</v>
       </c>
       <c r="F317" t="n">
         <v>669.51</v>
@@ -40895,13 +41000,13 @@
         <v>284.94</v>
       </c>
       <c r="C318" t="n">
-        <v>395.26</v>
+        <v>469.26</v>
       </c>
       <c r="D318" t="n">
-        <v>680.2</v>
+        <v>754.1900000000001</v>
       </c>
       <c r="E318" t="n">
-        <v>545.05</v>
+        <v>597.33</v>
       </c>
       <c r="F318" t="n">
         <v>670.01</v>
@@ -40917,13 +41022,13 @@
         <v>284.16</v>
       </c>
       <c r="C319" t="n">
-        <v>396.55</v>
+        <v>470.65</v>
       </c>
       <c r="D319" t="n">
-        <v>680.71</v>
+        <v>754.8200000000001</v>
       </c>
       <c r="E319" t="n">
-        <v>545.13</v>
+        <v>597.55</v>
       </c>
       <c r="F319" t="n">
         <v>670.52</v>
@@ -40939,13 +41044,13 @@
         <v>283.39</v>
       </c>
       <c r="C320" t="n">
-        <v>397.83</v>
+        <v>472.05</v>
       </c>
       <c r="D320" t="n">
-        <v>681.22</v>
+        <v>755.4400000000001</v>
       </c>
       <c r="E320" t="n">
-        <v>545.88</v>
+        <v>598.27</v>
       </c>
       <c r="F320" t="n">
         <v>673.04</v>
@@ -40961,13 +41066,13 @@
         <v>282.61</v>
       </c>
       <c r="C321" t="n">
-        <v>399.12</v>
+        <v>473.45</v>
       </c>
       <c r="D321" t="n">
-        <v>681.73</v>
+        <v>756.0599999999999</v>
       </c>
       <c r="E321" t="n">
-        <v>546.13</v>
+        <v>598.61</v>
       </c>
       <c r="F321" t="n">
         <v>674.05</v>
@@ -40983,13 +41088,13 @@
         <v>281.84</v>
       </c>
       <c r="C322" t="n">
-        <v>400.41</v>
+        <v>474.85</v>
       </c>
       <c r="D322" t="n">
-        <v>682.25</v>
+        <v>756.6799999999999</v>
       </c>
       <c r="E322" t="n">
-        <v>546.05</v>
+        <v>598.71</v>
       </c>
       <c r="F322" t="n">
         <v>674.05</v>
@@ -41005,13 +41110,13 @@
         <v>281.06</v>
       </c>
       <c r="C323" t="n">
-        <v>401.7</v>
+        <v>476.24</v>
       </c>
       <c r="D323" t="n">
-        <v>682.76</v>
+        <v>757.3099999999999</v>
       </c>
       <c r="E323" t="n">
-        <v>546.12</v>
+        <v>598.92</v>
       </c>
       <c r="F323" t="n">
         <v>674.55</v>
@@ -41027,13 +41132,13 @@
         <v>280.29</v>
       </c>
       <c r="C324" t="n">
-        <v>402.98</v>
+        <v>477.64</v>
       </c>
       <c r="D324" t="n">
-        <v>683.27</v>
+        <v>757.9299999999999</v>
       </c>
       <c r="E324" t="n">
-        <v>546.04</v>
+        <v>599.01</v>
       </c>
       <c r="F324" t="n">
         <v>674.55</v>
@@ -41049,13 +41154,13 @@
         <v>279.52</v>
       </c>
       <c r="C325" t="n">
-        <v>404.26</v>
+        <v>479.04</v>
       </c>
       <c r="D325" t="n">
-        <v>683.78</v>
+        <v>758.55</v>
       </c>
       <c r="E325" t="n">
-        <v>546.12</v>
+        <v>599.23</v>
       </c>
       <c r="F325" t="n">
         <v>675.0599999999999</v>
@@ -41071,13 +41176,13 @@
         <v>278.74</v>
       </c>
       <c r="C326" t="n">
-        <v>404.02</v>
+        <v>480.43</v>
       </c>
       <c r="D326" t="n">
-        <v>682.76</v>
+        <v>759.17</v>
       </c>
       <c r="E326" t="n">
-        <v>545.52</v>
+        <v>598.9299999999999</v>
       </c>
       <c r="F326" t="n">
         <v>675.0599999999999</v>
@@ -41093,13 +41198,13 @@
         <v>277.97</v>
       </c>
       <c r="C327" t="n">
-        <v>403.76</v>
+        <v>481.83</v>
       </c>
       <c r="D327" t="n">
-        <v>681.73</v>
+        <v>759.8</v>
       </c>
       <c r="E327" t="n">
-        <v>545.09</v>
+        <v>598.76</v>
       </c>
       <c r="F327" t="n">
         <v>675.5599999999999</v>
@@ -41115,13 +41220,13 @@
         <v>277.19</v>
       </c>
       <c r="C328" t="n">
-        <v>405.06</v>
+        <v>483.23</v>
       </c>
       <c r="D328" t="n">
-        <v>682.25</v>
+        <v>760.42</v>
       </c>
       <c r="E328" t="n">
-        <v>545.17</v>
+        <v>598.98</v>
       </c>
       <c r="F328" t="n">
         <v>676.0700000000001</v>
@@ -41137,13 +41242,13 @@
         <v>276.42</v>
       </c>
       <c r="C329" t="n">
-        <v>404.8</v>
+        <v>484.62</v>
       </c>
       <c r="D329" t="n">
-        <v>681.22</v>
+        <v>761.04</v>
       </c>
       <c r="E329" t="n">
-        <v>544.5700000000001</v>
+        <v>598.6900000000001</v>
       </c>
       <c r="F329" t="n">
         <v>676.0700000000001</v>
@@ -41159,13 +41264,13 @@
         <v>275.65</v>
       </c>
       <c r="C330" t="n">
-        <v>405.06</v>
+        <v>486.02</v>
       </c>
       <c r="D330" t="n">
-        <v>680.71</v>
+        <v>761.66</v>
       </c>
       <c r="E330" t="n">
-        <v>544.98</v>
+        <v>599.15</v>
       </c>
       <c r="F330" t="n">
         <v>678.59</v>
@@ -41181,13 +41286,13 @@
         <v>274.87</v>
       </c>
       <c r="C331" t="n">
-        <v>409.28</v>
+        <v>487.42</v>
       </c>
       <c r="D331" t="n">
-        <v>684.15</v>
+        <v>762.29</v>
       </c>
       <c r="E331" t="n">
-        <v>546.24</v>
+        <v>600.25</v>
       </c>
       <c r="F331" t="n">
         <v>684.15</v>
@@ -41203,13 +41308,13 @@
         <v>274.1</v>
       </c>
       <c r="C332" t="n">
-        <v>411.06</v>
+        <v>488.81</v>
       </c>
       <c r="D332" t="n">
-        <v>685.16</v>
+        <v>762.91</v>
       </c>
       <c r="E332" t="n">
-        <v>545.98</v>
+        <v>600.21</v>
       </c>
       <c r="F332" t="n">
         <v>685.16</v>
@@ -41225,13 +41330,13 @@
         <v>273.32</v>
       </c>
       <c r="C333" t="n">
-        <v>412.34</v>
+        <v>490.21</v>
       </c>
       <c r="D333" t="n">
-        <v>685.66</v>
+        <v>763.53</v>
       </c>
       <c r="E333" t="n">
-        <v>545.54</v>
+        <v>600.04</v>
       </c>
       <c r="F333" t="n">
         <v>685.66</v>
@@ -41247,13 +41352,13 @@
         <v>272.55</v>
       </c>
       <c r="C334" t="n">
-        <v>414.12</v>
+        <v>491.61</v>
       </c>
       <c r="D334" t="n">
-        <v>686.67</v>
+        <v>764.15</v>
       </c>
       <c r="E334" t="n">
-        <v>545.45</v>
+        <v>600.13</v>
       </c>
       <c r="F334" t="n">
         <v>686.67</v>
@@ -41269,13 +41374,13 @@
         <v>271.77</v>
       </c>
       <c r="C335" t="n">
-        <v>415.4</v>
+        <v>493</v>
       </c>
       <c r="D335" t="n">
-        <v>687.17</v>
+        <v>764.78</v>
       </c>
       <c r="E335" t="n">
-        <v>545.02</v>
+        <v>599.96</v>
       </c>
       <c r="F335" t="n">
         <v>687.17</v>
@@ -41291,13 +41396,13 @@
         <v>271</v>
       </c>
       <c r="C336" t="n">
-        <v>416.17</v>
+        <v>494.4</v>
       </c>
       <c r="D336" t="n">
-        <v>687.17</v>
+        <v>765.4</v>
       </c>
       <c r="E336" t="n">
-        <v>544.42</v>
+        <v>599.66</v>
       </c>
       <c r="F336" t="n">
         <v>687.17</v>
@@ -41313,13 +41418,13 @@
         <v>271.4</v>
       </c>
       <c r="C337" t="n">
-        <v>416.28</v>
+        <v>494.55</v>
       </c>
       <c r="D337" t="n">
-        <v>687.6799999999999</v>
+        <v>765.95</v>
       </c>
       <c r="E337" t="n">
-        <v>544.38</v>
+        <v>599.78</v>
       </c>
       <c r="F337" t="n">
         <v>687.6799999999999</v>
@@ -41335,13 +41440,13 @@
         <v>271.8</v>
       </c>
       <c r="C338" t="n">
-        <v>416.89</v>
+        <v>494.71</v>
       </c>
       <c r="D338" t="n">
-        <v>688.6900000000001</v>
+        <v>766.51</v>
       </c>
       <c r="E338" t="n">
-        <v>544.51</v>
+        <v>600.01</v>
       </c>
       <c r="F338" t="n">
         <v>688.6900000000001</v>
@@ -41357,13 +41462,13 @@
         <v>272.2</v>
       </c>
       <c r="C339" t="n">
-        <v>417</v>
+        <v>494.86</v>
       </c>
       <c r="D339" t="n">
-        <v>689.2</v>
+        <v>767.0599999999999</v>
       </c>
       <c r="E339" t="n">
-        <v>544.64</v>
+        <v>600.25</v>
       </c>
       <c r="F339" t="n">
         <v>689.2</v>
@@ -41379,13 +41484,13 @@
         <v>272.6</v>
       </c>
       <c r="C340" t="n">
-        <v>416.6</v>
+        <v>495.01</v>
       </c>
       <c r="D340" t="n">
-        <v>689.2</v>
+        <v>767.61</v>
       </c>
       <c r="E340" t="n">
-        <v>544.78</v>
+        <v>600.49</v>
       </c>
       <c r="F340" t="n">
         <v>689.2</v>
@@ -41401,13 +41506,13 @@
         <v>273</v>
       </c>
       <c r="C341" t="n">
-        <v>416.7</v>
+        <v>495.17</v>
       </c>
       <c r="D341" t="n">
-        <v>689.7</v>
+        <v>768.17</v>
       </c>
       <c r="E341" t="n">
-        <v>545.25</v>
+        <v>600.98</v>
       </c>
       <c r="F341" t="n">
         <v>689.7</v>
@@ -41423,13 +41528,13 @@
         <v>273.4</v>
       </c>
       <c r="C342" t="n">
-        <v>416.81</v>
+        <v>495.32</v>
       </c>
       <c r="D342" t="n">
-        <v>690.21</v>
+        <v>768.72</v>
       </c>
       <c r="E342" t="n">
-        <v>545.72</v>
+        <v>601.47</v>
       </c>
       <c r="F342" t="n">
         <v>690.21</v>
@@ -41445,13 +41550,13 @@
         <v>273.8</v>
       </c>
       <c r="C343" t="n">
-        <v>416.41</v>
+        <v>495.47</v>
       </c>
       <c r="D343" t="n">
-        <v>690.21</v>
+        <v>769.27</v>
       </c>
       <c r="E343" t="n">
-        <v>545.51</v>
+        <v>601.45</v>
       </c>
       <c r="F343" t="n">
         <v>690.21</v>
@@ -41467,13 +41572,13 @@
         <v>274.2</v>
       </c>
       <c r="C344" t="n">
-        <v>416.51</v>
+        <v>495.63</v>
       </c>
       <c r="D344" t="n">
-        <v>690.71</v>
+        <v>769.83</v>
       </c>
       <c r="E344" t="n">
-        <v>545.99</v>
+        <v>601.95</v>
       </c>
       <c r="F344" t="n">
         <v>690.71</v>
@@ -41489,13 +41594,13 @@
         <v>274.6</v>
       </c>
       <c r="C345" t="n">
-        <v>416.11</v>
+        <v>495.78</v>
       </c>
       <c r="D345" t="n">
-        <v>690.71</v>
+        <v>770.38</v>
       </c>
       <c r="E345" t="n">
-        <v>546.29</v>
+        <v>602.3099999999999</v>
       </c>
       <c r="F345" t="n">
         <v>690.71</v>
@@ -41511,13 +41616,13 @@
         <v>275</v>
       </c>
       <c r="C346" t="n">
-        <v>416.22</v>
+        <v>495.93</v>
       </c>
       <c r="D346" t="n">
-        <v>691.22</v>
+        <v>770.9299999999999</v>
       </c>
       <c r="E346" t="n">
-        <v>546.76</v>
+        <v>602.8099999999999</v>
       </c>
       <c r="F346" t="n">
         <v>691.22</v>
@@ -41533,13 +41638,13 @@
         <v>275.4</v>
       </c>
       <c r="C347" t="n">
-        <v>416.83</v>
+        <v>496.09</v>
       </c>
       <c r="D347" t="n">
-        <v>692.23</v>
+        <v>771.49</v>
       </c>
       <c r="E347" t="n">
-        <v>547.66</v>
+        <v>603.62</v>
       </c>
       <c r="F347" t="n">
         <v>692.23</v>
@@ -41555,13 +41660,13 @@
         <v>275.8</v>
       </c>
       <c r="C348" t="n">
-        <v>416.94</v>
+        <v>496.24</v>
       </c>
       <c r="D348" t="n">
-        <v>692.74</v>
+        <v>772.04</v>
       </c>
       <c r="E348" t="n">
-        <v>548.22</v>
+        <v>604.17</v>
       </c>
       <c r="F348" t="n">
         <v>692.74</v>
@@ -41577,13 +41682,13 @@
         <v>276.2</v>
       </c>
       <c r="C349" t="n">
-        <v>416.54</v>
+        <v>496.39</v>
       </c>
       <c r="D349" t="n">
-        <v>692.74</v>
+        <v>772.59</v>
       </c>
       <c r="E349" t="n">
-        <v>548.52</v>
+        <v>604.54</v>
       </c>
       <c r="F349" t="n">
         <v>692.74</v>
@@ -41599,13 +41704,13 @@
         <v>276.6</v>
       </c>
       <c r="C350" t="n">
-        <v>416.14</v>
+        <v>496.55</v>
       </c>
       <c r="D350" t="n">
-        <v>692.74</v>
+        <v>773.15</v>
       </c>
       <c r="E350" t="n">
-        <v>548.83</v>
+        <v>604.91</v>
       </c>
       <c r="F350" t="n">
         <v>692.74</v>
@@ -41621,13 +41726,13 @@
         <v>277</v>
       </c>
       <c r="C351" t="n">
-        <v>416.24</v>
+        <v>496.7</v>
       </c>
       <c r="D351" t="n">
-        <v>693.24</v>
+        <v>773.7</v>
       </c>
       <c r="E351" t="n">
-        <v>549.13</v>
+        <v>605.27</v>
       </c>
       <c r="F351" t="n">
         <v>693.24</v>
@@ -41643,13 +41748,13 @@
         <v>277.4</v>
       </c>
       <c r="C352" t="n">
-        <v>416.35</v>
+        <v>496.85</v>
       </c>
       <c r="D352" t="n">
-        <v>693.75</v>
+        <v>774.25</v>
       </c>
       <c r="E352" t="n">
-        <v>549.6</v>
+        <v>605.76</v>
       </c>
       <c r="F352" t="n">
         <v>693.75</v>
@@ -41665,13 +41770,13 @@
         <v>277.8</v>
       </c>
       <c r="C353" t="n">
-        <v>415.95</v>
+        <v>497.01</v>
       </c>
       <c r="D353" t="n">
-        <v>693.75</v>
+        <v>774.8099999999999</v>
       </c>
       <c r="E353" t="n">
-        <v>549.9</v>
+        <v>606.13</v>
       </c>
       <c r="F353" t="n">
         <v>693.75</v>
@@ -41687,13 +41792,13 @@
         <v>278.2</v>
       </c>
       <c r="C354" t="n">
-        <v>416.06</v>
+        <v>497.16</v>
       </c>
       <c r="D354" t="n">
-        <v>694.26</v>
+        <v>775.36</v>
       </c>
       <c r="E354" t="n">
-        <v>550.38</v>
+        <v>606.62</v>
       </c>
       <c r="F354" t="n">
         <v>694.26</v>
@@ -41709,13 +41814,13 @@
         <v>278.6</v>
       </c>
       <c r="C355" t="n">
-        <v>415.66</v>
+        <v>497.31</v>
       </c>
       <c r="D355" t="n">
-        <v>694.26</v>
+        <v>775.91</v>
       </c>
       <c r="E355" t="n">
-        <v>550.6799999999999</v>
+        <v>606.99</v>
       </c>
       <c r="F355" t="n">
         <v>694.26</v>
@@ -41731,13 +41836,13 @@
         <v>279</v>
       </c>
       <c r="C356" t="n">
-        <v>417.79</v>
+        <v>497.47</v>
       </c>
       <c r="D356" t="n">
-        <v>696.79</v>
+        <v>776.47</v>
       </c>
       <c r="E356" t="n">
-        <v>552.17</v>
+        <v>608.24</v>
       </c>
       <c r="F356" t="n">
         <v>696.79</v>
@@ -41753,13 +41858,13 @@
         <v>279.4</v>
       </c>
       <c r="C357" t="n">
-        <v>418.9</v>
+        <v>497.62</v>
       </c>
       <c r="D357" t="n">
-        <v>698.3</v>
+        <v>777.02</v>
       </c>
       <c r="E357" t="n">
-        <v>553.3200000000001</v>
+        <v>609.24</v>
       </c>
       <c r="F357" t="n">
         <v>698.3</v>
@@ -41775,13 +41880,13 @@
         <v>279.8</v>
       </c>
       <c r="C358" t="n">
-        <v>418.5</v>
+        <v>497.77</v>
       </c>
       <c r="D358" t="n">
-        <v>698.3</v>
+        <v>777.5700000000001</v>
       </c>
       <c r="E358" t="n">
-        <v>553.62</v>
+        <v>609.61</v>
       </c>
       <c r="F358" t="n">
         <v>698.3</v>
@@ -41797,13 +41902,13 @@
         <v>280.2</v>
       </c>
       <c r="C359" t="n">
-        <v>418.61</v>
+        <v>497.93</v>
       </c>
       <c r="D359" t="n">
-        <v>698.8099999999999</v>
+        <v>778.13</v>
       </c>
       <c r="E359" t="n">
-        <v>554.4299999999999</v>
+        <v>610.36</v>
       </c>
       <c r="F359" t="n">
         <v>698.8099999999999</v>
@@ -41819,13 +41924,13 @@
         <v>280.6</v>
       </c>
       <c r="C360" t="n">
-        <v>420.24</v>
+        <v>498.08</v>
       </c>
       <c r="D360" t="n">
-        <v>700.84</v>
+        <v>778.6799999999999</v>
       </c>
       <c r="E360" t="n">
-        <v>555.41</v>
+        <v>611.23</v>
       </c>
       <c r="F360" t="n">
         <v>700.84</v>
@@ -41841,13 +41946,13 @@
         <v>281</v>
       </c>
       <c r="C361" t="n">
-        <v>421.36</v>
+        <v>498.23</v>
       </c>
       <c r="D361" t="n">
-        <v>702.36</v>
+        <v>779.23</v>
       </c>
       <c r="E361" t="n">
-        <v>556.22</v>
+        <v>611.98</v>
       </c>
       <c r="F361" t="n">
         <v>702.36</v>
@@ -41863,13 +41968,13 @@
         <v>281.4</v>
       </c>
       <c r="C362" t="n">
-        <v>421.97</v>
+        <v>498.39</v>
       </c>
       <c r="D362" t="n">
-        <v>703.37</v>
+        <v>779.79</v>
       </c>
       <c r="E362" t="n">
-        <v>556.86</v>
+        <v>612.59</v>
       </c>
       <c r="F362" t="n">
         <v>703.37</v>
@@ -41885,13 +41990,13 @@
         <v>281.8</v>
       </c>
       <c r="C363" t="n">
-        <v>422.08</v>
+        <v>498.54</v>
       </c>
       <c r="D363" t="n">
-        <v>703.88</v>
+        <v>780.34</v>
       </c>
       <c r="E363" t="n">
-        <v>557.34</v>
+        <v>613.09</v>
       </c>
       <c r="F363" t="n">
         <v>703.88</v>
@@ -41907,13 +42012,13 @@
         <v>282.2</v>
       </c>
       <c r="C364" t="n">
-        <v>422.19</v>
+        <v>498.69</v>
       </c>
       <c r="D364" t="n">
-        <v>704.39</v>
+        <v>780.89</v>
       </c>
       <c r="E364" t="n">
-        <v>557.64</v>
+        <v>613.45</v>
       </c>
       <c r="F364" t="n">
         <v>704.39</v>
@@ -41929,13 +42034,13 @@
         <v>282.6</v>
       </c>
       <c r="C365" t="n">
-        <v>422.8</v>
+        <v>498.85</v>
       </c>
       <c r="D365" t="n">
-        <v>705.4</v>
+        <v>781.45</v>
       </c>
       <c r="E365" t="n">
-        <v>558.28</v>
+        <v>614.0700000000001</v>
       </c>
       <c r="F365" t="n">
         <v>705.4</v>
@@ -41951,13 +42056,13 @@
         <v>283</v>
       </c>
       <c r="C366" t="n">
-        <v>423.16</v>
+        <v>499</v>
       </c>
       <c r="D366" t="n">
-        <v>706.16</v>
+        <v>782</v>
       </c>
       <c r="E366" t="n">
-        <v>558.84</v>
+        <v>614.63</v>
       </c>
       <c r="F366" t="n">
         <v>706.16</v>
@@ -46685,7 +46790,7 @@
         <v>512</v>
       </c>
       <c r="E213" t="n">
-        <v>455.23</v>
+        <v>453.69</v>
       </c>
       <c r="F213" t="n">
         <v>427.63</v>
@@ -63182,7 +63287,7 @@
         <v>124.15</v>
       </c>
       <c r="J337" t="n">
-        <v>4576</v>
+        <v>4575.2</v>
       </c>
       <c r="K337" t="n">
         <v>43.84</v>
@@ -63219,10 +63324,10 @@
         <v>123.25</v>
       </c>
       <c r="J338" t="n">
-        <v>4570.3</v>
+        <v>4568.8</v>
       </c>
       <c r="K338" t="n">
-        <v>43.79</v>
+        <v>43.78</v>
       </c>
       <c r="L338" t="inlineStr">
         <is>
@@ -63256,10 +63361,10 @@
         <v>122.27</v>
       </c>
       <c r="J339" t="n">
-        <v>4556.3</v>
+        <v>4554</v>
       </c>
       <c r="K339" t="n">
-        <v>43.66</v>
+        <v>43.63</v>
       </c>
       <c r="L339" t="inlineStr">
         <is>
@@ -63293,10 +63398,10 @@
         <v>120.93</v>
       </c>
       <c r="J340" t="n">
-        <v>4536.1</v>
+        <v>4533.1</v>
       </c>
       <c r="K340" t="n">
-        <v>43.46</v>
+        <v>43.43</v>
       </c>
       <c r="L340" t="inlineStr">
         <is>
@@ -63330,10 +63435,10 @@
         <v>119.52</v>
       </c>
       <c r="J341" t="n">
-        <v>4515.6</v>
+        <v>4511.8</v>
       </c>
       <c r="K341" t="n">
-        <v>43.27</v>
+        <v>43.23</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
@@ -63367,10 +63472,10 @@
         <v>118.26</v>
       </c>
       <c r="J342" t="n">
-        <v>4508</v>
+        <v>4503.5</v>
       </c>
       <c r="K342" t="n">
-        <v>43.19</v>
+        <v>43.15</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
@@ -63401,10 +63506,10 @@
         <v>116.99</v>
       </c>
       <c r="J343" t="n">
-        <v>4510.5</v>
+        <v>4505.2</v>
       </c>
       <c r="K343" t="n">
-        <v>43.22</v>
+        <v>43.17</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
@@ -63438,10 +63543,10 @@
         <v>115.77</v>
       </c>
       <c r="J344" t="n">
-        <v>4503.8</v>
+        <v>4497.7</v>
       </c>
       <c r="K344" t="n">
-        <v>43.15</v>
+        <v>43.09</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
@@ -63475,10 +63580,10 @@
         <v>115.12</v>
       </c>
       <c r="J345" t="n">
-        <v>4496</v>
+        <v>4489.2</v>
       </c>
       <c r="K345" t="n">
-        <v>43.08</v>
+        <v>43.01</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
@@ -63512,10 +63617,10 @@
         <v>113.84</v>
       </c>
       <c r="J346" t="n">
-        <v>4482.4</v>
+        <v>4474.8</v>
       </c>
       <c r="K346" t="n">
-        <v>42.95</v>
+        <v>42.87</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
@@ -63548,6 +63653,12 @@
       <c r="I347" t="n">
         <v>112.88</v>
       </c>
+      <c r="J347" t="n">
+        <v>4460.4</v>
+      </c>
+      <c r="K347" t="n">
+        <v>42.74</v>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63579,6 +63690,12 @@
       <c r="I348" t="n">
         <v>111.91</v>
       </c>
+      <c r="J348" t="n">
+        <v>4450.7</v>
+      </c>
+      <c r="K348" t="n">
+        <v>42.64</v>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63610,6 +63727,12 @@
       <c r="I349" t="n">
         <v>110.84</v>
       </c>
+      <c r="J349" t="n">
+        <v>4431.6</v>
+      </c>
+      <c r="K349" t="n">
+        <v>42.46</v>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63623,6 +63746,9 @@
       <c r="B350" t="n">
         <v>839.0700000000001</v>
       </c>
+      <c r="C350" t="n">
+        <v>438.9</v>
+      </c>
       <c r="D350" t="n">
         <v>535.8200000000001</v>
       </c>
@@ -63632,15 +63758,24 @@
       <c r="F350" t="n">
         <v>1761.08</v>
       </c>
+      <c r="G350" t="n">
+        <v>759.1</v>
+      </c>
       <c r="H350" t="n">
         <v>67.48</v>
       </c>
       <c r="I350" t="n">
         <v>109.66</v>
       </c>
+      <c r="J350" t="n">
+        <v>4404.5</v>
+      </c>
+      <c r="K350" t="n">
+        <v>42.2</v>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: Rapel; LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -63669,6 +63804,12 @@
       <c r="I351" t="n">
         <v>108.51</v>
       </c>
+      <c r="J351" t="n">
+        <v>4394.6</v>
+      </c>
+      <c r="K351" t="n">
+        <v>42.11</v>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63700,6 +63841,12 @@
       <c r="I352" t="n">
         <v>107.51</v>
       </c>
+      <c r="J352" t="n">
+        <v>4374.4</v>
+      </c>
+      <c r="K352" t="n">
+        <v>41.91</v>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63731,6 +63878,12 @@
       <c r="I353" t="n">
         <v>106.49</v>
       </c>
+      <c r="J353" t="n">
+        <v>4348.9</v>
+      </c>
+      <c r="K353" t="n">
+        <v>41.67</v>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63762,6 +63915,12 @@
       <c r="I354" t="n">
         <v>105.4</v>
       </c>
+      <c r="J354" t="n">
+        <v>4330</v>
+      </c>
+      <c r="K354" t="n">
+        <v>41.49</v>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63793,6 +63952,12 @@
       <c r="I355" t="n">
         <v>104.42</v>
       </c>
+      <c r="J355" t="n">
+        <v>4306.5</v>
+      </c>
+      <c r="K355" t="n">
+        <v>41.26</v>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63824,6 +63989,12 @@
       <c r="I356" t="n">
         <v>103.39</v>
       </c>
+      <c r="J356" t="n">
+        <v>4287.3</v>
+      </c>
+      <c r="K356" t="n">
+        <v>41.08</v>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63855,6 +64026,12 @@
       <c r="I357" t="n">
         <v>102.42</v>
       </c>
+      <c r="J357" t="n">
+        <v>4267.8</v>
+      </c>
+      <c r="K357" t="n">
+        <v>40.89</v>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63883,6 +64060,12 @@
       <c r="I358" t="n">
         <v>101.44</v>
       </c>
+      <c r="J358" t="n">
+        <v>4256.3</v>
+      </c>
+      <c r="K358" t="n">
+        <v>40.78</v>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63914,6 +64097,12 @@
       <c r="I359" t="n">
         <v>100.26</v>
       </c>
+      <c r="J359" t="n">
+        <v>4245</v>
+      </c>
+      <c r="K359" t="n">
+        <v>40.67</v>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63945,6 +64134,12 @@
       <c r="I360" t="n">
         <v>99.2</v>
       </c>
+      <c r="J360" t="n">
+        <v>4240.5</v>
+      </c>
+      <c r="K360" t="n">
+        <v>40.63</v>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -63976,6 +64171,12 @@
       <c r="I361" t="n">
         <v>98.56999999999999</v>
       </c>
+      <c r="J361" t="n">
+        <v>4235.3</v>
+      </c>
+      <c r="K361" t="n">
+        <v>40.58</v>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64007,6 +64208,12 @@
       <c r="I362" t="n">
         <v>97.42</v>
       </c>
+      <c r="J362" t="n">
+        <v>4218</v>
+      </c>
+      <c r="K362" t="n">
+        <v>40.41</v>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64038,6 +64245,12 @@
       <c r="I363" t="n">
         <v>96.39</v>
       </c>
+      <c r="J363" t="n">
+        <v>4202.7</v>
+      </c>
+      <c r="K363" t="n">
+        <v>40.27</v>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64069,6 +64282,12 @@
       <c r="I364" t="n">
         <v>95.08</v>
       </c>
+      <c r="J364" t="n">
+        <v>4189.2</v>
+      </c>
+      <c r="K364" t="n">
+        <v>40.14</v>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64100,6 +64319,12 @@
       <c r="I365" t="n">
         <v>94.09999999999999</v>
       </c>
+      <c r="J365" t="n">
+        <v>4172.5</v>
+      </c>
+      <c r="K365" t="n">
+        <v>39.98</v>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64131,6 +64356,12 @@
       <c r="I366" t="n">
         <v>93.13</v>
       </c>
+      <c r="J366" t="n">
+        <v>4152.2</v>
+      </c>
+      <c r="K366" t="n">
+        <v>39.78</v>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64162,6 +64393,12 @@
       <c r="I367" t="n">
         <v>92.40000000000001</v>
       </c>
+      <c r="J367" t="n">
+        <v>4150.3</v>
+      </c>
+      <c r="K367" t="n">
+        <v>39.77</v>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64190,6 +64427,12 @@
       <c r="I368" t="n">
         <v>91.64</v>
       </c>
+      <c r="J368" t="n">
+        <v>4139.6</v>
+      </c>
+      <c r="K368" t="n">
+        <v>39.66</v>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64221,6 +64464,12 @@
       <c r="I369" t="n">
         <v>90.95</v>
       </c>
+      <c r="J369" t="n">
+        <v>4126.7</v>
+      </c>
+      <c r="K369" t="n">
+        <v>39.54</v>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64252,6 +64501,12 @@
       <c r="I370" t="n">
         <v>90.14</v>
       </c>
+      <c r="J370" t="n">
+        <v>4122.8</v>
+      </c>
+      <c r="K370" t="n">
+        <v>39.5</v>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64283,6 +64538,12 @@
       <c r="I371" t="n">
         <v>89.23</v>
       </c>
+      <c r="J371" t="n">
+        <v>4116.6</v>
+      </c>
+      <c r="K371" t="n">
+        <v>39.44</v>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64314,6 +64575,12 @@
       <c r="I372" t="n">
         <v>88.56</v>
       </c>
+      <c r="J372" t="n">
+        <v>4111.4</v>
+      </c>
+      <c r="K372" t="n">
+        <v>39.39</v>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64345,6 +64612,12 @@
       <c r="I373" t="n">
         <v>87.42</v>
       </c>
+      <c r="J373" t="n">
+        <v>4087.6</v>
+      </c>
+      <c r="K373" t="n">
+        <v>39.16</v>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64376,6 +64649,12 @@
       <c r="I374" t="n">
         <v>86.25</v>
       </c>
+      <c r="J374" t="n">
+        <v>4074.7</v>
+      </c>
+      <c r="K374" t="n">
+        <v>39.04</v>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64407,6 +64686,12 @@
       <c r="I375" t="n">
         <v>85.26000000000001</v>
       </c>
+      <c r="J375" t="n">
+        <v>4062.2</v>
+      </c>
+      <c r="K375" t="n">
+        <v>38.92</v>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64438,6 +64723,12 @@
       <c r="I376" t="n">
         <v>85.12</v>
       </c>
+      <c r="J376" t="n">
+        <v>4070.7</v>
+      </c>
+      <c r="K376" t="n">
+        <v>39</v>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64469,6 +64760,12 @@
       <c r="I377" t="n">
         <v>84.28</v>
       </c>
+      <c r="J377" t="n">
+        <v>4073.9</v>
+      </c>
+      <c r="K377" t="n">
+        <v>39.03</v>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64500,6 +64797,12 @@
       <c r="I378" t="n">
         <v>83.13</v>
       </c>
+      <c r="J378" t="n">
+        <v>4070.4</v>
+      </c>
+      <c r="K378" t="n">
+        <v>39</v>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64531,6 +64834,12 @@
       <c r="I379" t="n">
         <v>82.29000000000001</v>
       </c>
+      <c r="J379" t="n">
+        <v>4064.4</v>
+      </c>
+      <c r="K379" t="n">
+        <v>38.94</v>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64562,6 +64871,12 @@
       <c r="I380" t="n">
         <v>81.23999999999999</v>
       </c>
+      <c r="J380" t="n">
+        <v>4049.3</v>
+      </c>
+      <c r="K380" t="n">
+        <v>38.8</v>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64587,15 +64902,24 @@
       <c r="F381" t="n">
         <v>1605.46</v>
       </c>
+      <c r="G381" t="n">
+        <v>743.1</v>
+      </c>
       <c r="H381" t="n">
         <v>72.75</v>
       </c>
       <c r="I381" t="n">
         <v>80.69</v>
       </c>
+      <c r="J381" t="n">
+        <v>4046.1</v>
+      </c>
+      <c r="K381" t="n">
+        <v>38.77</v>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -64624,6 +64948,12 @@
       <c r="I382" t="n">
         <v>80.27</v>
       </c>
+      <c r="J382" t="n">
+        <v>4044.6</v>
+      </c>
+      <c r="K382" t="n">
+        <v>38.75</v>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64655,6 +64985,12 @@
       <c r="I383" t="n">
         <v>79.3</v>
       </c>
+      <c r="J383" t="n">
+        <v>4017.7</v>
+      </c>
+      <c r="K383" t="n">
+        <v>38.49</v>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64686,6 +65022,12 @@
       <c r="I384" t="n">
         <v>78.09</v>
       </c>
+      <c r="J384" t="n">
+        <v>4002.8</v>
+      </c>
+      <c r="K384" t="n">
+        <v>38.35</v>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64717,6 +65059,12 @@
       <c r="I385" t="n">
         <v>77.39</v>
       </c>
+      <c r="J385" t="n">
+        <v>3976.7</v>
+      </c>
+      <c r="K385" t="n">
+        <v>38.1</v>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64748,6 +65096,12 @@
       <c r="I386" t="n">
         <v>76.67</v>
       </c>
+      <c r="J386" t="n">
+        <v>3970.5</v>
+      </c>
+      <c r="K386" t="n">
+        <v>38.04</v>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64779,6 +65133,12 @@
       <c r="I387" t="n">
         <v>75.95999999999999</v>
       </c>
+      <c r="J387" t="n">
+        <v>3947.9</v>
+      </c>
+      <c r="K387" t="n">
+        <v>37.83</v>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64810,6 +65170,12 @@
       <c r="I388" t="n">
         <v>75.34999999999999</v>
       </c>
+      <c r="J388" t="n">
+        <v>3925.4</v>
+      </c>
+      <c r="K388" t="n">
+        <v>37.61</v>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64841,6 +65207,12 @@
       <c r="I389" t="n">
         <v>74.72</v>
       </c>
+      <c r="J389" t="n">
+        <v>3915.5</v>
+      </c>
+      <c r="K389" t="n">
+        <v>37.52</v>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64872,6 +65244,12 @@
       <c r="I390" t="n">
         <v>73.86</v>
       </c>
+      <c r="J390" t="n">
+        <v>3889.4</v>
+      </c>
+      <c r="K390" t="n">
+        <v>37.27</v>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64903,6 +65281,12 @@
       <c r="I391" t="n">
         <v>73.04000000000001</v>
       </c>
+      <c r="J391" t="n">
+        <v>3864.6</v>
+      </c>
+      <c r="K391" t="n">
+        <v>37.03</v>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64934,6 +65318,12 @@
       <c r="I392" t="n">
         <v>72.18000000000001</v>
       </c>
+      <c r="J392" t="n">
+        <v>3850.9</v>
+      </c>
+      <c r="K392" t="n">
+        <v>36.9</v>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64965,6 +65355,12 @@
       <c r="I393" t="n">
         <v>71.67</v>
       </c>
+      <c r="J393" t="n">
+        <v>3844.8</v>
+      </c>
+      <c r="K393" t="n">
+        <v>36.84</v>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -64996,6 +65392,12 @@
       <c r="I394" t="n">
         <v>70.90000000000001</v>
       </c>
+      <c r="J394" t="n">
+        <v>3823.1</v>
+      </c>
+      <c r="K394" t="n">
+        <v>36.63</v>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65027,6 +65429,12 @@
       <c r="I395" t="n">
         <v>70.16</v>
       </c>
+      <c r="J395" t="n">
+        <v>3807.7</v>
+      </c>
+      <c r="K395" t="n">
+        <v>36.48</v>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65058,6 +65466,12 @@
       <c r="I396" t="n">
         <v>69.84</v>
       </c>
+      <c r="J396" t="n">
+        <v>3812.3</v>
+      </c>
+      <c r="K396" t="n">
+        <v>36.53</v>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65089,6 +65503,12 @@
       <c r="I397" t="n">
         <v>69.37</v>
       </c>
+      <c r="J397" t="n">
+        <v>3808.8</v>
+      </c>
+      <c r="K397" t="n">
+        <v>36.49</v>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65120,6 +65540,12 @@
       <c r="I398" t="n">
         <v>68.64</v>
       </c>
+      <c r="J398" t="n">
+        <v>3793.2</v>
+      </c>
+      <c r="K398" t="n">
+        <v>36.34</v>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65151,6 +65577,12 @@
       <c r="I399" t="n">
         <v>67.93000000000001</v>
       </c>
+      <c r="J399" t="n">
+        <v>3790.2</v>
+      </c>
+      <c r="K399" t="n">
+        <v>36.32</v>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65182,6 +65614,12 @@
       <c r="I400" t="n">
         <v>66.73999999999999</v>
       </c>
+      <c r="J400" t="n">
+        <v>3786.5</v>
+      </c>
+      <c r="K400" t="n">
+        <v>36.28</v>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65213,6 +65651,12 @@
       <c r="I401" t="n">
         <v>65.95</v>
       </c>
+      <c r="J401" t="n">
+        <v>3770.3</v>
+      </c>
+      <c r="K401" t="n">
+        <v>36.12</v>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65244,6 +65688,12 @@
       <c r="I402" t="n">
         <v>65.20999999999999</v>
       </c>
+      <c r="J402" t="n">
+        <v>3751.7</v>
+      </c>
+      <c r="K402" t="n">
+        <v>35.95</v>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65275,6 +65725,12 @@
       <c r="I403" t="n">
         <v>64.66</v>
       </c>
+      <c r="J403" t="n">
+        <v>3764.2</v>
+      </c>
+      <c r="K403" t="n">
+        <v>36.07</v>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65306,6 +65762,12 @@
       <c r="I404" t="n">
         <v>64.14</v>
       </c>
+      <c r="J404" t="n">
+        <v>3763.2</v>
+      </c>
+      <c r="K404" t="n">
+        <v>36.06</v>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65337,6 +65799,12 @@
       <c r="I405" t="n">
         <v>63.13</v>
       </c>
+      <c r="J405" t="n">
+        <v>3747.8</v>
+      </c>
+      <c r="K405" t="n">
+        <v>35.91</v>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65368,6 +65836,12 @@
       <c r="I406" t="n">
         <v>62.12</v>
       </c>
+      <c r="J406" t="n">
+        <v>3722.2</v>
+      </c>
+      <c r="K406" t="n">
+        <v>35.66</v>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65399,6 +65873,12 @@
       <c r="I407" t="n">
         <v>60.77</v>
       </c>
+      <c r="J407" t="n">
+        <v>3707.8</v>
+      </c>
+      <c r="K407" t="n">
+        <v>35.53</v>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65430,6 +65910,12 @@
       <c r="I408" t="n">
         <v>59.69</v>
       </c>
+      <c r="J408" t="n">
+        <v>3700.1</v>
+      </c>
+      <c r="K408" t="n">
+        <v>35.45</v>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65461,6 +65947,12 @@
       <c r="I409" t="n">
         <v>58.8</v>
       </c>
+      <c r="J409" t="n">
+        <v>3682.5</v>
+      </c>
+      <c r="K409" t="n">
+        <v>35.28</v>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65492,6 +65984,12 @@
       <c r="I410" t="n">
         <v>58.52</v>
       </c>
+      <c r="J410" t="n">
+        <v>3683.6</v>
+      </c>
+      <c r="K410" t="n">
+        <v>35.29</v>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65517,15 +66015,24 @@
       <c r="F411" t="n">
         <v>1451.14</v>
       </c>
+      <c r="G411" t="n">
+        <v>731.1</v>
+      </c>
       <c r="H411" t="n">
         <v>71.27</v>
       </c>
       <c r="I411" t="n">
         <v>58.21</v>
       </c>
+      <c r="J411" t="n">
+        <v>3689.6</v>
+      </c>
+      <c r="K411" t="n">
+        <v>35.35</v>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -65554,6 +66061,12 @@
       <c r="I412" t="n">
         <v>57.38</v>
       </c>
+      <c r="J412" t="n">
+        <v>3651.3</v>
+      </c>
+      <c r="K412" t="n">
+        <v>34.98</v>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65585,6 +66098,12 @@
       <c r="I413" t="n">
         <v>56.52</v>
       </c>
+      <c r="J413" t="n">
+        <v>3643.7</v>
+      </c>
+      <c r="K413" t="n">
+        <v>34.91</v>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65616,6 +66135,12 @@
       <c r="I414" t="n">
         <v>55.9</v>
       </c>
+      <c r="J414" t="n">
+        <v>3634.3</v>
+      </c>
+      <c r="K414" t="n">
+        <v>34.82</v>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65647,6 +66172,12 @@
       <c r="I415" t="n">
         <v>55.27</v>
       </c>
+      <c r="J415" t="n">
+        <v>3630.5</v>
+      </c>
+      <c r="K415" t="n">
+        <v>34.78</v>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65678,6 +66209,12 @@
       <c r="I416" t="n">
         <v>54.67</v>
       </c>
+      <c r="J416" t="n">
+        <v>3633</v>
+      </c>
+      <c r="K416" t="n">
+        <v>34.81</v>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65709,6 +66246,12 @@
       <c r="I417" t="n">
         <v>54.24</v>
       </c>
+      <c r="J417" t="n">
+        <v>3646.6</v>
+      </c>
+      <c r="K417" t="n">
+        <v>34.94</v>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65740,6 +66283,12 @@
       <c r="I418" t="n">
         <v>54.24</v>
       </c>
+      <c r="J418" t="n">
+        <v>3664.5</v>
+      </c>
+      <c r="K418" t="n">
+        <v>35.11</v>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65771,6 +66320,12 @@
       <c r="I419" t="n">
         <v>53.57</v>
       </c>
+      <c r="J419" t="n">
+        <v>3672.7</v>
+      </c>
+      <c r="K419" t="n">
+        <v>35.19</v>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65802,6 +66357,12 @@
       <c r="I420" t="n">
         <v>52.67</v>
       </c>
+      <c r="J420" t="n">
+        <v>3675</v>
+      </c>
+      <c r="K420" t="n">
+        <v>35.21</v>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65833,6 +66394,12 @@
       <c r="I421" t="n">
         <v>51.49</v>
       </c>
+      <c r="J421" t="n">
+        <v>3679.7</v>
+      </c>
+      <c r="K421" t="n">
+        <v>35.26</v>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65864,6 +66431,12 @@
       <c r="I422" t="n">
         <v>51.17</v>
       </c>
+      <c r="J422" t="n">
+        <v>3687.7</v>
+      </c>
+      <c r="K422" t="n">
+        <v>35.33</v>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65895,6 +66468,12 @@
       <c r="I423" t="n">
         <v>50.93</v>
       </c>
+      <c r="J423" t="n">
+        <v>3698.4</v>
+      </c>
+      <c r="K423" t="n">
+        <v>35.44</v>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65926,6 +66505,12 @@
       <c r="I424" t="n">
         <v>50.2</v>
       </c>
+      <c r="J424" t="n">
+        <v>3690.8</v>
+      </c>
+      <c r="K424" t="n">
+        <v>35.36</v>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65957,6 +66542,12 @@
       <c r="I425" t="n">
         <v>48.97</v>
       </c>
+      <c r="J425" t="n">
+        <v>3671.1</v>
+      </c>
+      <c r="K425" t="n">
+        <v>35.17</v>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -65988,6 +66579,12 @@
       <c r="I426" t="n">
         <v>47.55</v>
       </c>
+      <c r="J426" t="n">
+        <v>3606.1</v>
+      </c>
+      <c r="K426" t="n">
+        <v>34.55</v>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66019,6 +66616,12 @@
       <c r="I427" t="n">
         <v>46.54</v>
       </c>
+      <c r="J427" t="n">
+        <v>3605.7</v>
+      </c>
+      <c r="K427" t="n">
+        <v>34.55</v>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66050,6 +66653,12 @@
       <c r="I428" t="n">
         <v>45.45</v>
       </c>
+      <c r="J428" t="n">
+        <v>3609.3</v>
+      </c>
+      <c r="K428" t="n">
+        <v>34.58</v>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66081,6 +66690,12 @@
       <c r="I429" t="n">
         <v>44.17</v>
       </c>
+      <c r="J429" t="n">
+        <v>3611.1</v>
+      </c>
+      <c r="K429" t="n">
+        <v>34.6</v>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66112,6 +66727,12 @@
       <c r="I430" t="n">
         <v>42.84</v>
       </c>
+      <c r="J430" t="n">
+        <v>3604.1</v>
+      </c>
+      <c r="K430" t="n">
+        <v>34.53</v>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66143,6 +66764,12 @@
       <c r="I431" t="n">
         <v>41.88</v>
       </c>
+      <c r="J431" t="n">
+        <v>3603.7</v>
+      </c>
+      <c r="K431" t="n">
+        <v>34.53</v>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66174,6 +66801,12 @@
       <c r="I432" t="n">
         <v>40.66</v>
       </c>
+      <c r="J432" t="n">
+        <v>3594.8</v>
+      </c>
+      <c r="K432" t="n">
+        <v>34.44</v>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66205,6 +66838,12 @@
       <c r="I433" t="n">
         <v>39.27</v>
       </c>
+      <c r="J433" t="n">
+        <v>3595.8</v>
+      </c>
+      <c r="K433" t="n">
+        <v>34.45</v>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66236,6 +66875,12 @@
       <c r="I434" t="n">
         <v>38.01</v>
       </c>
+      <c r="J434" t="n">
+        <v>3592.5</v>
+      </c>
+      <c r="K434" t="n">
+        <v>34.42</v>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66267,6 +66912,12 @@
       <c r="I435" t="n">
         <v>36.66</v>
       </c>
+      <c r="J435" t="n">
+        <v>3590.3</v>
+      </c>
+      <c r="K435" t="n">
+        <v>34.4</v>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66298,6 +66949,12 @@
       <c r="I436" t="n">
         <v>35.51</v>
       </c>
+      <c r="J436" t="n">
+        <v>3600.5</v>
+      </c>
+      <c r="K436" t="n">
+        <v>34.5</v>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66329,6 +66986,12 @@
       <c r="I437" t="n">
         <v>34.57</v>
       </c>
+      <c r="J437" t="n">
+        <v>3595.8</v>
+      </c>
+      <c r="K437" t="n">
+        <v>34.45</v>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66360,6 +67023,12 @@
       <c r="I438" t="n">
         <v>34.25</v>
       </c>
+      <c r="J438" t="n">
+        <v>3594.7</v>
+      </c>
+      <c r="K438" t="n">
+        <v>34.44</v>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66391,6 +67060,12 @@
       <c r="I439" t="n">
         <v>34.57</v>
       </c>
+      <c r="J439" t="n">
+        <v>3596.3</v>
+      </c>
+      <c r="K439" t="n">
+        <v>34.46</v>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66422,6 +67097,12 @@
       <c r="I440" t="n">
         <v>34.57</v>
       </c>
+      <c r="J440" t="n">
+        <v>3598.3</v>
+      </c>
+      <c r="K440" t="n">
+        <v>34.48</v>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66453,6 +67134,12 @@
       <c r="I441" t="n">
         <v>34.11</v>
       </c>
+      <c r="J441" t="n">
+        <v>3606.8</v>
+      </c>
+      <c r="K441" t="n">
+        <v>34.56</v>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66478,15 +67165,24 @@
       <c r="F442" t="n">
         <v>1377.71</v>
       </c>
+      <c r="G442" t="n">
+        <v>746.1</v>
+      </c>
       <c r="H442" t="n">
         <v>69.38</v>
       </c>
       <c r="I442" t="n">
         <v>34.07</v>
       </c>
+      <c r="J442" t="n">
+        <v>3664.2</v>
+      </c>
+      <c r="K442" t="n">
+        <v>35.11</v>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -66515,6 +67211,12 @@
       <c r="I443" t="n">
         <v>34.94</v>
       </c>
+      <c r="J443" t="n">
+        <v>3736.2</v>
+      </c>
+      <c r="K443" t="n">
+        <v>35.8</v>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66546,6 +67248,12 @@
       <c r="I444" t="n">
         <v>35.64</v>
       </c>
+      <c r="J444" t="n">
+        <v>3820.7</v>
+      </c>
+      <c r="K444" t="n">
+        <v>36.61</v>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66577,6 +67285,12 @@
       <c r="I445" t="n">
         <v>36.14</v>
       </c>
+      <c r="J445" t="n">
+        <v>3891.7</v>
+      </c>
+      <c r="K445" t="n">
+        <v>37.29</v>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66608,6 +67322,12 @@
       <c r="I446" t="n">
         <v>36.64</v>
       </c>
+      <c r="J446" t="n">
+        <v>3888.9</v>
+      </c>
+      <c r="K446" t="n">
+        <v>37.26</v>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66639,6 +67359,12 @@
       <c r="I447" t="n">
         <v>37.17</v>
       </c>
+      <c r="J447" t="n">
+        <v>3876.1</v>
+      </c>
+      <c r="K447" t="n">
+        <v>37.14</v>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66670,6 +67396,12 @@
       <c r="I448" t="n">
         <v>37.68</v>
       </c>
+      <c r="J448" t="n">
+        <v>3887.2</v>
+      </c>
+      <c r="K448" t="n">
+        <v>37.24</v>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66701,6 +67433,12 @@
       <c r="I449" t="n">
         <v>38.23</v>
       </c>
+      <c r="J449" t="n">
+        <v>3924.3</v>
+      </c>
+      <c r="K449" t="n">
+        <v>37.6</v>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66732,6 +67470,12 @@
       <c r="I450" t="n">
         <v>38.69</v>
       </c>
+      <c r="J450" t="n">
+        <v>3944.9</v>
+      </c>
+      <c r="K450" t="n">
+        <v>37.8</v>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66763,6 +67507,12 @@
       <c r="I451" t="n">
         <v>39.15</v>
       </c>
+      <c r="J451" t="n">
+        <v>3948.5</v>
+      </c>
+      <c r="K451" t="n">
+        <v>37.83</v>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66794,6 +67544,12 @@
       <c r="I452" t="n">
         <v>39.63</v>
       </c>
+      <c r="J452" t="n">
+        <v>3967.5</v>
+      </c>
+      <c r="K452" t="n">
+        <v>38.01</v>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66825,6 +67581,12 @@
       <c r="I453" t="n">
         <v>40.07</v>
       </c>
+      <c r="J453" t="n">
+        <v>3979.1</v>
+      </c>
+      <c r="K453" t="n">
+        <v>38.12</v>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66856,6 +67618,12 @@
       <c r="I454" t="n">
         <v>40.57</v>
       </c>
+      <c r="J454" t="n">
+        <v>4001.7</v>
+      </c>
+      <c r="K454" t="n">
+        <v>38.34</v>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66887,6 +67655,12 @@
       <c r="I455" t="n">
         <v>41.12</v>
       </c>
+      <c r="J455" t="n">
+        <v>4014.4</v>
+      </c>
+      <c r="K455" t="n">
+        <v>38.46</v>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66918,6 +67692,12 @@
       <c r="I456" t="n">
         <v>41.67</v>
       </c>
+      <c r="J456" t="n">
+        <v>4016.9</v>
+      </c>
+      <c r="K456" t="n">
+        <v>38.49</v>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66949,6 +67729,12 @@
       <c r="I457" t="n">
         <v>42.19</v>
       </c>
+      <c r="J457" t="n">
+        <v>4023.7</v>
+      </c>
+      <c r="K457" t="n">
+        <v>38.55</v>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -66980,6 +67766,12 @@
       <c r="I458" t="n">
         <v>42.65</v>
       </c>
+      <c r="J458" t="n">
+        <v>4012.8</v>
+      </c>
+      <c r="K458" t="n">
+        <v>38.45</v>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67011,6 +67803,12 @@
       <c r="I459" t="n">
         <v>43.16</v>
       </c>
+      <c r="J459" t="n">
+        <v>4009.5</v>
+      </c>
+      <c r="K459" t="n">
+        <v>38.42</v>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67042,6 +67840,12 @@
       <c r="I460" t="n">
         <v>43.64</v>
       </c>
+      <c r="J460" t="n">
+        <v>4010.9</v>
+      </c>
+      <c r="K460" t="n">
+        <v>38.43</v>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67073,6 +67877,12 @@
       <c r="I461" t="n">
         <v>44.11</v>
       </c>
+      <c r="J461" t="n">
+        <v>3996.9</v>
+      </c>
+      <c r="K461" t="n">
+        <v>38.3</v>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67104,6 +67914,12 @@
       <c r="I462" t="n">
         <v>44.63</v>
       </c>
+      <c r="J462" t="n">
+        <v>4022.3</v>
+      </c>
+      <c r="K462" t="n">
+        <v>38.54</v>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67135,6 +67951,12 @@
       <c r="I463" t="n">
         <v>45.13</v>
       </c>
+      <c r="J463" t="n">
+        <v>4041.5</v>
+      </c>
+      <c r="K463" t="n">
+        <v>38.72</v>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67166,6 +67988,12 @@
       <c r="I464" t="n">
         <v>45.71</v>
       </c>
+      <c r="J464" t="n">
+        <v>4025.2</v>
+      </c>
+      <c r="K464" t="n">
+        <v>38.57</v>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67197,6 +68025,12 @@
       <c r="I465" t="n">
         <v>45.69</v>
       </c>
+      <c r="J465" t="n">
+        <v>4021.5</v>
+      </c>
+      <c r="K465" t="n">
+        <v>38.53</v>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67228,6 +68062,12 @@
       <c r="I466" t="n">
         <v>46.12</v>
       </c>
+      <c r="J466" t="n">
+        <v>4044.5</v>
+      </c>
+      <c r="K466" t="n">
+        <v>38.75</v>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67259,6 +68099,12 @@
       <c r="I467" t="n">
         <v>46.54</v>
       </c>
+      <c r="J467" t="n">
+        <v>4062.9</v>
+      </c>
+      <c r="K467" t="n">
+        <v>38.93</v>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67290,6 +68136,12 @@
       <c r="I468" t="n">
         <v>47</v>
       </c>
+      <c r="J468" t="n">
+        <v>4080.9</v>
+      </c>
+      <c r="K468" t="n">
+        <v>39.1</v>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67321,6 +68173,12 @@
       <c r="I469" t="n">
         <v>47.46</v>
       </c>
+      <c r="J469" t="n">
+        <v>4101.1</v>
+      </c>
+      <c r="K469" t="n">
+        <v>39.29</v>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67352,6 +68210,12 @@
       <c r="I470" t="n">
         <v>47.86</v>
       </c>
+      <c r="J470" t="n">
+        <v>4104.7</v>
+      </c>
+      <c r="K470" t="n">
+        <v>39.33</v>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67383,6 +68247,12 @@
       <c r="I471" t="n">
         <v>48.29</v>
       </c>
+      <c r="J471" t="n">
+        <v>4106</v>
+      </c>
+      <c r="K471" t="n">
+        <v>39.34</v>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67414,6 +68284,12 @@
       <c r="I472" t="n">
         <v>48.64</v>
       </c>
+      <c r="J472" t="n">
+        <v>4122</v>
+      </c>
+      <c r="K472" t="n">
+        <v>39.49</v>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67439,15 +68315,24 @@
       <c r="F473" t="n">
         <v>1457</v>
       </c>
+      <c r="G473" t="n">
+        <v>765.4</v>
+      </c>
       <c r="H473" t="n">
         <v>72.31</v>
       </c>
       <c r="I473" t="n">
         <v>49.16</v>
       </c>
+      <c r="J473" t="n">
+        <v>4133.9</v>
+      </c>
+      <c r="K473" t="n">
+        <v>39.61</v>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -67476,6 +68361,12 @@
       <c r="I474" t="n">
         <v>49.63</v>
       </c>
+      <c r="J474" t="n">
+        <v>4154.3</v>
+      </c>
+      <c r="K474" t="n">
+        <v>39.8</v>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67507,6 +68398,12 @@
       <c r="I475" t="n">
         <v>50.06</v>
       </c>
+      <c r="J475" t="n">
+        <v>4160.9</v>
+      </c>
+      <c r="K475" t="n">
+        <v>39.87</v>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67538,6 +68435,12 @@
       <c r="I476" t="n">
         <v>50.41</v>
       </c>
+      <c r="J476" t="n">
+        <v>4164</v>
+      </c>
+      <c r="K476" t="n">
+        <v>39.9</v>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67569,6 +68472,12 @@
       <c r="I477" t="n">
         <v>50.81</v>
       </c>
+      <c r="J477" t="n">
+        <v>4176.4</v>
+      </c>
+      <c r="K477" t="n">
+        <v>40.02</v>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67600,6 +68509,12 @@
       <c r="I478" t="n">
         <v>51.23</v>
       </c>
+      <c r="J478" t="n">
+        <v>4188.7</v>
+      </c>
+      <c r="K478" t="n">
+        <v>40.13</v>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67631,6 +68546,12 @@
       <c r="I479" t="n">
         <v>51.7</v>
       </c>
+      <c r="J479" t="n">
+        <v>4180.8</v>
+      </c>
+      <c r="K479" t="n">
+        <v>40.06</v>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67662,6 +68583,12 @@
       <c r="I480" t="n">
         <v>52.11</v>
       </c>
+      <c r="J480" t="n">
+        <v>4169.3</v>
+      </c>
+      <c r="K480" t="n">
+        <v>39.95</v>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67693,6 +68620,12 @@
       <c r="I481" t="n">
         <v>52.52</v>
       </c>
+      <c r="J481" t="n">
+        <v>4165.5</v>
+      </c>
+      <c r="K481" t="n">
+        <v>39.91</v>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67721,6 +68654,12 @@
       <c r="I482" t="n">
         <v>52.95</v>
       </c>
+      <c r="J482" t="n">
+        <v>4185.7</v>
+      </c>
+      <c r="K482" t="n">
+        <v>40.1</v>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67752,6 +68691,12 @@
       <c r="I483" t="n">
         <v>53.53</v>
       </c>
+      <c r="J483" t="n">
+        <v>4215.4</v>
+      </c>
+      <c r="K483" t="n">
+        <v>40.39</v>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67783,6 +68728,12 @@
       <c r="I484" t="n">
         <v>53.98</v>
       </c>
+      <c r="J484" t="n">
+        <v>4247.9</v>
+      </c>
+      <c r="K484" t="n">
+        <v>40.7</v>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67814,6 +68765,12 @@
       <c r="I485" t="n">
         <v>54.48</v>
       </c>
+      <c r="J485" t="n">
+        <v>4255.6</v>
+      </c>
+      <c r="K485" t="n">
+        <v>40.77</v>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67845,6 +68802,12 @@
       <c r="I486" t="n">
         <v>54.97</v>
       </c>
+      <c r="J486" t="n">
+        <v>4260.7</v>
+      </c>
+      <c r="K486" t="n">
+        <v>40.82</v>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67876,6 +68839,12 @@
       <c r="I487" t="n">
         <v>55.49</v>
       </c>
+      <c r="J487" t="n">
+        <v>4282</v>
+      </c>
+      <c r="K487" t="n">
+        <v>41.03</v>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67907,6 +68876,12 @@
       <c r="I488" t="n">
         <v>55.96</v>
       </c>
+      <c r="J488" t="n">
+        <v>4298.4</v>
+      </c>
+      <c r="K488" t="n">
+        <v>41.18</v>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67938,6 +68913,12 @@
       <c r="I489" t="n">
         <v>56.45</v>
       </c>
+      <c r="J489" t="n">
+        <v>4313.2</v>
+      </c>
+      <c r="K489" t="n">
+        <v>41.33</v>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -67969,6 +68950,12 @@
       <c r="I490" t="n">
         <v>56.97</v>
       </c>
+      <c r="J490" t="n">
+        <v>4312.5</v>
+      </c>
+      <c r="K490" t="n">
+        <v>41.32</v>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68000,6 +68987,12 @@
       <c r="I491" t="n">
         <v>57.54</v>
       </c>
+      <c r="J491" t="n">
+        <v>4320.7</v>
+      </c>
+      <c r="K491" t="n">
+        <v>41.4</v>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68028,6 +69021,12 @@
       <c r="I492" t="n">
         <v>58.21</v>
       </c>
+      <c r="J492" t="n">
+        <v>4325.4</v>
+      </c>
+      <c r="K492" t="n">
+        <v>41.44</v>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68056,6 +69055,12 @@
       <c r="I493" t="n">
         <v>58.89</v>
       </c>
+      <c r="J493" t="n">
+        <v>4338.5</v>
+      </c>
+      <c r="K493" t="n">
+        <v>41.57</v>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68084,6 +69089,12 @@
       <c r="I494" t="n">
         <v>59.78</v>
       </c>
+      <c r="J494" t="n">
+        <v>4351.6</v>
+      </c>
+      <c r="K494" t="n">
+        <v>41.69</v>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68112,6 +69123,12 @@
       <c r="I495" t="n">
         <v>60.36</v>
       </c>
+      <c r="J495" t="n">
+        <v>4361.8</v>
+      </c>
+      <c r="K495" t="n">
+        <v>41.79</v>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68140,6 +69157,12 @@
       <c r="I496" t="n">
         <v>60.89</v>
       </c>
+      <c r="J496" t="n">
+        <v>4375.3</v>
+      </c>
+      <c r="K496" t="n">
+        <v>41.92</v>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68168,6 +69191,12 @@
       <c r="I497" t="n">
         <v>61.44</v>
       </c>
+      <c r="J497" t="n">
+        <v>4388.4</v>
+      </c>
+      <c r="K497" t="n">
+        <v>42.05</v>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68196,6 +69225,12 @@
       <c r="I498" t="n">
         <v>61.96</v>
       </c>
+      <c r="J498" t="n">
+        <v>4393.3</v>
+      </c>
+      <c r="K498" t="n">
+        <v>42.09</v>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68224,6 +69259,12 @@
       <c r="I499" t="n">
         <v>62.53</v>
       </c>
+      <c r="J499" t="n">
+        <v>4402.8</v>
+      </c>
+      <c r="K499" t="n">
+        <v>42.18</v>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68255,6 +69296,12 @@
       <c r="I500" t="n">
         <v>63.45</v>
       </c>
+      <c r="J500" t="n">
+        <v>4432.7</v>
+      </c>
+      <c r="K500" t="n">
+        <v>42.47</v>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68286,6 +69333,12 @@
       <c r="I501" t="n">
         <v>64.14</v>
       </c>
+      <c r="J501" t="n">
+        <v>4450.9</v>
+      </c>
+      <c r="K501" t="n">
+        <v>42.65</v>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68317,6 +69370,12 @@
       <c r="I502" t="n">
         <v>64.92</v>
       </c>
+      <c r="J502" t="n">
+        <v>4470.6</v>
+      </c>
+      <c r="K502" t="n">
+        <v>42.83</v>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68342,15 +69401,24 @@
       <c r="F503" t="n">
         <v>1529.24</v>
       </c>
+      <c r="G503" t="n">
+        <v>782</v>
+      </c>
       <c r="H503" t="n">
         <v>69.17</v>
       </c>
       <c r="I503" t="n">
         <v>65.73</v>
       </c>
+      <c r="J503" t="n">
+        <v>4490.7</v>
+      </c>
+      <c r="K503" t="n">
+        <v>43.03</v>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
-          <t>DGA online (daily median)</t>
+          <t>DGA online (daily median); bulletin month-end: LagunaMaule</t>
         </is>
       </c>
     </row>
@@ -68379,6 +69447,12 @@
       <c r="I504" t="n">
         <v>66.56999999999999</v>
       </c>
+      <c r="J504" t="n">
+        <v>4493.9</v>
+      </c>
+      <c r="K504" t="n">
+        <v>43.06</v>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68410,6 +69484,12 @@
       <c r="I505" t="n">
         <v>67.48</v>
       </c>
+      <c r="J505" t="n">
+        <v>4495.4</v>
+      </c>
+      <c r="K505" t="n">
+        <v>43.07</v>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68441,6 +69521,12 @@
       <c r="I506" t="n">
         <v>68.45</v>
       </c>
+      <c r="J506" t="n">
+        <v>4494.5</v>
+      </c>
+      <c r="K506" t="n">
+        <v>43.06</v>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68472,6 +69558,12 @@
       <c r="I507" t="n">
         <v>69.73999999999999</v>
       </c>
+      <c r="J507" t="n">
+        <v>4516.1</v>
+      </c>
+      <c r="K507" t="n">
+        <v>43.27</v>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68503,6 +69595,12 @@
       <c r="I508" t="n">
         <v>71.09999999999999</v>
       </c>
+      <c r="J508" t="n">
+        <v>4545.1</v>
+      </c>
+      <c r="K508" t="n">
+        <v>43.55</v>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68534,6 +69632,12 @@
       <c r="I509" t="n">
         <v>72.08</v>
       </c>
+      <c r="J509" t="n">
+        <v>4579.7</v>
+      </c>
+      <c r="K509" t="n">
+        <v>43.88</v>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68565,6 +69669,12 @@
       <c r="I510" t="n">
         <v>72.97</v>
       </c>
+      <c r="J510" t="n">
+        <v>4590.3</v>
+      </c>
+      <c r="K510" t="n">
+        <v>43.98</v>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68596,6 +69706,12 @@
       <c r="I511" t="n">
         <v>73.81</v>
       </c>
+      <c r="J511" t="n">
+        <v>4589.5</v>
+      </c>
+      <c r="K511" t="n">
+        <v>43.97</v>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68627,6 +69743,12 @@
       <c r="I512" t="n">
         <v>74.67</v>
       </c>
+      <c r="J512" t="n">
+        <v>4587.3</v>
+      </c>
+      <c r="K512" t="n">
+        <v>43.95</v>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68658,6 +69780,12 @@
       <c r="I513" t="n">
         <v>75.63</v>
       </c>
+      <c r="J513" t="n">
+        <v>4586.4</v>
+      </c>
+      <c r="K513" t="n">
+        <v>43.94</v>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68689,6 +69817,12 @@
       <c r="I514" t="n">
         <v>76.75</v>
       </c>
+      <c r="J514" t="n">
+        <v>4598</v>
+      </c>
+      <c r="K514" t="n">
+        <v>44.05</v>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68720,6 +69854,12 @@
       <c r="I515" t="n">
         <v>77.77</v>
       </c>
+      <c r="J515" t="n">
+        <v>4609.1</v>
+      </c>
+      <c r="K515" t="n">
+        <v>44.16</v>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68751,6 +69891,12 @@
       <c r="I516" t="n">
         <v>78.65000000000001</v>
       </c>
+      <c r="J516" t="n">
+        <v>4617.7</v>
+      </c>
+      <c r="K516" t="n">
+        <v>44.24</v>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68779,6 +69925,12 @@
       <c r="H517" t="n">
         <v>72.81</v>
       </c>
+      <c r="J517" t="n">
+        <v>4630.7</v>
+      </c>
+      <c r="K517" t="n">
+        <v>44.37</v>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68810,6 +69962,12 @@
       <c r="I518" t="n">
         <v>81.34999999999999</v>
       </c>
+      <c r="J518" t="n">
+        <v>4634.8</v>
+      </c>
+      <c r="K518" t="n">
+        <v>44.41</v>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68841,6 +69999,12 @@
       <c r="I519" t="n">
         <v>82.34</v>
       </c>
+      <c r="J519" t="n">
+        <v>4650.2</v>
+      </c>
+      <c r="K519" t="n">
+        <v>44.55</v>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68872,6 +70036,12 @@
       <c r="I520" t="n">
         <v>83.66</v>
       </c>
+      <c r="J520" t="n">
+        <v>4671.3</v>
+      </c>
+      <c r="K520" t="n">
+        <v>44.76</v>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68903,6 +70073,12 @@
       <c r="I521" t="n">
         <v>85.04000000000001</v>
       </c>
+      <c r="J521" t="n">
+        <v>4688.3</v>
+      </c>
+      <c r="K521" t="n">
+        <v>44.92</v>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68934,6 +70110,12 @@
       <c r="I522" t="n">
         <v>86.44</v>
       </c>
+      <c r="J522" t="n">
+        <v>4698.1</v>
+      </c>
+      <c r="K522" t="n">
+        <v>45.01</v>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68965,6 +70147,12 @@
       <c r="I523" t="n">
         <v>88.02</v>
       </c>
+      <c r="J523" t="n">
+        <v>4704.2</v>
+      </c>
+      <c r="K523" t="n">
+        <v>45.07</v>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -68996,6 +70184,12 @@
       <c r="I524" t="n">
         <v>89.75</v>
       </c>
+      <c r="J524" t="n">
+        <v>4711.7</v>
+      </c>
+      <c r="K524" t="n">
+        <v>45.14</v>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69027,6 +70221,12 @@
       <c r="I525" t="n">
         <v>91.42</v>
       </c>
+      <c r="J525" t="n">
+        <v>4717.9</v>
+      </c>
+      <c r="K525" t="n">
+        <v>45.2</v>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69058,6 +70258,12 @@
       <c r="I526" t="n">
         <v>93.15000000000001</v>
       </c>
+      <c r="J526" t="n">
+        <v>4728.9</v>
+      </c>
+      <c r="K526" t="n">
+        <v>45.31</v>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69089,6 +70295,12 @@
       <c r="I527" t="n">
         <v>94.70999999999999</v>
       </c>
+      <c r="J527" t="n">
+        <v>4724.6</v>
+      </c>
+      <c r="K527" t="n">
+        <v>45.27</v>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69120,6 +70332,12 @@
       <c r="I528" t="n">
         <v>96.13</v>
       </c>
+      <c r="J528" t="n">
+        <v>4736.4</v>
+      </c>
+      <c r="K528" t="n">
+        <v>45.38</v>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69151,6 +70369,12 @@
       <c r="I529" t="n">
         <v>96.81999999999999</v>
       </c>
+      <c r="J529" t="n">
+        <v>4748.4</v>
+      </c>
+      <c r="K529" t="n">
+        <v>45.5</v>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69182,6 +70406,12 @@
       <c r="I530" t="n">
         <v>97.65000000000001</v>
       </c>
+      <c r="J530" t="n">
+        <v>4760.2</v>
+      </c>
+      <c r="K530" t="n">
+        <v>45.61</v>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69213,6 +70443,12 @@
       <c r="I531" t="n">
         <v>98.31</v>
       </c>
+      <c r="J531" t="n">
+        <v>4760.3</v>
+      </c>
+      <c r="K531" t="n">
+        <v>45.61</v>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69244,6 +70480,12 @@
       <c r="I532" t="n">
         <v>99.40000000000001</v>
       </c>
+      <c r="J532" t="n">
+        <v>4768.8</v>
+      </c>
+      <c r="K532" t="n">
+        <v>45.69</v>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69275,6 +70517,12 @@
       <c r="I533" t="n">
         <v>100.66</v>
       </c>
+      <c r="J533" t="n">
+        <v>4784.8</v>
+      </c>
+      <c r="K533" t="n">
+        <v>45.84</v>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69306,6 +70554,12 @@
       <c r="I534" t="n">
         <v>102</v>
       </c>
+      <c r="J534" t="n">
+        <v>4800.5</v>
+      </c>
+      <c r="K534" t="n">
+        <v>46</v>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69337,6 +70591,12 @@
       <c r="I535" t="n">
         <v>103.36</v>
       </c>
+      <c r="J535" t="n">
+        <v>4818.3</v>
+      </c>
+      <c r="K535" t="n">
+        <v>46.17</v>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69368,6 +70628,12 @@
       <c r="I536" t="n">
         <v>104.78</v>
       </c>
+      <c r="J536" t="n">
+        <v>4835.8</v>
+      </c>
+      <c r="K536" t="n">
+        <v>46.33</v>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69399,6 +70665,12 @@
       <c r="I537" t="n">
         <v>106.37</v>
       </c>
+      <c r="J537" t="n">
+        <v>4852.9</v>
+      </c>
+      <c r="K537" t="n">
+        <v>46.5</v>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -69430,6 +70702,12 @@
       <c r="I538" t="n">
         <v>108.17</v>
       </c>
+      <c r="J538" t="n">
+        <v>4868.7</v>
+      </c>
+      <c r="K538" t="n">
+        <v>46.65</v>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
@@ -82005,7 +83283,7 @@
         <v>531.4</v>
       </c>
       <c r="D869" t="n">
-        <v>1154.61</v>
+        <v>1154.77</v>
       </c>
       <c r="E869" t="n">
         <v>83.06</v>
@@ -82023,7 +83301,7 @@
         <v>55.92</v>
       </c>
       <c r="J869" t="n">
-        <v>5506.7</v>
+        <v>5506.9</v>
       </c>
       <c r="K869" t="n">
         <v>52.76</v>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -184,7 +184,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Total'!$A$2:$A$366</f>
+              <f>'Water year - Total'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -210,7 +210,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Total'!$A$2:$A$366</f>
+              <f>'Water year - Total'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -250,7 +250,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Total'!$A$2:$A$366</f>
+              <f>'Water year - Total'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -286,7 +286,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Total'!$A$2:$A$366</f>
+              <f>'Water year - Total'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -322,7 +322,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Total'!$A$2:$A$366</f>
+              <f>'Water year - Total'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -411,7 +411,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Colbun'!$A$2:$A$366</f>
+              <f>'Water year - Colbun'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -437,7 +437,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Colbun'!$A$2:$A$366</f>
+              <f>'Water year - Colbun'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -477,7 +477,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Colbun'!$A$2:$A$366</f>
+              <f>'Water year - Colbun'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -513,7 +513,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Colbun'!$A$2:$A$366</f>
+              <f>'Water year - Colbun'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -549,7 +549,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Colbun'!$A$2:$A$366</f>
+              <f>'Water year - Colbun'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -638,7 +638,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - LagoLaja'!$A$2:$A$366</f>
+              <f>'Water year - LagoLaja'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -664,7 +664,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - LagoLaja'!$A$2:$A$366</f>
+              <f>'Water year - LagoLaja'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -704,7 +704,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagoLaja'!$A$2:$A$366</f>
+              <f>'Water year - LagoLaja'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -740,7 +740,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagoLaja'!$A$2:$A$366</f>
+              <f>'Water year - LagoLaja'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -776,7 +776,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagoLaja'!$A$2:$A$366</f>
+              <f>'Water year - LagoLaja'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -865,7 +865,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Ralco'!$A$2:$A$366</f>
+              <f>'Water year - Ralco'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -891,7 +891,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Ralco'!$A$2:$A$366</f>
+              <f>'Water year - Ralco'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -931,7 +931,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Ralco'!$A$2:$A$366</f>
+              <f>'Water year - Ralco'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -967,7 +967,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Ralco'!$A$2:$A$366</f>
+              <f>'Water year - Ralco'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1003,7 +1003,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Ralco'!$A$2:$A$366</f>
+              <f>'Water year - Ralco'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1092,7 +1092,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - LagunaMaule'!$A$2:$A$366</f>
+              <f>'Water year - LagunaMaule'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1118,7 +1118,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - LagunaMaule'!$A$2:$A$366</f>
+              <f>'Water year - LagunaMaule'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1158,7 +1158,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagunaMaule'!$A$2:$A$366</f>
+              <f>'Water year - LagunaMaule'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1194,7 +1194,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagunaMaule'!$A$2:$A$366</f>
+              <f>'Water year - LagunaMaule'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1230,7 +1230,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - LagunaMaule'!$A$2:$A$366</f>
+              <f>'Water year - LagunaMaule'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1319,7 +1319,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Rapel'!$A$2:$A$366</f>
+              <f>'Water year - Rapel'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1345,7 +1345,7 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Water year - Rapel'!$A$2:$A$366</f>
+              <f>'Water year - Rapel'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1385,7 +1385,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Rapel'!$A$2:$A$366</f>
+              <f>'Water year - Rapel'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1421,7 +1421,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Rapel'!$A$2:$A$366</f>
+              <f>'Water year - Rapel'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -1457,7 +1457,7 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Water year - Rapel'!$A$2:$A$366</f>
+              <f>'Water year - Rapel'!$H$2:$H$366</f>
             </numRef>
           </cat>
           <val>
@@ -2099,7 +2099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2147,6 +2147,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2172,6 +2177,11 @@
       <c r="G2" t="n">
         <v>52.76</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2854,6 +2864,11 @@
       <c r="F33" t="n">
         <v>46.17</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3433,6 +3448,11 @@
       <c r="E63" t="n">
         <v>55.58</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4022,6 +4042,11 @@
       <c r="E94" t="n">
         <v>54.29</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4686,6 +4711,11 @@
       <c r="F125" t="n">
         <v>43.78</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5302,6 +5332,11 @@
       <c r="F153" t="n">
         <v>39.45</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5984,6 +6019,11 @@
       <c r="F184" t="n">
         <v>37.84</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -6644,6 +6684,11 @@
       <c r="F214" t="n">
         <v>35.18</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -7326,6 +7371,11 @@
       <c r="F245" t="n">
         <v>32.37</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7986,6 +8036,11 @@
       <c r="F275" t="n">
         <v>28.82</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -8668,6 +8723,11 @@
       <c r="F306" t="n">
         <v>44.03</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -9349,6 +9409,11 @@
       </c>
       <c r="F337" t="n">
         <v>50.71</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -10001,7 +10066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10049,6 +10114,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10074,6 +10144,11 @@
       <c r="G2" t="n">
         <v>1501.01</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10756,6 +10831,11 @@
       <c r="F33" t="n">
         <v>1229.7</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -11416,6 +11496,11 @@
       <c r="F63" t="n">
         <v>1257.13</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -12098,6 +12183,11 @@
       <c r="F94" t="n">
         <v>1160.87</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12780,6 +12870,11 @@
       <c r="F125" t="n">
         <v>1030.09</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -13396,6 +13491,11 @@
       <c r="F153" t="n">
         <v>913.24</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14078,6 +14178,11 @@
       <c r="F184" t="n">
         <v>925.02</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -14738,6 +14843,11 @@
       <c r="F214" t="n">
         <v>815.04</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15420,6 +15530,11 @@
       <c r="F245" t="n">
         <v>715.03</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -16080,6 +16195,11 @@
       <c r="F275" t="n">
         <v>564.36</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -16762,6 +16882,11 @@
       <c r="F306" t="n">
         <v>1188.93</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17443,6 +17568,11 @@
       </c>
       <c r="F337" t="n">
         <v>1513.57</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -18095,7 +18225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -18143,6 +18273,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18168,6 +18303,11 @@
       <c r="G2" t="n">
         <v>1529.98</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18850,6 +18990,11 @@
       <c r="F33" t="n">
         <v>1608.46</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -19510,6 +19655,11 @@
       <c r="F63" t="n">
         <v>1614.48</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -20192,6 +20342,11 @@
       <c r="F94" t="n">
         <v>1476.76</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -20874,6 +21029,11 @@
       <c r="F125" t="n">
         <v>1287.79</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -21490,6 +21650,11 @@
       <c r="F153" t="n">
         <v>1123.23</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -22172,6 +22337,11 @@
       <c r="F184" t="n">
         <v>1070.52</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -22832,6 +23002,11 @@
       <c r="F214" t="n">
         <v>1042.02</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -23514,6 +23689,11 @@
       <c r="F245" t="n">
         <v>969.76</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -24174,6 +24354,11 @@
       <c r="F275" t="n">
         <v>875</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -24856,6 +25041,11 @@
       <c r="F306" t="n">
         <v>1094.12</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -25537,6 +25727,11 @@
       </c>
       <c r="F337" t="n">
         <v>1298.84</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -26189,7 +26384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -26237,6 +26432,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26260,7 +26460,12 @@
         <v>494.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1154.77</v>
+        <v>1154.61</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -26944,6 +27149,11 @@
       <c r="F33" t="n">
         <v>542.4</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -27604,6 +27814,11 @@
       <c r="F63" t="n">
         <v>773.3099999999999</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -28286,6 +28501,11 @@
       <c r="F94" t="n">
         <v>897.87</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28968,6 +29188,11 @@
       <c r="F125" t="n">
         <v>860.85</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -29584,6 +29809,11 @@
       <c r="F153" t="n">
         <v>737.8</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -30266,6 +30496,11 @@
       <c r="F184" t="n">
         <v>728.11</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -30926,6 +31161,11 @@
       <c r="F214" t="n">
         <v>660.46</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -31608,6 +31848,11 @@
       <c r="F245" t="n">
         <v>599.14</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -32268,6 +32513,11 @@
       <c r="F275" t="n">
         <v>471.13</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -32950,6 +33200,11 @@
       <c r="F306" t="n">
         <v>998.99</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -33631,6 +33886,11 @@
       </c>
       <c r="F337" t="n">
         <v>1152.85</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -34283,7 +34543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -34331,6 +34591,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34351,7 +34616,12 @@
         <v>555.52</v>
       </c>
       <c r="G2" t="n">
-        <v>706.67</v>
+        <v>706.92</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -34942,6 +35212,11 @@
       <c r="E33" t="n">
         <v>533.55</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -35512,6 +35787,11 @@
       <c r="E63" t="n">
         <v>561.64</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -36101,6 +36381,11 @@
       <c r="E94" t="n">
         <v>584.39</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -36765,6 +37050,11 @@
       <c r="F125" t="n">
         <v>715.55</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -37381,6 +37671,11 @@
       <c r="F153" t="n">
         <v>674.05</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -38063,6 +38358,11 @@
       <c r="F184" t="n">
         <v>670.52</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -38723,6 +39023,11 @@
       <c r="F214" t="n">
         <v>647.89</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -39405,6 +39710,11 @@
       <c r="F245" t="n">
         <v>631.85</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -40065,6 +40375,11 @@
       <c r="F275" t="n">
         <v>632.35</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -40747,6 +41062,11 @@
       <c r="F306" t="n">
         <v>659.45</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -41428,6 +41748,11 @@
       </c>
       <c r="F337" t="n">
         <v>687.6799999999999</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -42080,7 +42405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G366"/>
+  <dimension ref="A1:H366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -42128,6 +42453,11 @@
           <t>WY 2026/27</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Axis label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -42153,6 +42483,11 @@
       <c r="G2" t="n">
         <v>531.4</v>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>01-Oct</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42835,6 +43170,11 @@
       <c r="F33" t="n">
         <v>579.0700000000001</v>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>01-Nov</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -43495,6 +43835,11 @@
       <c r="F63" t="n">
         <v>602.22</v>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>01-Dec</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -44177,6 +44522,11 @@
       <c r="F94" t="n">
         <v>597.09</v>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>01-Jan</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -44859,6 +45209,11 @@
       <c r="F125" t="n">
         <v>597.09</v>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>01-Feb</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -45475,6 +45830,11 @@
       <c r="F153" t="n">
         <v>591.22</v>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01-Mar</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -46157,6 +46517,11 @@
       <c r="F184" t="n">
         <v>481.46</v>
       </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>01-Apr</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -46817,6 +47182,11 @@
       <c r="F214" t="n">
         <v>430.09</v>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>01-May</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -47499,6 +47869,11 @@
       <c r="F245" t="n">
         <v>390.85</v>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>01-Jun</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -48159,6 +48534,11 @@
       <c r="F275" t="n">
         <v>393.02</v>
       </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>01-Jul</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -48841,6 +49221,11 @@
       <c r="F306" t="n">
         <v>572.17</v>
       </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>01-Aug</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -49522,6 +49907,11 @@
       </c>
       <c r="F337" t="n">
         <v>557.4299999999999</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>01-Sep</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -83283,25 +83673,25 @@
         <v>531.4</v>
       </c>
       <c r="D869" t="n">
-        <v>1154.77</v>
+        <v>1154.61</v>
       </c>
       <c r="E869" t="n">
-        <v>83.06</v>
+        <v>82.92</v>
       </c>
       <c r="F869" t="n">
         <v>1529.98</v>
       </c>
       <c r="G869" t="n">
-        <v>706.67</v>
+        <v>706.92</v>
       </c>
       <c r="H869" t="n">
-        <v>88.23999999999999</v>
+        <v>88.14</v>
       </c>
       <c r="I869" t="n">
         <v>55.92</v>
       </c>
       <c r="J869" t="n">
-        <v>5506.9</v>
+        <v>5506.8</v>
       </c>
       <c r="K869" t="n">
         <v>52.76</v>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -2175,7 +2175,7 @@
         <v>43.06</v>
       </c>
       <c r="G2" t="n">
-        <v>52.76</v>
+        <v>52.73</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>1057.15</v>
       </c>
       <c r="G2" t="n">
-        <v>1501.01</v>
+        <v>1500.29</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26460,7 +26460,7 @@
         <v>494.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1154.61</v>
+        <v>1154.45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>550.22</v>
       </c>
       <c r="G2" t="n">
-        <v>531.4</v>
+        <v>529.52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -83667,16 +83667,16 @@
         <v>46296</v>
       </c>
       <c r="B869" t="n">
-        <v>1501.01</v>
+        <v>1500.29</v>
       </c>
       <c r="C869" t="n">
-        <v>531.4</v>
+        <v>529.52</v>
       </c>
       <c r="D869" t="n">
-        <v>1154.61</v>
+        <v>1154.45</v>
       </c>
       <c r="E869" t="n">
-        <v>82.92</v>
+        <v>82.69</v>
       </c>
       <c r="F869" t="n">
         <v>1529.98</v>
@@ -83685,16 +83685,16 @@
         <v>706.92</v>
       </c>
       <c r="H869" t="n">
-        <v>88.14</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="I869" t="n">
-        <v>55.92</v>
+        <v>55.9</v>
       </c>
       <c r="J869" t="n">
-        <v>5506.8</v>
+        <v>5503.8</v>
       </c>
       <c r="K869" t="n">
-        <v>52.76</v>
+        <v>52.73</v>
       </c>
       <c r="L869" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -2175,7 +2175,7 @@
         <v>43.06</v>
       </c>
       <c r="G2" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>1057.15</v>
       </c>
       <c r="G2" t="n">
-        <v>1500.29</v>
+        <v>1499.57</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -18301,7 +18301,7 @@
         <v>1531.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1529.98</v>
+        <v>1531.84</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -83667,7 +83667,7 @@
         <v>46296</v>
       </c>
       <c r="B869" t="n">
-        <v>1500.29</v>
+        <v>1499.57</v>
       </c>
       <c r="C869" t="n">
         <v>529.52</v>
@@ -83676,25 +83676,25 @@
         <v>1154.45</v>
       </c>
       <c r="E869" t="n">
-        <v>82.69</v>
+        <v>82.52</v>
       </c>
       <c r="F869" t="n">
-        <v>1529.98</v>
+        <v>1531.84</v>
       </c>
       <c r="G869" t="n">
         <v>706.92</v>
       </c>
       <c r="H869" t="n">
-        <v>88.18000000000001</v>
+        <v>88.33</v>
       </c>
       <c r="I869" t="n">
         <v>55.9</v>
       </c>
       <c r="J869" t="n">
-        <v>5503.8</v>
+        <v>5504.8</v>
       </c>
       <c r="K869" t="n">
-        <v>52.73</v>
+        <v>52.74</v>
       </c>
       <c r="L869" t="inlineStr">
         <is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -159,7 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -340,23 +340,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="100"/>
+          <min val="0"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>% full</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="20"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -386,7 +428,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -567,23 +609,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1600"/>
+          <min val="400"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="200"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -613,7 +697,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -794,23 +878,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="2500"/>
+          <min val="500"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="250"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -840,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1021,23 +1147,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="1200"/>
+          <min val="400"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="200"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1067,7 +1235,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1248,23 +1416,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="900"/>
+          <min val="200"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="100"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1294,7 +1504,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-01</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1475,23 +1685,65 @@
         <scaling>
           <orientation val="minMax"/>
         </scaling>
-        <axPos val="l"/>
+        <delete val="0"/>
+        <axPos val="b"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="650"/>
+          <min val="350"/>
         </scaling>
+        <delete val="0"/>
         <axPos val="l"/>
         <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>million m3</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+          <overlay val="0"/>
+        </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <majorUnit val="50"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1987,6 +2239,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -2001,6 +2254,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -2036,6 +2290,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -2175,7 +2430,7 @@
         <v>43.06</v>
       </c>
       <c r="G2" t="n">
-        <v>52.74</v>
+        <v>52.73</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -2203,6 +2458,9 @@
       </c>
       <c r="F3" t="n">
         <v>43.07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>52.78</v>
       </c>
     </row>
     <row r="4">
@@ -10142,7 +10400,7 @@
         <v>1057.15</v>
       </c>
       <c r="G2" t="n">
-        <v>1499.57</v>
+        <v>1496.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -10170,6 +10428,9 @@
       </c>
       <c r="F3" t="n">
         <v>1061.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1495.73</v>
       </c>
     </row>
     <row r="4">
@@ -18301,7 +18562,7 @@
         <v>1531.47</v>
       </c>
       <c r="G2" t="n">
-        <v>1531.84</v>
+        <v>1534.44</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -18329,6 +18590,9 @@
       </c>
       <c r="F3" t="n">
         <v>1534.44</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1544.08</v>
       </c>
     </row>
     <row r="4">
@@ -26460,7 +26724,7 @@
         <v>494.9</v>
       </c>
       <c r="G2" t="n">
-        <v>1154.45</v>
+        <v>1154.29</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -26488,6 +26752,9 @@
       </c>
       <c r="F3" t="n">
         <v>495.78</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1154.29</v>
       </c>
     </row>
     <row r="4">
@@ -34642,6 +34909,9 @@
       <c r="E3" t="n">
         <v>556.1</v>
       </c>
+      <c r="G3" t="n">
+        <v>708.1900000000001</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -42510,6 +42780,9 @@
       <c r="F3" t="n">
         <v>545.2</v>
       </c>
+      <c r="G3" t="n">
+        <v>523.87</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -50564,7 +50837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L869"/>
+  <dimension ref="A1:L870"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83667,36 +83940,76 @@
         <v>46296</v>
       </c>
       <c r="B869" t="n">
-        <v>1499.57</v>
+        <v>1496.21</v>
       </c>
       <c r="C869" t="n">
         <v>529.52</v>
       </c>
       <c r="D869" t="n">
-        <v>1154.45</v>
+        <v>1154.29</v>
       </c>
       <c r="E869" t="n">
-        <v>82.52</v>
+        <v>82.37</v>
       </c>
       <c r="F869" t="n">
-        <v>1531.84</v>
+        <v>1534.44</v>
       </c>
       <c r="G869" t="n">
         <v>706.92</v>
       </c>
       <c r="H869" t="n">
-        <v>88.33</v>
+        <v>89.69</v>
       </c>
       <c r="I869" t="n">
-        <v>55.9</v>
+        <v>56.41</v>
       </c>
       <c r="J869" t="n">
-        <v>5504.8</v>
+        <v>5503.8</v>
       </c>
       <c r="K869" t="n">
-        <v>52.74</v>
+        <v>52.73</v>
       </c>
       <c r="L869" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="3" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B870" t="n">
+        <v>1495.73</v>
+      </c>
+      <c r="C870" t="n">
+        <v>523.87</v>
+      </c>
+      <c r="D870" t="n">
+        <v>1154.29</v>
+      </c>
+      <c r="E870" t="n">
+        <v>82.42</v>
+      </c>
+      <c r="F870" t="n">
+        <v>1544.08</v>
+      </c>
+      <c r="G870" t="n">
+        <v>708.1900000000001</v>
+      </c>
+      <c r="H870" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="I870" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="J870" t="n">
+        <v>5508.6</v>
+      </c>
+      <c r="K870" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="L870" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -159,7 +159,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -428,7 +428,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -697,7 +697,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -966,7 +966,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1235,7 +1235,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1504,7 +1504,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-02</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -2460,7 +2460,7 @@
         <v>43.07</v>
       </c>
       <c r="G3" t="n">
-        <v>52.78</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="4">
@@ -2484,6 +2484,9 @@
       <c r="F4" t="n">
         <v>43.06</v>
       </c>
+      <c r="G4" t="n">
+        <v>53.02</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2506,6 +2509,9 @@
       <c r="F5" t="n">
         <v>43.27</v>
       </c>
+      <c r="G5" t="n">
+        <v>53.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2528,6 +2534,9 @@
       <c r="F6" t="n">
         <v>43.55</v>
       </c>
+      <c r="G6" t="n">
+        <v>53.32</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2550,6 +2559,9 @@
       <c r="F7" t="n">
         <v>43.88</v>
       </c>
+      <c r="G7" t="n">
+        <v>53.29</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2572,6 +2584,9 @@
       <c r="F8" t="n">
         <v>43.98</v>
       </c>
+      <c r="G8" t="n">
+        <v>53.73</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2593,6 +2608,9 @@
       </c>
       <c r="F9" t="n">
         <v>43.97</v>
+      </c>
+      <c r="G9" t="n">
+        <v>54.21</v>
       </c>
     </row>
     <row r="10">
@@ -10430,7 +10448,7 @@
         <v>1061.6</v>
       </c>
       <c r="G3" t="n">
-        <v>1495.73</v>
+        <v>1496.93</v>
       </c>
     </row>
     <row r="4">
@@ -10454,6 +10472,9 @@
       <c r="F4" t="n">
         <v>1067.5</v>
       </c>
+      <c r="G4" t="n">
+        <v>1511.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10476,6 +10497,9 @@
       <c r="F5" t="n">
         <v>1080.11</v>
       </c>
+      <c r="G5" t="n">
+        <v>1518.18</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10498,6 +10522,9 @@
       <c r="F6" t="n">
         <v>1093.58</v>
       </c>
+      <c r="G6" t="n">
+        <v>1524.01</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10520,6 +10547,9 @@
       <c r="F7" t="n">
         <v>1105.72</v>
       </c>
+      <c r="G7" t="n">
+        <v>1501.73</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -10542,6 +10572,9 @@
       <c r="F8" t="n">
         <v>1110.91</v>
       </c>
+      <c r="G8" t="n">
+        <v>1500.53</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -10563,6 +10596,9 @@
       </c>
       <c r="F9" t="n">
         <v>1116.12</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1511.87</v>
       </c>
     </row>
     <row r="10">
@@ -18592,7 +18628,7 @@
         <v>1534.44</v>
       </c>
       <c r="G3" t="n">
-        <v>1544.08</v>
+        <v>1545.57</v>
       </c>
     </row>
     <row r="4">
@@ -18616,6 +18652,9 @@
       <c r="F4" t="n">
         <v>1535.92</v>
       </c>
+      <c r="G4" t="n">
+        <v>1558.18</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -18638,6 +18677,9 @@
       <c r="F5" t="n">
         <v>1538.89</v>
       </c>
+      <c r="G5" t="n">
+        <v>1568.61</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -18660,6 +18702,9 @@
       <c r="F6" t="n">
         <v>1543.34</v>
       </c>
+      <c r="G6" t="n">
+        <v>1577.26</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -18682,6 +18727,9 @@
       <c r="F7" t="n">
         <v>1546.31</v>
       </c>
+      <c r="G7" t="n">
+        <v>1587.03</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -18704,6 +18752,9 @@
       <c r="F8" t="n">
         <v>1548.53</v>
       </c>
+      <c r="G8" t="n">
+        <v>1594.93</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -18725,6 +18776,9 @@
       </c>
       <c r="F9" t="n">
         <v>1550.76</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1600.57</v>
       </c>
     </row>
     <row r="10">
@@ -26778,6 +26832,9 @@
       <c r="F4" t="n">
         <v>494.1</v>
       </c>
+      <c r="G4" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -26800,6 +26857,9 @@
       <c r="F5" t="n">
         <v>495.69</v>
       </c>
+      <c r="G5" t="n">
+        <v>1154.45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -26822,6 +26882,9 @@
       <c r="F6" t="n">
         <v>502.13</v>
       </c>
+      <c r="G6" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -26844,6 +26907,9 @@
       <c r="F7" t="n">
         <v>508.04</v>
       </c>
+      <c r="G7" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -26866,6 +26932,9 @@
       <c r="F8" t="n">
         <v>512</v>
       </c>
+      <c r="G8" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -26887,6 +26956,9 @@
       </c>
       <c r="F9" t="n">
         <v>509.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1154.61</v>
       </c>
     </row>
     <row r="10">
@@ -34910,7 +34982,7 @@
         <v>556.1</v>
       </c>
       <c r="G3" t="n">
-        <v>708.1900000000001</v>
+        <v>708.4400000000001</v>
       </c>
     </row>
     <row r="4">
@@ -34931,6 +35003,9 @@
       <c r="E4" t="n">
         <v>556.6799999999999</v>
       </c>
+      <c r="G4" t="n">
+        <v>709.46</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -34950,6 +35025,9 @@
       <c r="E5" t="n">
         <v>557.26</v>
       </c>
+      <c r="G5" t="n">
+        <v>709.97</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -34969,6 +35047,9 @@
       <c r="E6" t="n">
         <v>557.83</v>
       </c>
+      <c r="G6" t="n">
+        <v>710.47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -34988,6 +35069,9 @@
       <c r="E7" t="n">
         <v>558.41</v>
       </c>
+      <c r="G7" t="n">
+        <v>712.76</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -35007,6 +35091,9 @@
       <c r="E8" t="n">
         <v>559.12</v>
       </c>
+      <c r="G8" t="n">
+        <v>714.54</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -35025,6 +35112,9 @@
       </c>
       <c r="E9" t="n">
         <v>560.08</v>
+      </c>
+      <c r="G9" t="n">
+        <v>714.79</v>
       </c>
     </row>
     <row r="10">
@@ -42805,6 +42895,9 @@
       <c r="F4" t="n">
         <v>540.5</v>
       </c>
+      <c r="G4" t="n">
+        <v>517.67</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -42827,6 +42920,9 @@
       <c r="F5" t="n">
         <v>543.95</v>
       </c>
+      <c r="G5" t="n">
+        <v>517.12</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -42849,6 +42945,9 @@
       <c r="F6" t="n">
         <v>547.08</v>
       </c>
+      <c r="G6" t="n">
+        <v>517.12</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -42871,6 +42970,9 @@
       <c r="F7" t="n">
         <v>559</v>
       </c>
+      <c r="G7" t="n">
+        <v>523.87</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -42893,6 +42995,9 @@
       <c r="F8" t="n">
         <v>561.5</v>
       </c>
+      <c r="G8" t="n">
+        <v>561.1900000000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -42914,6 +43019,9 @@
       </c>
       <c r="F9" t="n">
         <v>554.29</v>
+      </c>
+      <c r="G9" t="n">
+        <v>593.42</v>
       </c>
     </row>
     <row r="10">
@@ -50837,7 +50945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L870"/>
+  <dimension ref="A1:L876"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83980,7 +84088,7 @@
         <v>46297</v>
       </c>
       <c r="B870" t="n">
-        <v>1495.73</v>
+        <v>1496.93</v>
       </c>
       <c r="C870" t="n">
         <v>523.87</v>
@@ -83989,27 +84097,267 @@
         <v>1154.29</v>
       </c>
       <c r="E870" t="n">
+        <v>82.45</v>
+      </c>
+      <c r="F870" t="n">
+        <v>1545.57</v>
+      </c>
+      <c r="G870" t="n">
+        <v>708.4400000000001</v>
+      </c>
+      <c r="H870" t="n">
+        <v>90.20999999999999</v>
+      </c>
+      <c r="I870" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="J870" t="n">
+        <v>5511.5</v>
+      </c>
+      <c r="K870" t="n">
+        <v>52.81</v>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="3" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B871" t="n">
+        <v>1511.15</v>
+      </c>
+      <c r="C871" t="n">
+        <v>517.67</v>
+      </c>
+      <c r="D871" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E871" t="n">
+        <v>82.56999999999999</v>
+      </c>
+      <c r="F871" t="n">
+        <v>1558.18</v>
+      </c>
+      <c r="G871" t="n">
+        <v>709.46</v>
+      </c>
+      <c r="H871" t="n">
+        <v>89.56</v>
+      </c>
+      <c r="I871" t="n">
+        <v>59</v>
+      </c>
+      <c r="J871" t="n">
+        <v>5533.2</v>
+      </c>
+      <c r="K871" t="n">
+        <v>53.02</v>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="3" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B872" t="n">
+        <v>1518.18</v>
+      </c>
+      <c r="C872" t="n">
+        <v>517.12</v>
+      </c>
+      <c r="D872" t="n">
+        <v>1154.45</v>
+      </c>
+      <c r="E872" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="F872" t="n">
+        <v>1568.61</v>
+      </c>
+      <c r="G872" t="n">
+        <v>709.97</v>
+      </c>
+      <c r="H872" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="I872" t="n">
+        <v>60.22</v>
+      </c>
+      <c r="J872" t="n">
+        <v>5550.7</v>
+      </c>
+      <c r="K872" t="n">
+        <v>53.18</v>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B873" t="n">
+        <v>1524.01</v>
+      </c>
+      <c r="C873" t="n">
+        <v>517.12</v>
+      </c>
+      <c r="D873" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E873" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="F873" t="n">
+        <v>1577.26</v>
+      </c>
+      <c r="G873" t="n">
+        <v>710.47</v>
+      </c>
+      <c r="H873" t="n">
+        <v>88.81999999999999</v>
+      </c>
+      <c r="I873" t="n">
+        <v>61</v>
+      </c>
+      <c r="J873" t="n">
+        <v>5565.4</v>
+      </c>
+      <c r="K873" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B874" t="n">
+        <v>1501.73</v>
+      </c>
+      <c r="C874" t="n">
+        <v>523.87</v>
+      </c>
+      <c r="D874" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E874" t="n">
         <v>82.42</v>
       </c>
-      <c r="F870" t="n">
-        <v>1544.08</v>
-      </c>
-      <c r="G870" t="n">
-        <v>708.1900000000001</v>
-      </c>
-      <c r="H870" t="n">
-        <v>90.28</v>
-      </c>
-      <c r="I870" t="n">
-        <v>57.56</v>
-      </c>
-      <c r="J870" t="n">
-        <v>5508.6</v>
-      </c>
-      <c r="K870" t="n">
-        <v>52.78</v>
-      </c>
-      <c r="L870" t="inlineStr">
+      <c r="F874" t="n">
+        <v>1587.03</v>
+      </c>
+      <c r="G874" t="n">
+        <v>712.76</v>
+      </c>
+      <c r="H874" t="n">
+        <v>90.36</v>
+      </c>
+      <c r="I874" t="n">
+        <v>61.96</v>
+      </c>
+      <c r="J874" t="n">
+        <v>5561.9</v>
+      </c>
+      <c r="K874" t="n">
+        <v>53.29</v>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B875" t="n">
+        <v>1500.53</v>
+      </c>
+      <c r="C875" t="n">
+        <v>561.1900000000001</v>
+      </c>
+      <c r="D875" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E875" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="F875" t="n">
+        <v>1594.93</v>
+      </c>
+      <c r="G875" t="n">
+        <v>714.54</v>
+      </c>
+      <c r="H875" t="n">
+        <v>90.17</v>
+      </c>
+      <c r="I875" t="n">
+        <v>63.59</v>
+      </c>
+      <c r="J875" t="n">
+        <v>5607.7</v>
+      </c>
+      <c r="K875" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B876" t="n">
+        <v>1511.87</v>
+      </c>
+      <c r="C876" t="n">
+        <v>593.42</v>
+      </c>
+      <c r="D876" t="n">
+        <v>1154.61</v>
+      </c>
+      <c r="E876" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="F876" t="n">
+        <v>1600.57</v>
+      </c>
+      <c r="G876" t="n">
+        <v>714.79</v>
+      </c>
+      <c r="H876" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="I876" t="n">
+        <v>64.28</v>
+      </c>
+      <c r="J876" t="n">
+        <v>5657.6</v>
+      </c>
+      <c r="K876" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="L876" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -159,7 +159,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -271,7 +272,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -428,7 +429,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -540,7 +542,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -697,7 +699,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -809,7 +812,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -966,7 +969,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1078,7 +1082,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1235,7 +1239,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1347,7 +1352,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1504,7 +1509,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-08</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1616,7 +1622,7 @@
           <spPr>
             <a:ln w="19050">
               <a:solidFill>
-                <a:srgbClr val="EB6834"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -2610,7 +2616,7 @@
         <v>43.97</v>
       </c>
       <c r="G9" t="n">
-        <v>54.21</v>
+        <v>54.37</v>
       </c>
     </row>
     <row r="10">
@@ -2634,6 +2640,9 @@
       <c r="F10" t="n">
         <v>43.95</v>
       </c>
+      <c r="G10" t="n">
+        <v>54.63</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2656,6 +2665,9 @@
       <c r="F11" t="n">
         <v>43.94</v>
       </c>
+      <c r="G11" t="n">
+        <v>54.75</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2678,6 +2690,9 @@
       <c r="F12" t="n">
         <v>44.05</v>
       </c>
+      <c r="G12" t="n">
+        <v>54.69</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2700,6 +2715,9 @@
       <c r="F13" t="n">
         <v>44.16</v>
       </c>
+      <c r="G13" t="n">
+        <v>54.73</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2722,6 +2740,9 @@
       <c r="F14" t="n">
         <v>44.24</v>
       </c>
+      <c r="G14" t="n">
+        <v>54.85</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2744,6 +2765,9 @@
       <c r="F15" t="n">
         <v>44.37</v>
       </c>
+      <c r="G15" t="n">
+        <v>54.94</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2766,6 +2790,9 @@
       <c r="F16" t="n">
         <v>44.41</v>
       </c>
+      <c r="G16" t="n">
+        <v>54.99</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2788,6 +2815,9 @@
       <c r="F17" t="n">
         <v>44.55</v>
       </c>
+      <c r="G17" t="n">
+        <v>55.13</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2810,6 +2840,9 @@
       <c r="F18" t="n">
         <v>44.76</v>
       </c>
+      <c r="G18" t="n">
+        <v>55.2</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2832,6 +2865,9 @@
       <c r="F19" t="n">
         <v>44.92</v>
       </c>
+      <c r="G19" t="n">
+        <v>55.31</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2854,6 +2890,9 @@
       <c r="F20" t="n">
         <v>45.01</v>
       </c>
+      <c r="G20" t="n">
+        <v>55.29</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2876,6 +2915,9 @@
       <c r="F21" t="n">
         <v>45.07</v>
       </c>
+      <c r="G21" t="n">
+        <v>55.39</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2898,6 +2940,9 @@
       <c r="F22" t="n">
         <v>45.14</v>
       </c>
+      <c r="G22" t="n">
+        <v>55.63</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2920,6 +2965,9 @@
       <c r="F23" t="n">
         <v>45.2</v>
       </c>
+      <c r="G23" t="n">
+        <v>55.91</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2942,6 +2990,9 @@
       <c r="F24" t="n">
         <v>45.31</v>
       </c>
+      <c r="G24" t="n">
+        <v>56.04</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2964,6 +3015,9 @@
       <c r="F25" t="n">
         <v>45.27</v>
       </c>
+      <c r="G25" t="n">
+        <v>56.24</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2986,6 +3040,9 @@
       <c r="F26" t="n">
         <v>45.38</v>
       </c>
+      <c r="G26" t="n">
+        <v>56.39</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3008,6 +3065,9 @@
       <c r="F27" t="n">
         <v>45.5</v>
       </c>
+      <c r="G27" t="n">
+        <v>56.41</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3029,6 +3089,9 @@
       </c>
       <c r="F28" t="n">
         <v>45.61</v>
+      </c>
+      <c r="G28" t="n">
+        <v>56.5</v>
       </c>
     </row>
     <row r="29">
@@ -10598,7 +10661,7 @@
         <v>1116.12</v>
       </c>
       <c r="G9" t="n">
-        <v>1511.87</v>
+        <v>1516.48</v>
       </c>
     </row>
     <row r="10">
@@ -10622,6 +10685,9 @@
       <c r="F10" t="n">
         <v>1117.05</v>
       </c>
+      <c r="G10" t="n">
+        <v>1530.12</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -10644,6 +10710,9 @@
       <c r="F11" t="n">
         <v>1117.05</v>
       </c>
+      <c r="G11" t="n">
+        <v>1530.85</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -10666,6 +10735,9 @@
       <c r="F12" t="n">
         <v>1119.1</v>
       </c>
+      <c r="G12" t="n">
+        <v>1519.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -10688,6 +10760,9 @@
       <c r="F13" t="n">
         <v>1122.47</v>
       </c>
+      <c r="G13" t="n">
+        <v>1515.02</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -10710,6 +10785,9 @@
       <c r="F14" t="n">
         <v>1128.86</v>
       </c>
+      <c r="G14" t="n">
+        <v>1517.45</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -10732,6 +10810,9 @@
       <c r="F15" t="n">
         <v>1141.34</v>
       </c>
+      <c r="G15" t="n">
+        <v>1515.99</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -10754,6 +10835,9 @@
       <c r="F16" t="n">
         <v>1145.91</v>
       </c>
+      <c r="G16" t="n">
+        <v>1514.54</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -10776,6 +10860,9 @@
       <c r="F17" t="n">
         <v>1152.41</v>
       </c>
+      <c r="G17" t="n">
+        <v>1513.57</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -10798,6 +10885,9 @@
       <c r="F18" t="n">
         <v>1161.64</v>
       </c>
+      <c r="G18" t="n">
+        <v>1511.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -10820,6 +10910,9 @@
       <c r="F19" t="n">
         <v>1172.68</v>
       </c>
+      <c r="G19" t="n">
+        <v>1510.66</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -10842,6 +10935,9 @@
       <c r="F20" t="n">
         <v>1179.71</v>
       </c>
+      <c r="G20" t="n">
+        <v>1509.69</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -10864,6 +10960,9 @@
       <c r="F21" t="n">
         <v>1184.61</v>
       </c>
+      <c r="G21" t="n">
+        <v>1517.2</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -10886,6 +10985,9 @@
       <c r="F22" t="n">
         <v>1189.33</v>
       </c>
+      <c r="G22" t="n">
+        <v>1526.21</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -10908,6 +11010,9 @@
       <c r="F23" t="n">
         <v>1194.85</v>
       </c>
+      <c r="G23" t="n">
+        <v>1523.77</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -10930,6 +11035,9 @@
       <c r="F24" t="n">
         <v>1200.6</v>
       </c>
+      <c r="G24" t="n">
+        <v>1520.36</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -10952,6 +11060,9 @@
       <c r="F25" t="n">
         <v>1201.59</v>
       </c>
+      <c r="G25" t="n">
+        <v>1524.99</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10974,6 +11085,9 @@
       <c r="F26" t="n">
         <v>1206.77</v>
       </c>
+      <c r="G26" t="n">
+        <v>1527.67</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -10996,6 +11110,9 @@
       <c r="F27" t="n">
         <v>1212.37</v>
       </c>
+      <c r="G27" t="n">
+        <v>1521.34</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -11017,6 +11134,9 @@
       </c>
       <c r="F28" t="n">
         <v>1213.17</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1523.77</v>
       </c>
     </row>
     <row r="29">
@@ -18778,7 +18898,7 @@
         <v>1550.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1600.57</v>
+        <v>1603.95</v>
       </c>
     </row>
     <row r="10">
@@ -18802,6 +18922,9 @@
       <c r="F10" t="n">
         <v>1552.99</v>
       </c>
+      <c r="G10" t="n">
+        <v>1612.22</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -18824,6 +18947,9 @@
       <c r="F11" t="n">
         <v>1555.95</v>
       </c>
+      <c r="G11" t="n">
+        <v>1620.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -18846,6 +18972,9 @@
       <c r="F12" t="n">
         <v>1559.66</v>
       </c>
+      <c r="G12" t="n">
+        <v>1627.26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18868,6 +18997,9 @@
       <c r="F13" t="n">
         <v>1562.63</v>
       </c>
+      <c r="G13" t="n">
+        <v>1634.78</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -18890,6 +19022,9 @@
       <c r="F14" t="n">
         <v>1564.86</v>
       </c>
+      <c r="G14" t="n">
+        <v>1644.22</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18912,6 +19047,9 @@
       <c r="F15" t="n">
         <v>1567.1</v>
       </c>
+      <c r="G15" t="n">
+        <v>1652.96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -18934,6 +19072,9 @@
       <c r="F16" t="n">
         <v>1570.11</v>
       </c>
+      <c r="G16" t="n">
+        <v>1661.32</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -18956,6 +19097,9 @@
       <c r="F17" t="n">
         <v>1573.12</v>
       </c>
+      <c r="G17" t="n">
+        <v>1670.44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -18978,6 +19122,9 @@
       <c r="F18" t="n">
         <v>1576.88</v>
       </c>
+      <c r="G18" t="n">
+        <v>1680.32</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -19000,6 +19147,9 @@
       <c r="F19" t="n">
         <v>1579.14</v>
       </c>
+      <c r="G19" t="n">
+        <v>1689.44</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -19022,6 +19172,9 @@
       <c r="F20" t="n">
         <v>1582.14</v>
       </c>
+      <c r="G20" t="n">
+        <v>1699.7</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -19044,6 +19197,9 @@
       <c r="F21" t="n">
         <v>1584.4</v>
       </c>
+      <c r="G21" t="n">
+        <v>1709.58</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -19066,6 +19222,9 @@
       <c r="F22" t="n">
         <v>1587.41</v>
       </c>
+      <c r="G22" t="n">
+        <v>1719.5</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -19088,6 +19247,9 @@
       <c r="F23" t="n">
         <v>1590.42</v>
       </c>
+      <c r="G23" t="n">
+        <v>1730.66</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -19110,6 +19272,9 @@
       <c r="F24" t="n">
         <v>1592.67</v>
       </c>
+      <c r="G24" t="n">
+        <v>1741.44</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -19132,6 +19297,9 @@
       <c r="F25" t="n">
         <v>1594.93</v>
       </c>
+      <c r="G25" t="n">
+        <v>1752.22</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -19154,6 +19322,9 @@
       <c r="F26" t="n">
         <v>1597.18</v>
       </c>
+      <c r="G26" t="n">
+        <v>1761.84</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -19176,6 +19347,9 @@
       <c r="F27" t="n">
         <v>1598.69</v>
       </c>
+      <c r="G27" t="n">
+        <v>1771.08</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -19197,6 +19371,9 @@
       </c>
       <c r="F28" t="n">
         <v>1601.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1780.32</v>
       </c>
     </row>
     <row r="29">
@@ -26982,6 +27159,9 @@
       <c r="F10" t="n">
         <v>506.54</v>
       </c>
+      <c r="G10" t="n">
+        <v>1154.61</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -27004,6 +27184,9 @@
       <c r="F11" t="n">
         <v>503.63</v>
       </c>
+      <c r="G11" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -27026,6 +27209,9 @@
       <c r="F12" t="n">
         <v>502.84</v>
       </c>
+      <c r="G12" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -27048,6 +27234,9 @@
       <c r="F13" t="n">
         <v>506.72</v>
       </c>
+      <c r="G13" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -27070,6 +27259,9 @@
       <c r="F14" t="n">
         <v>509.2</v>
       </c>
+      <c r="G14" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -27092,6 +27284,9 @@
       <c r="F15" t="n">
         <v>506.46</v>
       </c>
+      <c r="G15" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -27114,6 +27309,9 @@
       <c r="F16" t="n">
         <v>505.05</v>
       </c>
+      <c r="G16" t="n">
+        <v>1154.45</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -27136,6 +27334,9 @@
       <c r="F17" t="n">
         <v>508.49</v>
       </c>
+      <c r="G17" t="n">
+        <v>1154.45</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -27158,6 +27359,9 @@
       <c r="F18" t="n">
         <v>510.37</v>
       </c>
+      <c r="G18" t="n">
+        <v>1154.45</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -27180,6 +27384,9 @@
       <c r="F19" t="n">
         <v>511.27</v>
       </c>
+      <c r="G19" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -27202,6 +27409,9 @@
       <c r="F20" t="n">
         <v>511.27</v>
       </c>
+      <c r="G20" t="n">
+        <v>1153.81</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -27224,6 +27434,9 @@
       <c r="F21" t="n">
         <v>510.19</v>
       </c>
+      <c r="G21" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -27246,6 +27459,9 @@
       <c r="F22" t="n">
         <v>509.11</v>
       </c>
+      <c r="G22" t="n">
+        <v>1154.61</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -27268,6 +27484,9 @@
       <c r="F23" t="n">
         <v>510.01</v>
       </c>
+      <c r="G23" t="n">
+        <v>1154.29</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -27290,6 +27509,9 @@
       <c r="F24" t="n">
         <v>510.73</v>
       </c>
+      <c r="G24" t="n">
+        <v>1154.29</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -27312,6 +27534,9 @@
       <c r="F25" t="n">
         <v>509.38</v>
       </c>
+      <c r="G25" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -27334,6 +27559,9 @@
       <c r="F26" t="n">
         <v>508.05</v>
       </c>
+      <c r="G26" t="n">
+        <v>1154.13</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -27356,6 +27584,9 @@
       <c r="F27" t="n">
         <v>507.25</v>
       </c>
+      <c r="G27" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -27377,6 +27608,9 @@
       </c>
       <c r="F28" t="n">
         <v>506.98</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1154.13</v>
       </c>
     </row>
     <row r="29">
@@ -35114,7 +35348,7 @@
         <v>560.08</v>
       </c>
       <c r="G9" t="n">
-        <v>714.79</v>
+        <v>715.05</v>
       </c>
     </row>
     <row r="10">
@@ -35135,6 +35369,9 @@
       <c r="E10" t="n">
         <v>560.66</v>
       </c>
+      <c r="G10" t="n">
+        <v>715.55</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -35154,6 +35391,9 @@
       <c r="E11" t="n">
         <v>561.24</v>
       </c>
+      <c r="G11" t="n">
+        <v>716.0599999999999</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -35173,6 +35413,9 @@
       <c r="E12" t="n">
         <v>562.0700000000001</v>
       </c>
+      <c r="G12" t="n">
+        <v>716.5700000000001</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -35192,6 +35435,9 @@
       <c r="E13" t="n">
         <v>562.65</v>
       </c>
+      <c r="G13" t="n">
+        <v>717.08</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -35211,6 +35457,9 @@
       <c r="E14" t="n">
         <v>563.23</v>
       </c>
+      <c r="G14" t="n">
+        <v>717.59</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -35230,6 +35479,9 @@
       <c r="E15" t="n">
         <v>564.0599999999999</v>
       </c>
+      <c r="G15" t="n">
+        <v>718.09</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -35249,6 +35501,9 @@
       <c r="E16" t="n">
         <v>564.64</v>
       </c>
+      <c r="G16" t="n">
+        <v>718.6</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -35268,6 +35523,9 @@
       <c r="E17" t="n">
         <v>565.22</v>
       </c>
+      <c r="G17" t="n">
+        <v>719.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -35287,6 +35545,9 @@
       <c r="E18" t="n">
         <v>565.8</v>
       </c>
+      <c r="G18" t="n">
+        <v>719.62</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -35306,6 +35567,9 @@
       <c r="E19" t="n">
         <v>566.64</v>
       </c>
+      <c r="G19" t="n">
+        <v>720.13</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -35325,6 +35589,9 @@
       <c r="E20" t="n">
         <v>567.47</v>
       </c>
+      <c r="G20" t="n">
+        <v>720.64</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -35344,6 +35611,9 @@
       <c r="E21" t="n">
         <v>568.0599999999999</v>
       </c>
+      <c r="G21" t="n">
+        <v>721.65</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -35363,6 +35633,9 @@
       <c r="E22" t="n">
         <v>568.89</v>
       </c>
+      <c r="G22" t="n">
+        <v>722.67</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -35382,6 +35655,9 @@
       <c r="E23" t="n">
         <v>569.48</v>
       </c>
+      <c r="G23" t="n">
+        <v>723.6900000000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -35401,6 +35677,9 @@
       <c r="E24" t="n">
         <v>570.83</v>
       </c>
+      <c r="G24" t="n">
+        <v>725.22</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -35420,6 +35699,9 @@
       <c r="E25" t="n">
         <v>571.67</v>
       </c>
+      <c r="G25" t="n">
+        <v>726.24</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -35439,6 +35721,9 @@
       <c r="E26" t="n">
         <v>572.51</v>
       </c>
+      <c r="G26" t="n">
+        <v>726.75</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -35458,6 +35743,9 @@
       <c r="E27" t="n">
         <v>573.35</v>
       </c>
+      <c r="G27" t="n">
+        <v>727.77</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -35476,6 +35764,9 @@
       </c>
       <c r="E28" t="n">
         <v>574.45</v>
+      </c>
+      <c r="G28" t="n">
+        <v>728.79</v>
       </c>
     </row>
     <row r="29">
@@ -43021,7 +43312,7 @@
         <v>554.29</v>
       </c>
       <c r="G9" t="n">
-        <v>593.42</v>
+        <v>602.22</v>
       </c>
     </row>
     <row r="10">
@@ -43045,6 +43336,9 @@
       <c r="F10" t="n">
         <v>550.22</v>
       </c>
+      <c r="G10" t="n">
+        <v>607.35</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -43067,6 +43361,9 @@
       <c r="F11" t="n">
         <v>550.22</v>
       </c>
+      <c r="G11" t="n">
+        <v>610.29</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -43089,6 +43386,9 @@
       <c r="F12" t="n">
         <v>558.37</v>
       </c>
+      <c r="G12" t="n">
+        <v>607.35</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -43111,6 +43411,9 @@
       <c r="F13" t="n">
         <v>560.88</v>
       </c>
+      <c r="G13" t="n">
+        <v>607.72</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -43133,6 +43436,9 @@
       <c r="F14" t="n">
         <v>557.74</v>
       </c>
+      <c r="G14" t="n">
+        <v>608.09</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -43155,6 +43461,9 @@
       <c r="F15" t="n">
         <v>555.23</v>
       </c>
+      <c r="G15" t="n">
+        <v>611.02</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -43177,6 +43486,9 @@
       <c r="F16" t="n">
         <v>554.61</v>
       </c>
+      <c r="G16" t="n">
+        <v>608.09</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43199,6 +43511,9 @@
       <c r="F17" t="n">
         <v>556.8</v>
       </c>
+      <c r="G17" t="n">
+        <v>613.95</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -43221,6 +43536,9 @@
       <c r="F18" t="n">
         <v>561.5</v>
       </c>
+      <c r="G18" t="n">
+        <v>613.22</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -43243,6 +43561,9 @@
       <c r="F19" t="n">
         <v>562.13</v>
       </c>
+      <c r="G19" t="n">
+        <v>616.52</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43265,6 +43586,9 @@
       <c r="F20" t="n">
         <v>563.39</v>
       </c>
+      <c r="G20" t="n">
+        <v>604.42</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -43287,6 +43611,9 @@
       <c r="F21" t="n">
         <v>563.39</v>
       </c>
+      <c r="G21" t="n">
+        <v>596.35</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -43309,6 +43636,9 @@
       <c r="F22" t="n">
         <v>563.39</v>
       </c>
+      <c r="G22" t="n">
+        <v>600.75</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -43331,6 +43661,9 @@
       <c r="F23" t="n">
         <v>564.01</v>
       </c>
+      <c r="G23" t="n">
+        <v>620.55</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -43353,6 +43686,9 @@
       <c r="F24" t="n">
         <v>565.9</v>
       </c>
+      <c r="G24" t="n">
+        <v>624.95</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -43375,6 +43711,9 @@
       <c r="F25" t="n">
         <v>559.62</v>
       </c>
+      <c r="G25" t="n">
+        <v>630.09</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -43397,6 +43736,9 @@
       <c r="F26" t="n">
         <v>565.27</v>
       </c>
+      <c r="G26" t="n">
+        <v>633.02</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -43419,6 +43761,9 @@
       <c r="F27" t="n">
         <v>568.72</v>
       </c>
+      <c r="G27" t="n">
+        <v>630.09</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -43440,6 +43785,9 @@
       </c>
       <c r="F28" t="n">
         <v>574.05</v>
+      </c>
+      <c r="G28" t="n">
+        <v>627.89</v>
       </c>
     </row>
     <row r="29">
@@ -50945,7 +51293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L876"/>
+  <dimension ref="A1:L895"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84328,36 +84676,796 @@
         <v>46303</v>
       </c>
       <c r="B876" t="n">
-        <v>1511.87</v>
+        <v>1516.48</v>
       </c>
       <c r="C876" t="n">
-        <v>593.42</v>
+        <v>602.22</v>
       </c>
       <c r="D876" t="n">
         <v>1154.61</v>
       </c>
       <c r="E876" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="F876" t="n">
+        <v>1603.95</v>
+      </c>
+      <c r="G876" t="n">
+        <v>715.05</v>
+      </c>
+      <c r="H876" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="I876" t="n">
+        <v>64.59</v>
+      </c>
+      <c r="J876" t="n">
+        <v>5674.5</v>
+      </c>
+      <c r="K876" t="n">
+        <v>54.37</v>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B877" t="n">
+        <v>1530.12</v>
+      </c>
+      <c r="C877" t="n">
+        <v>607.35</v>
+      </c>
+      <c r="D877" t="n">
+        <v>1154.61</v>
+      </c>
+      <c r="E877" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="F877" t="n">
+        <v>1612.22</v>
+      </c>
+      <c r="G877" t="n">
+        <v>715.55</v>
+      </c>
+      <c r="H877" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="I877" t="n">
+        <v>65.56999999999999</v>
+      </c>
+      <c r="J877" t="n">
+        <v>5702.1</v>
+      </c>
+      <c r="K877" t="n">
+        <v>54.63</v>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="3" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B878" t="n">
+        <v>1530.85</v>
+      </c>
+      <c r="C878" t="n">
+        <v>610.29</v>
+      </c>
+      <c r="D878" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E878" t="n">
+        <v>82.13</v>
+      </c>
+      <c r="F878" t="n">
+        <v>1620.5</v>
+      </c>
+      <c r="G878" t="n">
+        <v>716.0599999999999</v>
+      </c>
+      <c r="H878" t="n">
+        <v>89.94</v>
+      </c>
+      <c r="I878" t="n">
+        <v>66.43000000000001</v>
+      </c>
+      <c r="J878" t="n">
+        <v>5714</v>
+      </c>
+      <c r="K878" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="3" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B879" t="n">
+        <v>1519.39</v>
+      </c>
+      <c r="C879" t="n">
+        <v>607.35</v>
+      </c>
+      <c r="D879" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E879" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F879" t="n">
+        <v>1627.26</v>
+      </c>
+      <c r="G879" t="n">
+        <v>716.5700000000001</v>
+      </c>
+      <c r="H879" t="n">
+        <v>89.06</v>
+      </c>
+      <c r="I879" t="n">
+        <v>67.38</v>
+      </c>
+      <c r="J879" t="n">
+        <v>5707.5</v>
+      </c>
+      <c r="K879" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B880" t="n">
+        <v>1515.02</v>
+      </c>
+      <c r="C880" t="n">
+        <v>607.72</v>
+      </c>
+      <c r="D880" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E880" t="n">
         <v>82.37</v>
       </c>
-      <c r="F876" t="n">
-        <v>1600.57</v>
-      </c>
-      <c r="G876" t="n">
-        <v>714.79</v>
-      </c>
-      <c r="H876" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="I876" t="n">
-        <v>64.28</v>
-      </c>
-      <c r="J876" t="n">
-        <v>5657.6</v>
-      </c>
-      <c r="K876" t="n">
-        <v>54.21</v>
-      </c>
-      <c r="L876" t="inlineStr">
+      <c r="F880" t="n">
+        <v>1634.78</v>
+      </c>
+      <c r="G880" t="n">
+        <v>717.08</v>
+      </c>
+      <c r="H880" t="n">
+        <v>89.45999999999999</v>
+      </c>
+      <c r="I880" t="n">
+        <v>68.22</v>
+      </c>
+      <c r="J880" t="n">
+        <v>5711.7</v>
+      </c>
+      <c r="K880" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B881" t="n">
+        <v>1517.45</v>
+      </c>
+      <c r="C881" t="n">
+        <v>608.09</v>
+      </c>
+      <c r="D881" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E881" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="F881" t="n">
+        <v>1644.22</v>
+      </c>
+      <c r="G881" t="n">
+        <v>717.59</v>
+      </c>
+      <c r="H881" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="I881" t="n">
+        <v>69</v>
+      </c>
+      <c r="J881" t="n">
+        <v>5724.6</v>
+      </c>
+      <c r="K881" t="n">
+        <v>54.85</v>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B882" t="n">
+        <v>1515.99</v>
+      </c>
+      <c r="C882" t="n">
+        <v>611.02</v>
+      </c>
+      <c r="D882" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E882" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F882" t="n">
+        <v>1652.96</v>
+      </c>
+      <c r="G882" t="n">
+        <v>718.09</v>
+      </c>
+      <c r="H882" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="I882" t="n">
+        <v>70.09</v>
+      </c>
+      <c r="J882" t="n">
+        <v>5734.5</v>
+      </c>
+      <c r="K882" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B883" t="n">
+        <v>1514.54</v>
+      </c>
+      <c r="C883" t="n">
+        <v>608.09</v>
+      </c>
+      <c r="D883" t="n">
+        <v>1154.45</v>
+      </c>
+      <c r="E883" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F883" t="n">
+        <v>1661.32</v>
+      </c>
+      <c r="G883" t="n">
+        <v>718.6</v>
+      </c>
+      <c r="H883" t="n">
+        <v>89.39</v>
+      </c>
+      <c r="I883" t="n">
+        <v>70.81999999999999</v>
+      </c>
+      <c r="J883" t="n">
+        <v>5739.2</v>
+      </c>
+      <c r="K883" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B884" t="n">
+        <v>1513.57</v>
+      </c>
+      <c r="C884" t="n">
+        <v>613.95</v>
+      </c>
+      <c r="D884" t="n">
+        <v>1154.45</v>
+      </c>
+      <c r="E884" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="F884" t="n">
+        <v>1670.44</v>
+      </c>
+      <c r="G884" t="n">
+        <v>719.11</v>
+      </c>
+      <c r="H884" t="n">
+        <v>89.04000000000001</v>
+      </c>
+      <c r="I884" t="n">
+        <v>71.73999999999999</v>
+      </c>
+      <c r="J884" t="n">
+        <v>5753.7</v>
+      </c>
+      <c r="K884" t="n">
+        <v>55.13</v>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="3" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B885" t="n">
+        <v>1511.39</v>
+      </c>
+      <c r="C885" t="n">
+        <v>613.22</v>
+      </c>
+      <c r="D885" t="n">
+        <v>1154.45</v>
+      </c>
+      <c r="E885" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="F885" t="n">
+        <v>1680.32</v>
+      </c>
+      <c r="G885" t="n">
+        <v>719.62</v>
+      </c>
+      <c r="H885" t="n">
+        <v>89.69</v>
+      </c>
+      <c r="I885" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="J885" t="n">
+        <v>5761.3</v>
+      </c>
+      <c r="K885" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="3" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B886" t="n">
+        <v>1510.66</v>
+      </c>
+      <c r="C886" t="n">
+        <v>616.52</v>
+      </c>
+      <c r="D886" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E886" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="F886" t="n">
+        <v>1689.44</v>
+      </c>
+      <c r="G886" t="n">
+        <v>720.13</v>
+      </c>
+      <c r="H886" t="n">
+        <v>89.78</v>
+      </c>
+      <c r="I886" t="n">
+        <v>74.54000000000001</v>
+      </c>
+      <c r="J886" t="n">
+        <v>5773.1</v>
+      </c>
+      <c r="K886" t="n">
+        <v>55.31</v>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B887" t="n">
+        <v>1509.69</v>
+      </c>
+      <c r="C887" t="n">
+        <v>604.42</v>
+      </c>
+      <c r="D887" t="n">
+        <v>1153.81</v>
+      </c>
+      <c r="E887" t="n">
+        <v>82.47</v>
+      </c>
+      <c r="F887" t="n">
+        <v>1699.7</v>
+      </c>
+      <c r="G887" t="n">
+        <v>720.64</v>
+      </c>
+      <c r="H887" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="I887" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="J887" t="n">
+        <v>5770.7</v>
+      </c>
+      <c r="K887" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B888" t="n">
+        <v>1517.2</v>
+      </c>
+      <c r="C888" t="n">
+        <v>596.35</v>
+      </c>
+      <c r="D888" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E888" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="F888" t="n">
+        <v>1709.58</v>
+      </c>
+      <c r="G888" t="n">
+        <v>721.65</v>
+      </c>
+      <c r="H888" t="n">
+        <v>90.13</v>
+      </c>
+      <c r="I888" t="n">
+        <v>77.03</v>
+      </c>
+      <c r="J888" t="n">
+        <v>5781.3</v>
+      </c>
+      <c r="K888" t="n">
+        <v>55.39</v>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B889" t="n">
+        <v>1526.21</v>
+      </c>
+      <c r="C889" t="n">
+        <v>600.75</v>
+      </c>
+      <c r="D889" t="n">
+        <v>1154.61</v>
+      </c>
+      <c r="E889" t="n">
+        <v>82.31999999999999</v>
+      </c>
+      <c r="F889" t="n">
+        <v>1719.5</v>
+      </c>
+      <c r="G889" t="n">
+        <v>722.67</v>
+      </c>
+      <c r="H889" t="n">
+        <v>89.23</v>
+      </c>
+      <c r="I889" t="n">
+        <v>78.81</v>
+      </c>
+      <c r="J889" t="n">
+        <v>5806.1</v>
+      </c>
+      <c r="K889" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B890" t="n">
+        <v>1523.77</v>
+      </c>
+      <c r="C890" t="n">
+        <v>620.55</v>
+      </c>
+      <c r="D890" t="n">
+        <v>1154.29</v>
+      </c>
+      <c r="E890" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F890" t="n">
+        <v>1730.66</v>
+      </c>
+      <c r="G890" t="n">
+        <v>723.6900000000001</v>
+      </c>
+      <c r="H890" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="I890" t="n">
+        <v>80.34999999999999</v>
+      </c>
+      <c r="J890" t="n">
+        <v>5835.2</v>
+      </c>
+      <c r="K890" t="n">
+        <v>55.91</v>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B891" t="n">
+        <v>1520.36</v>
+      </c>
+      <c r="C891" t="n">
+        <v>624.95</v>
+      </c>
+      <c r="D891" t="n">
+        <v>1154.29</v>
+      </c>
+      <c r="E891" t="n">
+        <v>82.37</v>
+      </c>
+      <c r="F891" t="n">
+        <v>1741.44</v>
+      </c>
+      <c r="G891" t="n">
+        <v>725.22</v>
+      </c>
+      <c r="H891" t="n">
+        <v>90.48</v>
+      </c>
+      <c r="I891" t="n">
+        <v>82.11</v>
+      </c>
+      <c r="J891" t="n">
+        <v>5848.6</v>
+      </c>
+      <c r="K891" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="3" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B892" t="n">
+        <v>1524.99</v>
+      </c>
+      <c r="C892" t="n">
+        <v>630.09</v>
+      </c>
+      <c r="D892" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E892" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F892" t="n">
+        <v>1752.22</v>
+      </c>
+      <c r="G892" t="n">
+        <v>726.24</v>
+      </c>
+      <c r="H892" t="n">
+        <v>89.52</v>
+      </c>
+      <c r="I892" t="n">
+        <v>83.55</v>
+      </c>
+      <c r="J892" t="n">
+        <v>5870</v>
+      </c>
+      <c r="K892" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="3" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B893" t="n">
+        <v>1527.67</v>
+      </c>
+      <c r="C893" t="n">
+        <v>633.02</v>
+      </c>
+      <c r="D893" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E893" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F893" t="n">
+        <v>1761.84</v>
+      </c>
+      <c r="G893" t="n">
+        <v>726.75</v>
+      </c>
+      <c r="H893" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="I893" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="J893" t="n">
+        <v>5885.7</v>
+      </c>
+      <c r="K893" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B894" t="n">
+        <v>1521.34</v>
+      </c>
+      <c r="C894" t="n">
+        <v>630.09</v>
+      </c>
+      <c r="D894" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E894" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="F894" t="n">
+        <v>1771.08</v>
+      </c>
+      <c r="G894" t="n">
+        <v>727.77</v>
+      </c>
+      <c r="H894" t="n">
+        <v>90.61</v>
+      </c>
+      <c r="I894" t="n">
+        <v>86.09</v>
+      </c>
+      <c r="J894" t="n">
+        <v>5887.3</v>
+      </c>
+      <c r="K894" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B895" t="n">
+        <v>1523.77</v>
+      </c>
+      <c r="C895" t="n">
+        <v>627.89</v>
+      </c>
+      <c r="D895" t="n">
+        <v>1154.13</v>
+      </c>
+      <c r="E895" t="n">
+        <v>82.18000000000001</v>
+      </c>
+      <c r="F895" t="n">
+        <v>1780.32</v>
+      </c>
+      <c r="G895" t="n">
+        <v>728.79</v>
+      </c>
+      <c r="H895" t="n">
+        <v>89.77</v>
+      </c>
+      <c r="I895" t="n">
+        <v>87.53</v>
+      </c>
+      <c r="J895" t="n">
+        <v>5897.1</v>
+      </c>
+      <c r="K895" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="L895" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -430,7 +430,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -700,7 +700,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1240,7 +1240,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1510,7 +1510,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-27</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3091,7 +3091,7 @@
         <v>45.61</v>
       </c>
       <c r="G28" t="n">
-        <v>56.5</v>
+        <v>56.52</v>
       </c>
     </row>
     <row r="29">
@@ -3114,6 +3114,9 @@
       </c>
       <c r="F29" t="n">
         <v>45.61</v>
+      </c>
+      <c r="G29" t="n">
+        <v>56.67</v>
       </c>
     </row>
     <row r="30">
@@ -11160,6 +11163,9 @@
       <c r="F29" t="n">
         <v>1213.57</v>
       </c>
+      <c r="G29" t="n">
+        <v>1526.21</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -19373,7 +19379,7 @@
         <v>1601.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1780.32</v>
+        <v>1780.71</v>
       </c>
     </row>
     <row r="29">
@@ -19396,6 +19402,9 @@
       </c>
       <c r="F29" t="n">
         <v>1603.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1788.41</v>
       </c>
     </row>
     <row r="30">
@@ -27634,6 +27643,9 @@
       <c r="F29" t="n">
         <v>506.28</v>
       </c>
+      <c r="G29" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -35787,6 +35799,9 @@
       <c r="E29" t="n">
         <v>575.29</v>
       </c>
+      <c r="G29" t="n">
+        <v>729.3</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -43787,7 +43802,7 @@
         <v>574.05</v>
       </c>
       <c r="G28" t="n">
-        <v>627.89</v>
+        <v>629.35</v>
       </c>
     </row>
     <row r="29">
@@ -43810,6 +43825,9 @@
       </c>
       <c r="F29" t="n">
         <v>575.3099999999999</v>
+      </c>
+      <c r="G29" t="n">
+        <v>633.76</v>
       </c>
     </row>
     <row r="30">
@@ -51293,7 +51311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L895"/>
+  <dimension ref="A1:L896"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85439,33 +85457,73 @@
         <v>1523.77</v>
       </c>
       <c r="C895" t="n">
-        <v>627.89</v>
+        <v>629.35</v>
       </c>
       <c r="D895" t="n">
         <v>1154.13</v>
       </c>
       <c r="E895" t="n">
-        <v>82.18000000000001</v>
+        <v>82.23</v>
       </c>
       <c r="F895" t="n">
-        <v>1780.32</v>
+        <v>1780.71</v>
       </c>
       <c r="G895" t="n">
         <v>728.79</v>
       </c>
       <c r="H895" t="n">
-        <v>89.77</v>
+        <v>90.23</v>
       </c>
       <c r="I895" t="n">
-        <v>87.53</v>
+        <v>87.64</v>
       </c>
       <c r="J895" t="n">
-        <v>5897.1</v>
+        <v>5899</v>
       </c>
       <c r="K895" t="n">
-        <v>56.5</v>
+        <v>56.52</v>
       </c>
       <c r="L895" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B896" t="n">
+        <v>1526.21</v>
+      </c>
+      <c r="C896" t="n">
+        <v>633.76</v>
+      </c>
+      <c r="D896" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E896" t="n">
+        <v>81.98</v>
+      </c>
+      <c r="F896" t="n">
+        <v>1788.41</v>
+      </c>
+      <c r="G896" t="n">
+        <v>729.3</v>
+      </c>
+      <c r="H896" t="n">
+        <v>89.92</v>
+      </c>
+      <c r="I896" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="J896" t="n">
+        <v>5914.4</v>
+      </c>
+      <c r="K896" t="n">
+        <v>56.67</v>
+      </c>
+      <c r="L896" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -430,7 +430,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -700,7 +700,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1240,7 +1240,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1510,7 +1510,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-28</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3140,6 +3140,9 @@
       <c r="F30" t="n">
         <v>45.69</v>
       </c>
+      <c r="G30" t="n">
+        <v>56.72</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -11188,6 +11191,9 @@
       <c r="F30" t="n">
         <v>1218.59</v>
       </c>
+      <c r="G30" t="n">
+        <v>1528.65</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -19404,7 +19410,7 @@
         <v>1603.2</v>
       </c>
       <c r="G29" t="n">
-        <v>1788.41</v>
+        <v>1789.95</v>
       </c>
     </row>
     <row r="30">
@@ -19427,6 +19433,9 @@
       </c>
       <c r="F30" t="n">
         <v>1604.7</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1798.47</v>
       </c>
     </row>
     <row r="31">
@@ -27644,7 +27653,7 @@
         <v>506.28</v>
       </c>
       <c r="G29" t="n">
-        <v>1154.77</v>
+        <v>1154.45</v>
       </c>
     </row>
     <row r="30">
@@ -27667,6 +27676,9 @@
       </c>
       <c r="F30" t="n">
         <v>511.45</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1154.45</v>
       </c>
     </row>
     <row r="31">
@@ -35821,6 +35833,9 @@
       <c r="E30" t="n">
         <v>576.38</v>
       </c>
+      <c r="G30" t="n">
+        <v>729.8099999999999</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -43827,7 +43842,7 @@
         <v>575.3099999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>633.76</v>
+        <v>633.02</v>
       </c>
     </row>
     <row r="30">
@@ -43850,6 +43865,9 @@
       </c>
       <c r="F30" t="n">
         <v>573.4299999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>626.42</v>
       </c>
     </row>
     <row r="31">
@@ -51311,7 +51329,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L896"/>
+  <dimension ref="A1:L897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85497,33 +85515,73 @@
         <v>1526.21</v>
       </c>
       <c r="C896" t="n">
-        <v>633.76</v>
+        <v>633.02</v>
       </c>
       <c r="D896" t="n">
-        <v>1154.77</v>
+        <v>1154.45</v>
       </c>
       <c r="E896" t="n">
-        <v>81.98</v>
+        <v>82.06</v>
       </c>
       <c r="F896" t="n">
-        <v>1788.41</v>
+        <v>1789.95</v>
       </c>
       <c r="G896" t="n">
         <v>729.3</v>
       </c>
       <c r="H896" t="n">
-        <v>89.92</v>
+        <v>90.05</v>
       </c>
       <c r="I896" t="n">
-        <v>88.94</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="J896" t="n">
-        <v>5914.4</v>
+        <v>5915</v>
       </c>
       <c r="K896" t="n">
         <v>56.67</v>
       </c>
       <c r="L896" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B897" t="n">
+        <v>1528.65</v>
+      </c>
+      <c r="C897" t="n">
+        <v>626.42</v>
+      </c>
+      <c r="D897" t="n">
+        <v>1154.45</v>
+      </c>
+      <c r="E897" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="F897" t="n">
+        <v>1798.47</v>
+      </c>
+      <c r="G897" t="n">
+        <v>729.8099999999999</v>
+      </c>
+      <c r="H897" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="I897" t="n">
+        <v>90.87</v>
+      </c>
+      <c r="J897" t="n">
+        <v>5919.9</v>
+      </c>
+      <c r="K897" t="n">
+        <v>56.72</v>
+      </c>
+      <c r="L897" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -430,7 +430,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -700,7 +700,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1240,7 +1240,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1510,7 +1510,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-29</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3141,7 +3141,7 @@
         <v>45.69</v>
       </c>
       <c r="G30" t="n">
-        <v>56.72</v>
+        <v>56.74</v>
       </c>
     </row>
     <row r="31">
@@ -3164,6 +3164,9 @@
       </c>
       <c r="F31" t="n">
         <v>45.84</v>
+      </c>
+      <c r="G31" t="n">
+        <v>56.87</v>
       </c>
     </row>
     <row r="32">
@@ -11192,7 +11195,7 @@
         <v>1218.59</v>
       </c>
       <c r="G30" t="n">
-        <v>1528.65</v>
+        <v>1529.63</v>
       </c>
     </row>
     <row r="31">
@@ -11215,6 +11218,9 @@
       </c>
       <c r="F31" t="n">
         <v>1225.25</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1536.49</v>
       </c>
     </row>
     <row r="32">
@@ -19435,7 +19441,7 @@
         <v>1604.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1798.47</v>
+        <v>1800.02</v>
       </c>
     </row>
     <row r="31">
@@ -19458,6 +19464,9 @@
       </c>
       <c r="F31" t="n">
         <v>1605.46</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1809.36</v>
       </c>
     </row>
     <row r="32">
@@ -27702,6 +27711,9 @@
       <c r="F31" t="n">
         <v>519.86</v>
       </c>
+      <c r="G31" t="n">
+        <v>1154.77</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -35834,7 +35846,7 @@
         <v>576.38</v>
       </c>
       <c r="G30" t="n">
-        <v>729.8099999999999</v>
+        <v>730.3200000000001</v>
       </c>
     </row>
     <row r="31">
@@ -35854,6 +35866,9 @@
       </c>
       <c r="E31" t="n">
         <v>577.48</v>
+      </c>
+      <c r="G31" t="n">
+        <v>730.83</v>
       </c>
     </row>
     <row r="32">
@@ -43867,7 +43882,7 @@
         <v>573.4299999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>626.42</v>
+        <v>624.95</v>
       </c>
     </row>
     <row r="31">
@@ -43890,6 +43905,9 @@
       </c>
       <c r="F31" t="n">
         <v>574.05</v>
+      </c>
+      <c r="G31" t="n">
+        <v>622.02</v>
       </c>
     </row>
     <row r="32">
@@ -51329,7 +51347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L897"/>
+  <dimension ref="A1:L898"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85552,36 +85570,76 @@
         <v>46324</v>
       </c>
       <c r="B897" t="n">
-        <v>1528.65</v>
+        <v>1529.63</v>
       </c>
       <c r="C897" t="n">
-        <v>626.42</v>
+        <v>624.95</v>
       </c>
       <c r="D897" t="n">
         <v>1154.45</v>
       </c>
       <c r="E897" t="n">
-        <v>82.08</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="F897" t="n">
-        <v>1798.47</v>
+        <v>1800.02</v>
       </c>
       <c r="G897" t="n">
-        <v>729.8099999999999</v>
+        <v>730.3200000000001</v>
       </c>
       <c r="H897" t="n">
-        <v>89.59999999999999</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="I897" t="n">
-        <v>90.87</v>
+        <v>91.36</v>
       </c>
       <c r="J897" t="n">
-        <v>5919.9</v>
+        <v>5921.5</v>
       </c>
       <c r="K897" t="n">
-        <v>56.72</v>
+        <v>56.74</v>
       </c>
       <c r="L897" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="3" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B898" t="n">
+        <v>1536.49</v>
+      </c>
+      <c r="C898" t="n">
+        <v>622.02</v>
+      </c>
+      <c r="D898" t="n">
+        <v>1154.77</v>
+      </c>
+      <c r="E898" t="n">
+        <v>82.28</v>
+      </c>
+      <c r="F898" t="n">
+        <v>1809.36</v>
+      </c>
+      <c r="G898" t="n">
+        <v>730.83</v>
+      </c>
+      <c r="H898" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="I898" t="n">
+        <v>93.18000000000001</v>
+      </c>
+      <c r="J898" t="n">
+        <v>5935.8</v>
+      </c>
+      <c r="K898" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="L898" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>

--- a/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
+++ b/output/Data and Chart Outputs/chile_hydro_reservoirs.xlsx
@@ -160,7 +160,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile hydro reservoirs, total of 6 generation reservoirs (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -430,7 +430,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile, Colbún reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -700,7 +700,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile, Lago Laja volume (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -970,7 +970,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile, Ralco reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1240,7 +1240,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile, Laguna del Maule volume (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1510,7 +1510,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-30</a:t>
+              <a:t>Chile, Rapel reservoir volume (DGA) - water year (Oct-Sep), data to 2026-10-31</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -3166,7 +3166,7 @@
         <v>45.84</v>
       </c>
       <c r="G31" t="n">
-        <v>56.87</v>
+        <v>56.92</v>
       </c>
     </row>
     <row r="32">
@@ -3189,6 +3189,9 @@
       </c>
       <c r="F32" t="n">
         <v>46</v>
+      </c>
+      <c r="G32" t="n">
+        <v>57</v>
       </c>
     </row>
     <row r="33">
@@ -11220,7 +11223,7 @@
         <v>1225.25</v>
       </c>
       <c r="G31" t="n">
-        <v>1536.49</v>
+        <v>1537.47</v>
       </c>
     </row>
     <row r="32">
@@ -11243,6 +11246,9 @@
       </c>
       <c r="F32" t="n">
         <v>1228.08</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1536.98</v>
       </c>
     </row>
     <row r="33">
@@ -19466,7 +19472,7 @@
         <v>1605.46</v>
       </c>
       <c r="G31" t="n">
-        <v>1809.36</v>
+        <v>1811.69</v>
       </c>
     </row>
     <row r="32">
@@ -19489,6 +19495,9 @@
       </c>
       <c r="F32" t="n">
         <v>1606.21</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1819.47</v>
       </c>
     </row>
     <row r="33">
@@ -27712,7 +27721,7 @@
         <v>519.86</v>
       </c>
       <c r="G31" t="n">
-        <v>1154.77</v>
+        <v>1153.97</v>
       </c>
     </row>
     <row r="32">
@@ -27735,6 +27744,9 @@
       </c>
       <c r="F32" t="n">
         <v>530.52</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1154.77</v>
       </c>
     </row>
     <row r="33">
@@ -35868,7 +35880,7 @@
         <v>577.48</v>
       </c>
       <c r="G31" t="n">
-        <v>730.83</v>
+        <v>731.34</v>
       </c>
     </row>
     <row r="32">
@@ -35888,6 +35900,9 @@
       </c>
       <c r="E32" t="n">
         <v>532.65</v>
+      </c>
+      <c r="G32" t="n">
+        <v>731.85</v>
       </c>
     </row>
     <row r="33">
@@ -43907,7 +43922,7 @@
         <v>574.05</v>
       </c>
       <c r="G31" t="n">
-        <v>622.02</v>
+        <v>624.22</v>
       </c>
     </row>
     <row r="32">
@@ -43930,6 +43945,9 @@
       </c>
       <c r="F32" t="n">
         <v>576.25</v>
+      </c>
+      <c r="G32" t="n">
+        <v>624.22</v>
       </c>
     </row>
     <row r="33">
@@ -51347,7 +51365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L898"/>
+  <dimension ref="A1:L899"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85610,36 +85628,76 @@
         <v>46325</v>
       </c>
       <c r="B898" t="n">
-        <v>1536.49</v>
+        <v>1537.47</v>
       </c>
       <c r="C898" t="n">
-        <v>622.02</v>
+        <v>624.22</v>
       </c>
       <c r="D898" t="n">
+        <v>1153.97</v>
+      </c>
+      <c r="E898" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="F898" t="n">
+        <v>1811.69</v>
+      </c>
+      <c r="G898" t="n">
+        <v>731.34</v>
+      </c>
+      <c r="H898" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="I898" t="n">
+        <v>93.77</v>
+      </c>
+      <c r="J898" t="n">
+        <v>5941</v>
+      </c>
+      <c r="K898" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>DGA online (daily median)</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="3" t="n">
+        <v>46326</v>
+      </c>
+      <c r="B899" t="n">
+        <v>1536.98</v>
+      </c>
+      <c r="C899" t="n">
+        <v>624.22</v>
+      </c>
+      <c r="D899" t="n">
         <v>1154.77</v>
       </c>
-      <c r="E898" t="n">
-        <v>82.28</v>
-      </c>
-      <c r="F898" t="n">
-        <v>1809.36</v>
-      </c>
-      <c r="G898" t="n">
-        <v>730.83</v>
-      </c>
-      <c r="H898" t="n">
-        <v>89.98999999999999</v>
-      </c>
-      <c r="I898" t="n">
-        <v>93.18000000000001</v>
-      </c>
-      <c r="J898" t="n">
-        <v>5935.8</v>
-      </c>
-      <c r="K898" t="n">
-        <v>56.87</v>
-      </c>
-      <c r="L898" t="inlineStr">
+      <c r="E899" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="F899" t="n">
+        <v>1819.47</v>
+      </c>
+      <c r="G899" t="n">
+        <v>731.85</v>
+      </c>
+      <c r="H899" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="I899" t="n">
+        <v>96.04000000000001</v>
+      </c>
+      <c r="J899" t="n">
+        <v>5949.4</v>
+      </c>
+      <c r="K899" t="n">
+        <v>57</v>
+      </c>
+      <c r="L899" t="inlineStr">
         <is>
           <t>DGA online (daily median)</t>
         </is>
